--- a/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
+++ b/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
@@ -3554,7 +3554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I130"/>
+  <dimension ref="A2:I303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3607,11 +3607,6 @@
           <t>Your Finding</t>
         </is>
       </c>
-      <c r="E6" s="50" t="n"/>
-      <c r="F6" s="50" t="n"/>
-      <c r="G6" s="50" t="n"/>
-      <c r="H6" s="50" t="n"/>
-      <c r="I6" s="51" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="B7" s="23" t="inlineStr">
@@ -3629,11 +3624,6 @@
           <t>SuiteQL REST API</t>
         </is>
       </c>
-      <c r="E7" s="50" t="n"/>
-      <c r="F7" s="50" t="n"/>
-      <c r="G7" s="50" t="n"/>
-      <c r="H7" s="50" t="n"/>
-      <c r="I7" s="51" t="n"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="B8" s="23" t="inlineStr">
@@ -3651,11 +3641,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E8" s="50" t="n"/>
-      <c r="F8" s="50" t="n"/>
-      <c r="G8" s="50" t="n"/>
-      <c r="H8" s="50" t="n"/>
-      <c r="I8" s="51" t="n"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="B9" s="23" t="inlineStr">
@@ -3673,11 +3658,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E9" s="50" t="n"/>
-      <c r="F9" s="50" t="n"/>
-      <c r="G9" s="50" t="n"/>
-      <c r="H9" s="50" t="n"/>
-      <c r="I9" s="51" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="B10" s="23" t="inlineStr">
@@ -3695,11 +3675,6 @@
           <t>Fabric Tables</t>
         </is>
       </c>
-      <c r="E10" s="50" t="n"/>
-      <c r="F10" s="50" t="n"/>
-      <c r="G10" s="50" t="n"/>
-      <c r="H10" s="50" t="n"/>
-      <c r="I10" s="51" t="n"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="B11" s="23" t="inlineStr">
@@ -3717,11 +3692,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="E11" s="50" t="n"/>
-      <c r="F11" s="50" t="n"/>
-      <c r="G11" s="50" t="n"/>
-      <c r="H11" s="50" t="n"/>
-      <c r="I11" s="51" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="B12" s="23" t="inlineStr">
@@ -3739,11 +3709,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="E12" s="50" t="n"/>
-      <c r="F12" s="50" t="n"/>
-      <c r="G12" s="50" t="n"/>
-      <c r="H12" s="50" t="n"/>
-      <c r="I12" s="51" t="n"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
       <c r="B13" s="23" t="inlineStr">
@@ -3758,14 +3723,9 @@
       </c>
       <c r="D13" s="44" t="inlineStr">
         <is>
-          <t>~10,500 rows across 10 key tables</t>
-        </is>
-      </c>
-      <c r="E13" s="50" t="n"/>
-      <c r="F13" s="50" t="n"/>
-      <c r="G13" s="50" t="n"/>
-      <c r="H13" s="50" t="n"/>
-      <c r="I13" s="51" t="n"/>
+          <t>10,377 rows across 10 key tables</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="B14" s="23" t="inlineStr">
@@ -3783,11 +3743,6 @@
           <t>2020-01-01 to 2025-03-01</t>
         </is>
       </c>
-      <c r="E14" s="50" t="n"/>
-      <c r="F14" s="50" t="n"/>
-      <c r="G14" s="50" t="n"/>
-      <c r="H14" s="50" t="n"/>
-      <c r="I14" s="51" t="n"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="B15" s="23" t="inlineStr">
@@ -3805,11 +3760,6 @@
           <t>NetSuite SuiteQL 2024.1</t>
         </is>
       </c>
-      <c r="E15" s="50" t="n"/>
-      <c r="F15" s="50" t="n"/>
-      <c r="G15" s="50" t="n"/>
-      <c r="H15" s="50" t="n"/>
-      <c r="I15" s="51" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="B16" s="23" t="inlineStr">
@@ -3827,11 +3777,6 @@
           <t>Minor null rate on subsidiary_id in TRANSACTION</t>
         </is>
       </c>
-      <c r="E16" s="50" t="n"/>
-      <c r="F16" s="50" t="n"/>
-      <c r="G16" s="50" t="n"/>
-      <c r="H16" s="50" t="n"/>
-      <c r="I16" s="51" t="n"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="B17" s="23" t="inlineStr">
@@ -3849,11 +3794,6 @@
           <t>TBD – awaiting TFG confirmation</t>
         </is>
       </c>
-      <c r="E17" s="50" t="n"/>
-      <c r="F17" s="50" t="n"/>
-      <c r="G17" s="50" t="n"/>
-      <c r="H17" s="50" t="n"/>
-      <c r="I17" s="51" t="n"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="B18" s="23" t="inlineStr">
@@ -3871,11 +3811,6 @@
           <t>Scheduled for 2025-03-15</t>
         </is>
       </c>
-      <c r="E18" s="50" t="n"/>
-      <c r="F18" s="50" t="n"/>
-      <c r="G18" s="50" t="n"/>
-      <c r="H18" s="50" t="n"/>
-      <c r="I18" s="51" t="n"/>
     </row>
     <row r="20" ht="7.5" customHeight="1"/>
     <row r="21" ht="15.75" customHeight="1">
@@ -3891,13 +3826,6 @@
           <t>Key tables to profile for NetSuite: TRANSACTION, TRANSACTIONLINE, CUSTOMER, LOCATION, ACCOUNT, DEPARTMENT, EMPLOYEE, VENDOR, ITEM, CURRENCY</t>
         </is>
       </c>
-      <c r="C22" s="50" t="n"/>
-      <c r="D22" s="50" t="n"/>
-      <c r="E22" s="50" t="n"/>
-      <c r="F22" s="50" t="n"/>
-      <c r="G22" s="50" t="n"/>
-      <c r="H22" s="50" t="n"/>
-      <c r="I22" s="50" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="47" t="inlineStr">
@@ -3922,11 +3850,6 @@
           <t>Result</t>
         </is>
       </c>
-      <c r="E24" s="50" t="n"/>
-      <c r="F24" s="50" t="n"/>
-      <c r="G24" s="50" t="n"/>
-      <c r="H24" s="50" t="n"/>
-      <c r="I24" s="51" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="25" t="inlineStr">
@@ -3944,11 +3867,6 @@
           <t>CUSTOMER</t>
         </is>
       </c>
-      <c r="E25" s="50" t="n"/>
-      <c r="F25" s="50" t="n"/>
-      <c r="G25" s="50" t="n"/>
-      <c r="H25" s="50" t="n"/>
-      <c r="I25" s="51" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="25" t="inlineStr">
@@ -3966,11 +3884,6 @@
           <t>Master record for all customers / billing entities</t>
         </is>
       </c>
-      <c r="E26" s="50" t="n"/>
-      <c r="F26" s="50" t="n"/>
-      <c r="G26" s="50" t="n"/>
-      <c r="H26" s="50" t="n"/>
-      <c r="I26" s="51" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="25" t="inlineStr">
@@ -3988,11 +3901,6 @@
           <t>One row = one customer</t>
         </is>
       </c>
-      <c r="E27" s="50" t="n"/>
-      <c r="F27" s="50" t="n"/>
-      <c r="G27" s="50" t="n"/>
-      <c r="H27" s="50" t="n"/>
-      <c r="I27" s="51" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="25" t="inlineStr">
@@ -4006,13 +3914,8 @@
         </is>
       </c>
       <c r="D28" s="43" t="n">
-        <v>485</v>
-      </c>
-      <c r="E28" s="50" t="n"/>
-      <c r="F28" s="50" t="n"/>
-      <c r="G28" s="50" t="n"/>
-      <c r="H28" s="50" t="n"/>
-      <c r="I28" s="51" t="n"/>
+        <v>458</v>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="25" t="inlineStr">
@@ -4030,11 +3933,6 @@
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
-      <c r="E29" s="50" t="n"/>
-      <c r="F29" s="50" t="n"/>
-      <c r="G29" s="50" t="n"/>
-      <c r="H29" s="50" t="n"/>
-      <c r="I29" s="51" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="25" t="inlineStr">
@@ -4052,11 +3950,6 @@
           <t>id (surrogate)</t>
         </is>
       </c>
-      <c r="E30" s="50" t="n"/>
-      <c r="F30" s="50" t="n"/>
-      <c r="G30" s="50" t="n"/>
-      <c r="H30" s="50" t="n"/>
-      <c r="I30" s="51" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="25" t="inlineStr">
@@ -4074,11 +3967,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E31" s="50" t="n"/>
-      <c r="F31" s="50" t="n"/>
-      <c r="G31" s="50" t="n"/>
-      <c r="H31" s="50" t="n"/>
-      <c r="I31" s="51" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="25" t="inlineStr">
@@ -4096,11 +3984,6 @@
           <t>D1 – Customers &amp; Locations</t>
         </is>
       </c>
-      <c r="E32" s="50" t="n"/>
-      <c r="F32" s="50" t="n"/>
-      <c r="G32" s="50" t="n"/>
-      <c r="H32" s="50" t="n"/>
-      <c r="I32" s="51" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="25" t="inlineStr">
@@ -4118,11 +4001,6 @@
           <t>CUSTOMER</t>
         </is>
       </c>
-      <c r="E33" s="50" t="n"/>
-      <c r="F33" s="50" t="n"/>
-      <c r="G33" s="50" t="n"/>
-      <c r="H33" s="50" t="n"/>
-      <c r="I33" s="51" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="25" t="inlineStr">
@@ -4140,11 +4018,6 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="E34" s="50" t="n"/>
-      <c r="F34" s="50" t="n"/>
-      <c r="G34" s="50" t="n"/>
-      <c r="H34" s="50" t="n"/>
-      <c r="I34" s="51" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="49" t="inlineStr">
@@ -4152,13 +4025,6 @@
           <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
         </is>
       </c>
-      <c r="C35" s="50" t="n"/>
-      <c r="D35" s="50" t="n"/>
-      <c r="E35" s="50" t="n"/>
-      <c r="F35" s="50" t="n"/>
-      <c r="G35" s="50" t="n"/>
-      <c r="H35" s="50" t="n"/>
-      <c r="I35" s="50" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="45" t="inlineStr">
@@ -4218,10 +4084,8 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>~500</t>
-        </is>
+      <c r="E37" s="16" t="n">
+        <v>458</v>
       </c>
       <c r="F37" s="16" t="n">
         <v>1</v>
@@ -4231,7 +4095,7 @@
       </c>
       <c r="H37" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls</t>
+          <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
       <c r="I37" s="16" t="inlineStr">
@@ -4256,10 +4120,8 @@
           <t>2%</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>~490</t>
-        </is>
+      <c r="E38" s="15" t="n">
+        <v>449</v>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
@@ -4298,10 +4160,8 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>~420</t>
-        </is>
+      <c r="E39" s="16" t="n">
+        <v>389</v>
       </c>
       <c r="F39" s="16" t="n"/>
       <c r="G39" s="16" t="n"/>
@@ -4332,10 +4192,8 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>~480</t>
-        </is>
+      <c r="E40" s="15" t="n">
+        <v>440</v>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
@@ -4406,13 +4264,6 @@
           <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
         </is>
       </c>
-      <c r="C43" s="50" t="n"/>
-      <c r="D43" s="50" t="n"/>
-      <c r="E43" s="50" t="n"/>
-      <c r="F43" s="50" t="n"/>
-      <c r="G43" s="50" t="n"/>
-      <c r="H43" s="50" t="n"/>
-      <c r="I43" s="50" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="45" t="inlineStr">
@@ -4554,11 +4405,6 @@
           <t>Result</t>
         </is>
       </c>
-      <c r="E50" s="50" t="n"/>
-      <c r="F50" s="50" t="n"/>
-      <c r="G50" s="50" t="n"/>
-      <c r="H50" s="50" t="n"/>
-      <c r="I50" s="51" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="25" t="inlineStr">
@@ -4576,11 +4422,6 @@
           <t>VENDOR</t>
         </is>
       </c>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="50" t="n"/>
-      <c r="G51" s="50" t="n"/>
-      <c r="H51" s="50" t="n"/>
-      <c r="I51" s="51" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="25" t="inlineStr">
@@ -4598,11 +4439,6 @@
           <t>Master record for all vendors and suppliers</t>
         </is>
       </c>
-      <c r="E52" s="50" t="n"/>
-      <c r="F52" s="50" t="n"/>
-      <c r="G52" s="50" t="n"/>
-      <c r="H52" s="50" t="n"/>
-      <c r="I52" s="51" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="25" t="inlineStr">
@@ -4620,11 +4456,6 @@
           <t>One row = one vendor</t>
         </is>
       </c>
-      <c r="E53" s="50" t="n"/>
-      <c r="F53" s="50" t="n"/>
-      <c r="G53" s="50" t="n"/>
-      <c r="H53" s="50" t="n"/>
-      <c r="I53" s="51" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="25" t="inlineStr">
@@ -4638,13 +4469,8 @@
         </is>
       </c>
       <c r="D54" s="43" t="n">
-        <v>242</v>
-      </c>
-      <c r="E54" s="50" t="n"/>
-      <c r="F54" s="50" t="n"/>
-      <c r="G54" s="50" t="n"/>
-      <c r="H54" s="50" t="n"/>
-      <c r="I54" s="51" t="n"/>
+        <v>223</v>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="25" t="inlineStr">
@@ -4662,11 +4488,6 @@
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
-      <c r="E55" s="50" t="n"/>
-      <c r="F55" s="50" t="n"/>
-      <c r="G55" s="50" t="n"/>
-      <c r="H55" s="50" t="n"/>
-      <c r="I55" s="51" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="25" t="inlineStr">
@@ -4684,11 +4505,6 @@
           <t>id (surrogate)</t>
         </is>
       </c>
-      <c r="E56" s="50" t="n"/>
-      <c r="F56" s="50" t="n"/>
-      <c r="G56" s="50" t="n"/>
-      <c r="H56" s="50" t="n"/>
-      <c r="I56" s="51" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="25" t="inlineStr">
@@ -4706,11 +4522,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E57" s="50" t="n"/>
-      <c r="F57" s="50" t="n"/>
-      <c r="G57" s="50" t="n"/>
-      <c r="H57" s="50" t="n"/>
-      <c r="I57" s="51" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="25" t="inlineStr">
@@ -4728,11 +4539,6 @@
           <t>D5 – Financials</t>
         </is>
       </c>
-      <c r="E58" s="50" t="n"/>
-      <c r="F58" s="50" t="n"/>
-      <c r="G58" s="50" t="n"/>
-      <c r="H58" s="50" t="n"/>
-      <c r="I58" s="51" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="25" t="inlineStr">
@@ -4750,11 +4556,6 @@
           <t>VENDOR</t>
         </is>
       </c>
-      <c r="E59" s="50" t="n"/>
-      <c r="F59" s="50" t="n"/>
-      <c r="G59" s="50" t="n"/>
-      <c r="H59" s="50" t="n"/>
-      <c r="I59" s="51" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="25" t="inlineStr">
@@ -4772,11 +4573,6 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="E60" s="50" t="n"/>
-      <c r="F60" s="50" t="n"/>
-      <c r="G60" s="50" t="n"/>
-      <c r="H60" s="50" t="n"/>
-      <c r="I60" s="51" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="B61" s="49" t="inlineStr">
@@ -4784,13 +4580,6 @@
           <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
         </is>
       </c>
-      <c r="C61" s="50" t="n"/>
-      <c r="D61" s="50" t="n"/>
-      <c r="E61" s="50" t="n"/>
-      <c r="F61" s="50" t="n"/>
-      <c r="G61" s="50" t="n"/>
-      <c r="H61" s="50" t="n"/>
-      <c r="I61" s="50" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="45" t="inlineStr">
@@ -4850,10 +4639,8 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>~200</t>
-        </is>
+      <c r="E63" s="16" t="n">
+        <v>223</v>
       </c>
       <c r="F63" s="16" t="n">
         <v>1</v>
@@ -4863,7 +4650,7 @@
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls</t>
+          <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
@@ -4888,10 +4675,8 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>~200</t>
-        </is>
+      <c r="E64" s="15" t="n">
+        <v>223</v>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
@@ -4926,10 +4711,8 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="E65" s="16" t="inlineStr">
-        <is>
-          <t>~160</t>
-        </is>
+      <c r="E65" s="16" t="n">
+        <v>178</v>
       </c>
       <c r="F65" s="16" t="n"/>
       <c r="G65" s="16" t="n"/>
@@ -4960,10 +4743,8 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>~195</t>
-        </is>
+      <c r="E66" s="15" t="n">
+        <v>216</v>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
@@ -5034,13 +4815,6 @@
           <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
         </is>
       </c>
-      <c r="C69" s="50" t="n"/>
-      <c r="D69" s="50" t="n"/>
-      <c r="E69" s="50" t="n"/>
-      <c r="F69" s="50" t="n"/>
-      <c r="G69" s="50" t="n"/>
-      <c r="H69" s="50" t="n"/>
-      <c r="I69" s="50" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="45" t="inlineStr">
@@ -5182,11 +4956,6 @@
           <t>Result</t>
         </is>
       </c>
-      <c r="E76" s="50" t="n"/>
-      <c r="F76" s="50" t="n"/>
-      <c r="G76" s="50" t="n"/>
-      <c r="H76" s="50" t="n"/>
-      <c r="I76" s="51" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="B77" s="25" t="inlineStr">
@@ -5204,11 +4973,6 @@
           <t>ITEM</t>
         </is>
       </c>
-      <c r="E77" s="50" t="n"/>
-      <c r="F77" s="50" t="n"/>
-      <c r="G77" s="50" t="n"/>
-      <c r="H77" s="50" t="n"/>
-      <c r="I77" s="51" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="B78" s="25" t="inlineStr">
@@ -5226,11 +4990,6 @@
           <t>Product and service catalog items</t>
         </is>
       </c>
-      <c r="E78" s="50" t="n"/>
-      <c r="F78" s="50" t="n"/>
-      <c r="G78" s="50" t="n"/>
-      <c r="H78" s="50" t="n"/>
-      <c r="I78" s="51" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="B79" s="25" t="inlineStr">
@@ -5248,11 +5007,6 @@
           <t>One row = one item / SKU</t>
         </is>
       </c>
-      <c r="E79" s="50" t="n"/>
-      <c r="F79" s="50" t="n"/>
-      <c r="G79" s="50" t="n"/>
-      <c r="H79" s="50" t="n"/>
-      <c r="I79" s="51" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="B80" s="25" t="inlineStr">
@@ -5266,13 +5020,8 @@
         </is>
       </c>
       <c r="D80" s="43" t="n">
-        <v>987</v>
-      </c>
-      <c r="E80" s="50" t="n"/>
-      <c r="F80" s="50" t="n"/>
-      <c r="G80" s="50" t="n"/>
-      <c r="H80" s="50" t="n"/>
-      <c r="I80" s="51" t="n"/>
+        <v>972</v>
+      </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="B81" s="25" t="inlineStr">
@@ -5290,11 +5039,6 @@
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
-      <c r="E81" s="50" t="n"/>
-      <c r="F81" s="50" t="n"/>
-      <c r="G81" s="50" t="n"/>
-      <c r="H81" s="50" t="n"/>
-      <c r="I81" s="51" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="B82" s="25" t="inlineStr">
@@ -5312,11 +5056,6 @@
           <t>id (surrogate)</t>
         </is>
       </c>
-      <c r="E82" s="50" t="n"/>
-      <c r="F82" s="50" t="n"/>
-      <c r="G82" s="50" t="n"/>
-      <c r="H82" s="50" t="n"/>
-      <c r="I82" s="51" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="B83" s="25" t="inlineStr">
@@ -5334,11 +5073,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E83" s="50" t="n"/>
-      <c r="F83" s="50" t="n"/>
-      <c r="G83" s="50" t="n"/>
-      <c r="H83" s="50" t="n"/>
-      <c r="I83" s="51" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="B84" s="25" t="inlineStr">
@@ -5356,11 +5090,6 @@
           <t>D2 – Contracts &amp; Revenue</t>
         </is>
       </c>
-      <c r="E84" s="50" t="n"/>
-      <c r="F84" s="50" t="n"/>
-      <c r="G84" s="50" t="n"/>
-      <c r="H84" s="50" t="n"/>
-      <c r="I84" s="51" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="B85" s="25" t="inlineStr">
@@ -5378,11 +5107,6 @@
           <t>ITEM</t>
         </is>
       </c>
-      <c r="E85" s="50" t="n"/>
-      <c r="F85" s="50" t="n"/>
-      <c r="G85" s="50" t="n"/>
-      <c r="H85" s="50" t="n"/>
-      <c r="I85" s="51" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="25" t="inlineStr">
@@ -5400,11 +5124,6 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="E86" s="50" t="n"/>
-      <c r="F86" s="50" t="n"/>
-      <c r="G86" s="50" t="n"/>
-      <c r="H86" s="50" t="n"/>
-      <c r="I86" s="51" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="B87" s="49" t="inlineStr">
@@ -5412,13 +5131,6 @@
           <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
         </is>
       </c>
-      <c r="C87" s="50" t="n"/>
-      <c r="D87" s="50" t="n"/>
-      <c r="E87" s="50" t="n"/>
-      <c r="F87" s="50" t="n"/>
-      <c r="G87" s="50" t="n"/>
-      <c r="H87" s="50" t="n"/>
-      <c r="I87" s="50" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="B88" s="45" t="inlineStr">
@@ -5478,10 +5190,8 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="E89" s="16" t="inlineStr">
-        <is>
-          <t>~1000</t>
-        </is>
+      <c r="E89" s="16" t="n">
+        <v>972</v>
       </c>
       <c r="F89" s="16" t="n">
         <v>1</v>
@@ -5491,7 +5201,7 @@
       </c>
       <c r="H89" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls</t>
+          <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
       <c r="I89" s="16" t="inlineStr">
@@ -5516,10 +5226,8 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="E90" s="15" t="inlineStr">
-        <is>
-          <t>~1000</t>
-        </is>
+      <c r="E90" s="15" t="n">
+        <v>972</v>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
@@ -5531,7 +5239,11 @@
           <t>ITEM-9999</t>
         </is>
       </c>
-      <c r="H90" s="15" t="inlineStr"/>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>Unique item code</t>
+        </is>
+      </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -5554,10 +5266,8 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="E91" s="16" t="inlineStr">
-        <is>
-          <t>~920</t>
-        </is>
+      <c r="E91" s="16" t="n">
+        <v>894</v>
       </c>
       <c r="F91" s="16" t="n"/>
       <c r="G91" s="16" t="n"/>
@@ -5588,10 +5298,8 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="E92" s="15" t="inlineStr">
-        <is>
-          <t>~800</t>
-        </is>
+      <c r="E92" s="15" t="n">
+        <v>778</v>
       </c>
       <c r="F92" s="15" t="n">
         <v>0.01</v>
@@ -5626,10 +5334,8 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="E93" s="16" t="inlineStr">
-        <is>
-          <t>~950</t>
-        </is>
+      <c r="E93" s="16" t="n">
+        <v>923</v>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
@@ -5664,13 +5370,6 @@
           <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
         </is>
       </c>
-      <c r="C95" s="50" t="n"/>
-      <c r="D95" s="50" t="n"/>
-      <c r="E95" s="50" t="n"/>
-      <c r="F95" s="50" t="n"/>
-      <c r="G95" s="50" t="n"/>
-      <c r="H95" s="50" t="n"/>
-      <c r="I95" s="50" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="B96" s="45" t="inlineStr">
@@ -5789,6 +5488,13 @@
       <c r="H99" s="16" t="n"/>
     </row>
     <row r="100" ht="7.5" customHeight="1"/>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Table 4: TRANSACTION</t>
+        </is>
+      </c>
+    </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="41" t="inlineStr">
         <is>
@@ -5802,13 +5508,11 @@
           <t>Trace the question: 'What is total revenue by customer this fiscal year?' through this source system. Document each step: what table you'd use, what's available, and where the chain breaks.</t>
         </is>
       </c>
-      <c r="C103" s="50" t="n"/>
-      <c r="D103" s="50" t="n"/>
-      <c r="E103" s="50" t="n"/>
-      <c r="F103" s="50" t="n"/>
-      <c r="G103" s="50" t="n"/>
-      <c r="H103" s="50" t="n"/>
-      <c r="I103" s="50" t="n"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>TRANSACTION</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="B104" s="45" t="inlineStr">
@@ -5823,7 +5527,7 @@
       </c>
       <c r="D104" s="45" t="inlineStr">
         <is>
-          <t>Table(s) Used</t>
+          <t>Records all financial transactions (invoices, payments, journals)</t>
         </is>
       </c>
       <c r="E104" s="45" t="inlineStr">
@@ -5855,7 +5559,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>CUSTOMER / ENTITY</t>
+          <t>One row = one transaction header</t>
         </is>
       </c>
       <c r="E105" s="4" t="n"/>
@@ -5873,10 +5577,8 @@
           <t>Get all contracts linked to each customer</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>CONTRACT / TRANSACTION</t>
-        </is>
+      <c r="D106" s="6" t="n">
+        <v>4993</v>
       </c>
       <c r="E106" s="6" t="n"/>
       <c r="F106" s="6" t="n"/>
@@ -5895,7 +5597,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>INVOICE / TRANSACTION</t>
+          <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
       <c r="E107" s="4" t="n"/>
@@ -5915,7 +5617,7 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>INVOICE + date filter</t>
+          <t>id (surrogate)</t>
         </is>
       </c>
       <c r="E108" s="6" t="n"/>
@@ -5935,7 +5637,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Cross-system check</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E109" s="4" t="n"/>
@@ -5955,14 +5657,27 @@
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Cross-system check</t>
+          <t>D5 – Financials</t>
         </is>
       </c>
       <c r="E110" s="6" t="n"/>
       <c r="F110" s="6" t="n"/>
       <c r="G110" s="6" t="n"/>
     </row>
-    <row r="112" ht="7.5" customHeight="1"/>
+    <row r="111">
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>TRANSACTION, INVOICE, JOURNAL_ENTRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="7.5" customHeight="1">
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="41" t="inlineStr">
         <is>
@@ -6010,245 +5725,260 @@
     <row r="115" ht="18" customHeight="1">
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>CUSTOMER</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C115" s="16" t="inlineStr">
         <is>
-          <t>datecreated</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="E115" s="16" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>4993</v>
       </c>
       <c r="F115" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G115" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G115" s="16" t="n">
+        <v>99999</v>
       </c>
       <c r="H115" s="16" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>PK – no nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>VENDOR</t>
+          <t>tranid</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>datecreated</t>
+          <t>VARCHAR</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="F116" s="15" t="n">
-        <v>5</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>4993</v>
+      </c>
+      <c r="F116" s="15" t="inlineStr">
+        <is>
+          <t>TRN-00001</t>
+        </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>TRN-09999</t>
         </is>
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Unique transaction reference</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>ITEM</t>
+          <t>recordtype</t>
         </is>
       </c>
       <c r="C117" s="16" t="inlineStr">
         <is>
-          <t>lastmodifieddate</t>
+          <t>VARCHAR</t>
         </is>
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="E117" s="16" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="F117" s="16" t="n">
-        <v>4</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F117" s="16" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
       </c>
       <c r="G117" s="16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>vendorbill</t>
         </is>
       </c>
       <c r="H117" s="16" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>8 distinct types</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>TRANSACTION</t>
+          <t>trandate</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>trandate</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="F118" s="15" t="n">
-        <v>6</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>1797</v>
+      </c>
+      <c r="F118" s="15" t="inlineStr">
+        <is>
+          <t>2020-01-02</t>
+        </is>
       </c>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>1797 unique dates</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>EMPLOYEE</t>
+          <t>entity_id</t>
         </is>
       </c>
       <c r="C119" s="16" t="inlineStr">
         <is>
-          <t>datecreated</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D119" s="16" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="E119" s="16" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>499</v>
       </c>
       <c r="F119" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="G119" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G119" s="16" t="n">
+        <v>9999</v>
       </c>
       <c r="H119" s="16" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>2% null – FK risk</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>ACCOUNT</t>
+          <t>subsidiary_id</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>lastmodifieddate</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>5</v>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>5</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>2% null – known issue</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="121" ht="7.5" customHeight="1">
       <c r="B121" t="inlineStr">
         <is>
-          <t>SUBSIDIARY</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>lastmodifieddate</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>4793</v>
       </c>
       <c r="F121" t="n">
-        <v>4</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Investigate load delay</t>
+        <v>0.01</v>
+      </c>
+      <c r="G121" t="n">
+        <v>999999.99</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -6262,70 +5992,107 @@
     <row r="123" ht="19.5" customHeight="1">
       <c r="B123" s="45" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>entity_id</t>
         </is>
       </c>
       <c r="C123" s="45" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>CUSTOMER</t>
         </is>
       </c>
       <c r="D123" s="45" t="inlineStr">
         <is>
-          <t>Your Notes</t>
-        </is>
-      </c>
-      <c r="E123" s="50" t="n"/>
-      <c r="F123" s="50" t="n"/>
-      <c r="G123" s="50" t="n"/>
-      <c r="H123" s="50" t="n"/>
-      <c r="I123" s="51" t="n"/>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>98</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="B124" s="23" t="inlineStr">
         <is>
-          <t>Overall system RAG</t>
+          <t>subsidiary_id</t>
         </is>
       </c>
       <c r="C124" s="24" t="inlineStr">
         <is>
-          <t>GREEN / AMBER / RED — is this source usable for the canonical model build?</t>
+          <t>SUBSIDIARY</t>
         </is>
       </c>
       <c r="D124" s="44" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="E124" s="50" t="n"/>
-      <c r="F124" s="50" t="n"/>
-      <c r="G124" s="50" t="n"/>
-      <c r="H124" s="50" t="n"/>
-      <c r="I124" s="51" t="n"/>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>95</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="B125" s="23" t="inlineStr">
         <is>
-          <t>Top 3 issues found</t>
+          <t>department_id</t>
         </is>
       </c>
       <c r="C125" s="24" t="inlineStr">
         <is>
-          <t>List the most important quality or coverage issues discovered</t>
+          <t>DEPARTMENT</t>
         </is>
       </c>
       <c r="D125" s="43" t="inlineStr">
         <is>
-          <t>1. Null subsidiary_id on ~2% of TRANSACTION rows
-2. DEPARTMENT row count lower than expected
-3. No direct FK from SALESORDER to CONTRACT</t>
-        </is>
-      </c>
-      <c r="E125" s="50" t="n"/>
-      <c r="F125" s="50" t="n"/>
-      <c r="G125" s="50" t="n"/>
-      <c r="H125" s="50" t="n"/>
-      <c r="I125" s="51" t="n"/>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>12</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="B126" s="23" t="inlineStr">
@@ -6338,21 +6105,12 @@
           <t>Which tables/API endpoints should be in scope for Phase 2 build?</t>
         </is>
       </c>
-      <c r="D126" s="44" t="inlineStr">
-        <is>
-          <t>Fabric Tables (pipeline confirmed PASS)</t>
-        </is>
-      </c>
-      <c r="E126" s="50" t="n"/>
-      <c r="F126" s="50" t="n"/>
-      <c r="G126" s="50" t="n"/>
-      <c r="H126" s="50" t="n"/>
-      <c r="I126" s="51" t="n"/>
+      <c r="D126" s="44" t="n"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="B127" s="23" t="inlineStr">
         <is>
-          <t>Entity resolution readiness</t>
+          <t>Table 5: EMPLOYEE</t>
         </is>
       </c>
       <c r="C127" s="24" t="inlineStr">
@@ -6360,16 +6118,7 @@
           <t>Which entity fields exist for cross-system matching? How clean are they?</t>
         </is>
       </c>
-      <c r="D127" s="43" t="inlineStr">
-        <is>
-          <t>CUSTOMER and VENDOR joinable on entity_id; EMPLOYEE separate</t>
-        </is>
-      </c>
-      <c r="E127" s="50" t="n"/>
-      <c r="F127" s="50" t="n"/>
-      <c r="G127" s="50" t="n"/>
-      <c r="H127" s="50" t="n"/>
-      <c r="I127" s="51" t="n"/>
+      <c r="D127" s="43" t="n"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="B128" s="23" t="inlineStr">
@@ -6382,16 +6131,7 @@
           <t>Anything that prevents completing this profile by Discovery deadline?</t>
         </is>
       </c>
-      <c r="D128" s="44" t="inlineStr">
-        <is>
-          <t>None — pipeline accessible</t>
-        </is>
-      </c>
-      <c r="E128" s="50" t="n"/>
-      <c r="F128" s="50" t="n"/>
-      <c r="G128" s="50" t="n"/>
-      <c r="H128" s="50" t="n"/>
-      <c r="I128" s="51" t="n"/>
+      <c r="D128" s="44" t="n"/>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="B129" s="23" t="inlineStr">
@@ -6406,14 +6146,9 @@
       </c>
       <c r="D129" s="43" t="inlineStr">
         <is>
-          <t>Proceed to field-level profiling for TRANSACTION and CUSTOMER</t>
-        </is>
-      </c>
-      <c r="E129" s="50" t="n"/>
-      <c r="F129" s="50" t="n"/>
-      <c r="G129" s="50" t="n"/>
-      <c r="H129" s="50" t="n"/>
-      <c r="I129" s="51" t="n"/>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="B130" s="23" t="inlineStr">
@@ -6428,90 +6163,2353 @@
       </c>
       <c r="D130" s="44" t="inlineStr">
         <is>
+          <t>HR employee master used for approvals and assignments</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>One row = one employee</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="D132" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2020-01-01 – 2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>id (surrogate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>D3 – Workforce</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>132</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>PK – no nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>entityid</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>132</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>EMP-150</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Unique employee code</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>firstname</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>131</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Zoe</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>lastname</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>131</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>125</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>5% null</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>hiredate</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>128</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2015-01-15</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>5</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>5</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1% null</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>2</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>department_id</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Table 6: ACCOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ACCOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Chart of accounts for GL posting</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>One row = one GL account</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="D158" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2020-01-01 – 2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>id (surrogate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>D5 – Financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>GL_ACCOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>256</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>PK – no nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>acctnumber</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>256</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Unique account number</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>acctname</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>253</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Accounts Pay</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Wages Exp</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>12</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>OtherExpense</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>12 account types</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>238</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Table 7: SUBSIDIARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Legal entities / subsidiaries within NetSuite OneWorld</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>One row = one subsidiary</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="D184" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2020-01-01 – 2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>id (surrogate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>D5 – Financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="n">
+        <v>20</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>PK – no nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Acme AU</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Zurich SA</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>6</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>6 currencies</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>5% null country</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>-17</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Table 8: DEPARTMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DEPARTMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Cost centre / department classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>One row = one department</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="D210" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2020-01-01 – 2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>id (surrogate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>D5 – Financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>DEPARTMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>65</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" t="n">
+        <v>50</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>PK – no nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>64</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2% null names</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>5</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>5</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>4% null – orphan risk</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>62</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>2</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Table 9: SALESORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SALESORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Sales orders linked to customers and items</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>One row = one sales order header</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="D236" t="n">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2020-01-01 – 2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>id (surrogate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>D2 – Contracts &amp; Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>SALES_ORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>2531</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>PK – no nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>tranid</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>2531</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>SO-00001</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>SO-09999</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Unique order reference</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>trandate</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2020-01-03</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>1620 unique dates</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>506</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>1% null – FK to CUSTOMER</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>DECIMAL</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>2480</v>
+      </c>
+      <c r="F249" t="n">
+        <v>50</v>
+      </c>
+      <c r="G249" t="n">
+        <v>99999.99000000001</v>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>6</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Billed</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>6 order statuses</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>CUSTOMER</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>22</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>8</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Table 10: PURCHASEORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>PURCHASEORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Purchase orders raised against vendors</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>One row = one purchase order header</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="D262" t="n">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2020-01-01 – 2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>id (surrogate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>D5 – Financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>PURCHASE_ORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>766</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1</v>
+      </c>
+      <c r="G271" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>PK – no nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>tranid</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>766</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>PO-00001</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>PO-03999</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Unique PO reference</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>trandate</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>720</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>2020-01-05</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>720 unique dates</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>184</v>
+      </c>
+      <c r="F274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G274" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>2% null – FK to VENDOR</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>DECIMAL</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>743</v>
+      </c>
+      <c r="F275" t="n">
+        <v>10</v>
+      </c>
+      <c r="G275" t="n">
+        <v>49999.99</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>1% null amounts</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>5</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>PendingReceipt</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>5 statuses</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>VENDOR</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>16</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>5</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Section D – Data Freshness</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>datecreated</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>3</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Within SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>VENDOR</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>datecreated</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>6</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Investigate load delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>4</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Investigate load delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>TRANSACTION</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>trandate</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>3</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Within SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>datecreated</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>4</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Investigate load delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ACCOUNT</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>3</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Within SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>5</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Investigate load delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>6</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Investigate load delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>SALESORDER</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>trandate</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>1</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Within SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>PURCHASEORDER</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>trandate</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>2</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Within SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Section E – Engineer Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>1. Null subsidiary_id on 100 TRANSACTION rows (2.0%)
+2. DEPARTMENT: 3 rows with null subsidiary_id (4.6%) – orphan risk
+3. No direct FK from SALESORDER to CONTRACT
+4. VENDOR: 45 rows with null email (20.2%) – enrich before CRM migration
+5. PURCHASEORDER: 15 rows with null entity_id (2.0%) – verify vendor onboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Fabric Tables (pipeline confirmed PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>CUSTOMER and VENDOR joinable on entity_id; EMPLOYEE separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>None — pipeline accessible</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Proceed to field-level profiling for TRANSACTION and CUSTOMER</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="D303" t="inlineStr">
+        <is>
           <t>Confirm fiscal year definition used in trandate filters</t>
         </is>
       </c>
-      <c r="E130" s="50" t="n"/>
-      <c r="F130" s="50" t="n"/>
-      <c r="G130" s="50" t="n"/>
-      <c r="H130" s="50" t="n"/>
-      <c r="I130" s="51" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D57:I57"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="D126:I126"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D53:I53"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="D125:I125"/>
-    <mergeCell ref="A113:I113"/>
-    <mergeCell ref="D86:I86"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="D56:I56"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D58:I58"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D127:I127"/>
-    <mergeCell ref="A122:I122"/>
-    <mergeCell ref="D83:I83"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="D130:I130"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D82:I82"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="D51:I51"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D129:I129"/>
-    <mergeCell ref="B69:I69"/>
-    <mergeCell ref="D123:I123"/>
-    <mergeCell ref="D85:I85"/>
-    <mergeCell ref="B103:I103"/>
-    <mergeCell ref="B87:I87"/>
-    <mergeCell ref="D54:I54"/>
-    <mergeCell ref="A102:I102"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="D79:I79"/>
-    <mergeCell ref="D59:I59"/>
-    <mergeCell ref="D50:I50"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D81:I81"/>
-    <mergeCell ref="D128:I128"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="D80:I80"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D52:I52"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="D124:I124"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
+++ b/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
@@ -3554,7 +3554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I303"/>
+  <dimension ref="A2:L303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="D13" s="44" t="inlineStr">
         <is>
-          <t>10,377 rows across 10 key tables</t>
+          <t>10,636 rows across 10 key tables</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="D28" s="43" t="n">
-        <v>458</v>
+        <v>513</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="E37" s="16" t="n">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="F37" s="16" t="n">
         <v>1</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="E38" s="15" t="n">
-        <v>449</v>
+        <v>503</v>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="E39" s="16" t="n">
-        <v>389</v>
+        <v>436</v>
       </c>
       <c r="F39" s="16" t="n"/>
       <c r="G39" s="16" t="n"/>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="E40" s="15" t="n">
-        <v>440</v>
+        <v>492</v>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="D54" s="43" t="n">
-        <v>223</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="E63" s="16" t="n">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="F63" s="16" t="n">
         <v>1</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="E64" s="15" t="n">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="E65" s="16" t="n">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="F65" s="16" t="n"/>
       <c r="G65" s="16" t="n"/>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="E66" s="15" t="n">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="D80" s="43" t="n">
-        <v>972</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="E89" s="16" t="n">
-        <v>972</v>
+        <v>1011</v>
       </c>
       <c r="F89" s="16" t="n">
         <v>1</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="E90" s="15" t="n">
-        <v>972</v>
+        <v>1011</v>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="E91" s="16" t="n">
-        <v>894</v>
+        <v>930</v>
       </c>
       <c r="F91" s="16" t="n"/>
       <c r="G91" s="16" t="n"/>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="E92" s="15" t="n">
-        <v>778</v>
+        <v>809</v>
       </c>
       <c r="F92" s="15" t="n">
         <v>0.01</v>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="E93" s="16" t="n">
-        <v>923</v>
+        <v>960</v>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
@@ -5489,201 +5489,192 @@
     </row>
     <row r="100" ht="7.5" customHeight="1"/>
     <row r="101">
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="47" t="inlineStr">
         <is>
           <t>Table 4: TRANSACTION</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="41" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t xml:space="preserve">  C  |  COVERAGE CASCADE — Can you answer 'revenue by customer' from this system alone?</t>
         </is>
       </c>
+      <c r="B102" s="48" t="n"/>
+      <c r="C102" s="48" t="n"/>
+      <c r="D102" s="48" t="n"/>
     </row>
     <row r="103" ht="31.5" customHeight="1">
-      <c r="B103" s="42" t="inlineStr">
+      <c r="B103" s="25" t="inlineStr">
         <is>
           <t>Trace the question: 'What is total revenue by customer this fiscal year?' through this source system. Document each step: what table you'd use, what's available, and where the chain breaks.</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="C103" s="24" t="n"/>
+      <c r="D103" s="44" t="inlineStr">
         <is>
           <t>TRANSACTION</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="B104" s="45" t="inlineStr">
+      <c r="B104" s="25" t="inlineStr">
         <is>
           <t>Step #</t>
         </is>
       </c>
-      <c r="C104" s="45" t="inlineStr">
+      <c r="C104" s="24" t="inlineStr">
         <is>
           <t>Question / Join Required</t>
         </is>
       </c>
-      <c r="D104" s="45" t="inlineStr">
+      <c r="D104" s="43" t="inlineStr">
         <is>
           <t>Records all financial transactions (invoices, payments, journals)</t>
         </is>
       </c>
-      <c r="E104" s="45" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Available in This System?</t>
         </is>
       </c>
-      <c r="F104" s="45" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Gap / Breakage Point</t>
         </is>
       </c>
-      <c r="G104" s="45" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>RAG</t>
         </is>
       </c>
     </row>
     <row r="105" ht="21.75" customHeight="1">
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B105" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C105" s="26" t="inlineStr">
+      <c r="C105" s="24" t="inlineStr">
         <is>
           <t>Get all customers in this system</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D105" s="44" t="inlineStr">
         <is>
           <t>One row = one transaction header</t>
         </is>
       </c>
-      <c r="E105" s="4" t="n"/>
-      <c r="F105" s="4" t="n"/>
-      <c r="G105" s="4" t="n"/>
     </row>
     <row r="106" ht="21.75" customHeight="1">
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B106" s="25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C106" s="27" t="inlineStr">
+      <c r="C106" s="24" t="inlineStr">
         <is>
           <t>Get all contracts linked to each customer</t>
         </is>
       </c>
-      <c r="D106" s="6" t="n">
-        <v>4993</v>
-      </c>
-      <c r="E106" s="6" t="n"/>
-      <c r="F106" s="6" t="n"/>
-      <c r="G106" s="6" t="n"/>
+      <c r="D106" s="43" t="n">
+        <v>5047</v>
+      </c>
     </row>
     <row r="107" ht="21.75" customHeight="1">
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C107" s="26" t="inlineStr">
+      <c r="C107" s="24" t="inlineStr">
         <is>
           <t>Get invoices linked to each contract</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="4" t="n"/>
     </row>
     <row r="108" ht="21.75" customHeight="1">
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B108" s="25" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C108" s="27" t="inlineStr">
+      <c r="C108" s="24" t="inlineStr">
         <is>
           <t>Sum invoice amounts by customer, filter by fiscal year</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D108" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
         </is>
       </c>
-      <c r="E108" s="6" t="n"/>
-      <c r="F108" s="6" t="n"/>
-      <c r="G108" s="6" t="n"/>
     </row>
     <row r="109" ht="21.75" customHeight="1">
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C109" s="26" t="inlineStr">
+      <c r="C109" s="24" t="inlineStr">
         <is>
           <t>Does this system cover ALL customers? (or only some divisions?)</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E109" s="4" t="n"/>
-      <c r="F109" s="4" t="n"/>
-      <c r="G109" s="4" t="n"/>
     </row>
     <row r="110" ht="21.75" customHeight="1">
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B110" s="25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C110" s="27" t="inlineStr">
+      <c r="C110" s="24" t="inlineStr">
         <is>
           <t>Any customers in other systems not in this one?</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D110" s="43" t="inlineStr">
         <is>
           <t>D5 – Financials</t>
         </is>
       </c>
-      <c r="E110" s="6" t="n"/>
-      <c r="F110" s="6" t="n"/>
-      <c r="G110" s="6" t="n"/>
     </row>
     <row r="111">
-      <c r="D111" t="inlineStr">
+      <c r="B111" s="25" t="n"/>
+      <c r="C111" s="24" t="n"/>
+      <c r="D111" s="44" t="inlineStr">
         <is>
           <t>TRANSACTION, INVOICE, JOURNAL_ENTRY</t>
         </is>
       </c>
     </row>
     <row r="112" ht="7.5" customHeight="1">
-      <c r="D112" t="inlineStr">
+      <c r="B112" s="25" t="n"/>
+      <c r="C112" s="24" t="n"/>
+      <c r="D112" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="41" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t xml:space="preserve">  D  |  DATA FRESHNESS — Is the data current enough to be trusted?</t>
         </is>
       </c>
+      <c r="B113" s="49" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="B114" s="45" t="inlineStr">
@@ -5721,6 +5712,7 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="I114" s="45" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="B115" s="16" t="inlineStr">
@@ -5739,7 +5731,7 @@
         </is>
       </c>
       <c r="E115" s="16" t="n">
-        <v>4993</v>
+        <v>5047</v>
       </c>
       <c r="F115" s="16" t="n">
         <v>1</v>
@@ -5752,7 +5744,7 @@
           <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I115" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
@@ -5775,7 +5767,7 @@
         </is>
       </c>
       <c r="E116" s="15" t="n">
-        <v>4993</v>
+        <v>5047</v>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
@@ -5792,7 +5784,7 @@
           <t>Unique transaction reference</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I116" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
@@ -5832,7 +5824,7 @@
           <t>8 distinct types</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
@@ -5855,7 +5847,7 @@
         </is>
       </c>
       <c r="E118" s="15" t="n">
-        <v>1797</v>
+        <v>1817</v>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -5869,10 +5861,10 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>1797 unique dates</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
+          <t>1817 unique dates</t>
+        </is>
+      </c>
+      <c r="I118" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
@@ -5895,7 +5887,7 @@
         </is>
       </c>
       <c r="E119" s="16" t="n">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="F119" s="16" t="n">
         <v>1</v>
@@ -5908,50 +5900,50 @@
           <t>2% null – FK risk</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I119" s="16" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="15" t="inlineStr">
         <is>
           <t>subsidiary_id</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="15" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="15" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G120" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H120" s="15" t="inlineStr">
         <is>
           <t>2% null – known issue</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I120" s="15" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="121" ht="7.5" customHeight="1">
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="49" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
@@ -5967,7 +5959,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4793</v>
+        <v>4845</v>
       </c>
       <c r="F121" t="n">
         <v>0.01</v>
@@ -5983,158 +5975,163 @@
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="41" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t xml:space="preserve">  E  |  ENGINEER SUMMARY — Your overall assessment and flags for the Discovery report</t>
         </is>
       </c>
+      <c r="B122" s="45" t="n"/>
+      <c r="C122" s="45" t="n"/>
+      <c r="D122" s="45" t="n"/>
+      <c r="E122" s="45" t="n"/>
+      <c r="F122" s="45" t="n"/>
+      <c r="G122" s="45" t="n"/>
+      <c r="H122" s="45" t="n"/>
     </row>
     <row r="123" ht="19.5" customHeight="1">
-      <c r="B123" s="45" t="inlineStr">
+      <c r="B123" s="16" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="C123" s="45" t="inlineStr">
+      <c r="C123" s="16" t="inlineStr">
         <is>
           <t>CUSTOMER</t>
         </is>
       </c>
-      <c r="D123" s="45" t="inlineStr">
+      <c r="D123" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" s="16" t="n">
         <v>98</v>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" s="16" t="inlineStr">
         <is>
           <t>2.0%</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G123" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H123" s="16" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
-      <c r="B124" s="23" t="inlineStr">
+      <c r="B124" s="15" t="inlineStr">
         <is>
           <t>subsidiary_id</t>
         </is>
       </c>
-      <c r="C124" s="24" t="inlineStr">
+      <c r="C124" s="15" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
         </is>
       </c>
-      <c r="D124" s="44" t="inlineStr">
+      <c r="D124" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" s="15" t="inlineStr">
         <is>
           <t>1.9%</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G124" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H124" s="15" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
-      <c r="B125" s="23" t="inlineStr">
+      <c r="B125" s="16" t="inlineStr">
         <is>
           <t>department_id</t>
         </is>
       </c>
-      <c r="C125" s="24" t="inlineStr">
+      <c r="C125" s="16" t="inlineStr">
         <is>
           <t>DEPARTMENT</t>
         </is>
       </c>
-      <c r="D125" s="43" t="inlineStr">
+      <c r="D125" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" s="16" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G125" s="16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H125" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
-      <c r="B126" s="23" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Recommended ingestion path</t>
         </is>
       </c>
-      <c r="C126" s="24" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Which tables/API endpoints should be in scope for Phase 2 build?</t>
         </is>
       </c>
-      <c r="D126" s="44" t="n"/>
     </row>
     <row r="127" ht="30" customHeight="1">
-      <c r="B127" s="23" t="inlineStr">
+      <c r="B127" s="47" t="inlineStr">
         <is>
           <t>Table 5: EMPLOYEE</t>
         </is>
       </c>
-      <c r="C127" s="24" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Which entity fields exist for cross-system matching? How clean are they?</t>
         </is>
       </c>
-      <c r="D127" s="43" t="n"/>
     </row>
     <row r="128" ht="30" customHeight="1">
-      <c r="B128" s="23" t="inlineStr">
+      <c r="B128" s="48" t="inlineStr">
         <is>
           <t>Blockers for Discovery</t>
         </is>
       </c>
-      <c r="C128" s="24" t="inlineStr">
+      <c r="C128" s="48" t="inlineStr">
         <is>
           <t>Anything that prevents completing this profile by Discovery deadline?</t>
         </is>
       </c>
-      <c r="D128" s="44" t="n"/>
+      <c r="D128" s="48" t="n"/>
     </row>
     <row r="129" ht="30" customHeight="1">
-      <c r="B129" s="23" t="inlineStr">
+      <c r="B129" s="25" t="inlineStr">
         <is>
           <t>Recommended next action</t>
         </is>
@@ -6144,14 +6141,14 @@
           <t>What should the team do based on this profile?</t>
         </is>
       </c>
-      <c r="D129" s="43" t="inlineStr">
+      <c r="D129" s="44" t="inlineStr">
         <is>
           <t>EMPLOYEE</t>
         </is>
       </c>
     </row>
     <row r="130" ht="30" customHeight="1">
-      <c r="B130" s="23" t="inlineStr">
+      <c r="B130" s="25" t="inlineStr">
         <is>
           <t>Open questions for TFG SME</t>
         </is>
@@ -6161,282 +6158,313 @@
           <t>Questions to raise in the SME interview for this system</t>
         </is>
       </c>
-      <c r="D130" s="44" t="inlineStr">
+      <c r="D130" s="43" t="inlineStr">
         <is>
           <t>HR employee master used for approvals and assignments</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="D131" t="inlineStr">
+      <c r="B131" s="25" t="n"/>
+      <c r="C131" s="24" t="n"/>
+      <c r="D131" s="44" t="inlineStr">
         <is>
           <t>One row = one employee</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="D132" t="n">
-        <v>132</v>
+      <c r="B132" s="25" t="n"/>
+      <c r="C132" s="24" t="n"/>
+      <c r="D132" s="43" t="n">
+        <v>189</v>
       </c>
     </row>
     <row r="133">
-      <c r="D133" t="inlineStr">
+      <c r="B133" s="25" t="n"/>
+      <c r="C133" s="24" t="n"/>
+      <c r="D133" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="D134" t="inlineStr">
+      <c r="B134" s="25" t="n"/>
+      <c r="C134" s="24" t="n"/>
+      <c r="D134" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="D135" t="inlineStr">
+      <c r="B135" s="25" t="n"/>
+      <c r="C135" s="24" t="n"/>
+      <c r="D135" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="D136" t="inlineStr">
+      <c r="B136" s="25" t="n"/>
+      <c r="C136" s="24" t="n"/>
+      <c r="D136" s="43" t="inlineStr">
         <is>
           <t>D3 – Workforce</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="D137" t="inlineStr">
+      <c r="B137" s="25" t="n"/>
+      <c r="C137" s="24" t="n"/>
+      <c r="D137" s="44" t="inlineStr">
         <is>
           <t>EMPLOYEE</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="D138" t="inlineStr">
+      <c r="B138" s="25" t="n"/>
+      <c r="C138" s="24" t="n"/>
+      <c r="D138" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="B139" s="49" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="45" t="n"/>
+      <c r="C140" s="45" t="n"/>
+      <c r="D140" s="45" t="n"/>
+      <c r="E140" s="45" t="n"/>
+      <c r="F140" s="45" t="n"/>
+      <c r="G140" s="45" t="n"/>
+      <c r="H140" s="45" t="n"/>
+      <c r="I140" s="45" t="n"/>
+    </row>
     <row r="141">
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C141" s="16" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E141" t="n">
-        <v>132</v>
-      </c>
-      <c r="F141" t="n">
+      <c r="E141" s="16" t="n">
+        <v>189</v>
+      </c>
+      <c r="F141" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G141" t="n">
+      <c r="G141" s="16" t="n">
         <v>9999</v>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H141" s="16" t="inlineStr">
         <is>
           <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I141" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="15" t="inlineStr">
         <is>
           <t>entityid</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E142" t="n">
-        <v>132</v>
-      </c>
-      <c r="F142" t="inlineStr">
+      <c r="E142" s="15" t="n">
+        <v>189</v>
+      </c>
+      <c r="F142" s="15" t="inlineStr">
         <is>
           <t>EMP-001</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G142" s="15" t="inlineStr">
         <is>
           <t>EMP-150</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H142" s="15" t="inlineStr">
         <is>
           <t>Unique employee code</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I142" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="16" t="inlineStr">
         <is>
           <t>firstname</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="16" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E143" t="n">
-        <v>131</v>
-      </c>
-      <c r="F143" t="inlineStr">
+      <c r="E143" s="16" t="n">
+        <v>187</v>
+      </c>
+      <c r="F143" s="16" t="inlineStr">
         <is>
           <t>Aaron</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G143" s="16" t="inlineStr">
         <is>
           <t>Zoe</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr">
+      <c r="H143" s="16" t="inlineStr"/>
+      <c r="I143" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="15" t="inlineStr">
         <is>
           <t>lastname</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C144" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E144" t="n">
-        <v>131</v>
-      </c>
-      <c r="F144" t="inlineStr">
+      <c r="E144" s="15" t="n">
+        <v>187</v>
+      </c>
+      <c r="F144" s="15" t="inlineStr">
         <is>
           <t>Adams</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G144" s="15" t="inlineStr">
         <is>
           <t>Young</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr">
+      <c r="H144" s="15" t="inlineStr"/>
+      <c r="I144" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="16" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C145" s="16" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" s="16" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="E145" t="n">
-        <v>125</v>
-      </c>
-      <c r="H145" t="inlineStr">
+      <c r="E145" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="F145" s="16" t="n"/>
+      <c r="G145" s="16" t="n"/>
+      <c r="H145" s="16" t="inlineStr">
         <is>
           <t>5% null</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I145" s="16" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="15" t="inlineStr">
         <is>
           <t>hiredate</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C146" s="15" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E146" t="n">
-        <v>128</v>
-      </c>
-      <c r="F146" t="inlineStr">
+      <c r="E146" s="15" t="n">
+        <v>183</v>
+      </c>
+      <c r="F146" s="15" t="inlineStr">
         <is>
           <t>2015-01-15</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G146" s="15" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr">
+      <c r="H146" s="15" t="inlineStr"/>
+      <c r="I146" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="49" t="inlineStr">
         <is>
           <t>subsidiary_id</t>
         </is>
@@ -6471,1627 +6499,2024 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="B148" s="45" t="n"/>
+      <c r="C148" s="45" t="n"/>
+      <c r="D148" s="45" t="n"/>
+      <c r="E148" s="45" t="n"/>
+      <c r="F148" s="45" t="n"/>
+      <c r="G148" s="45" t="n"/>
+      <c r="H148" s="45" t="n"/>
+    </row>
     <row r="149">
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="16" t="inlineStr">
         <is>
           <t>subsidiary_id</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C149" s="16" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F149" s="16" t="inlineStr">
         <is>
           <t>1.3%</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G149" s="16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="H149" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="15" t="inlineStr">
         <is>
           <t>department_id</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C150" s="15" t="inlineStr">
         <is>
           <t>DEPARTMENT</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G150" s="15" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="H150" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="B151" s="16" t="n"/>
+      <c r="C151" s="16" t="n"/>
+      <c r="D151" s="16" t="n"/>
+      <c r="E151" s="16" t="n"/>
+      <c r="F151" s="16" t="n"/>
+      <c r="G151" s="16" t="n"/>
+      <c r="H151" s="16" t="n"/>
+    </row>
+    <row r="152"/>
     <row r="153">
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="47" t="inlineStr">
         <is>
           <t>Table 6: ACCOUNT</t>
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="B154" s="48" t="n"/>
+      <c r="C154" s="48" t="n"/>
+      <c r="D154" s="48" t="n"/>
+    </row>
     <row r="155">
-      <c r="D155" t="inlineStr">
+      <c r="B155" s="25" t="n"/>
+      <c r="C155" s="24" t="n"/>
+      <c r="D155" s="44" t="inlineStr">
         <is>
           <t>ACCOUNT</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="D156" t="inlineStr">
+      <c r="B156" s="25" t="n"/>
+      <c r="C156" s="24" t="n"/>
+      <c r="D156" s="43" t="inlineStr">
         <is>
           <t>Chart of accounts for GL posting</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="D157" t="inlineStr">
+      <c r="B157" s="25" t="n"/>
+      <c r="C157" s="24" t="n"/>
+      <c r="D157" s="44" t="inlineStr">
         <is>
           <t>One row = one GL account</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="D158" t="n">
-        <v>256</v>
+      <c r="B158" s="25" t="n"/>
+      <c r="C158" s="24" t="n"/>
+      <c r="D158" s="43" t="n">
+        <v>307</v>
       </c>
     </row>
     <row r="159">
-      <c r="D159" t="inlineStr">
+      <c r="B159" s="25" t="n"/>
+      <c r="C159" s="24" t="n"/>
+      <c r="D159" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="D160" t="inlineStr">
+      <c r="B160" s="25" t="n"/>
+      <c r="C160" s="24" t="n"/>
+      <c r="D160" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="D161" t="inlineStr">
+      <c r="B161" s="25" t="n"/>
+      <c r="C161" s="24" t="n"/>
+      <c r="D161" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="D162" t="inlineStr">
+      <c r="B162" s="25" t="n"/>
+      <c r="C162" s="24" t="n"/>
+      <c r="D162" s="43" t="inlineStr">
         <is>
           <t>D5 – Financials</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="D163" t="inlineStr">
+      <c r="B163" s="25" t="n"/>
+      <c r="C163" s="24" t="n"/>
+      <c r="D163" s="44" t="inlineStr">
         <is>
           <t>GL_ACCOUNT</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="D164" t="inlineStr">
+      <c r="B164" s="25" t="n"/>
+      <c r="C164" s="24" t="n"/>
+      <c r="D164" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="B165" s="49" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="45" t="n"/>
+      <c r="C166" s="45" t="n"/>
+      <c r="D166" s="45" t="n"/>
+      <c r="E166" s="45" t="n"/>
+      <c r="F166" s="45" t="n"/>
+      <c r="G166" s="45" t="n"/>
+      <c r="H166" s="45" t="n"/>
+      <c r="I166" s="45" t="n"/>
+    </row>
     <row r="167">
-      <c r="B167" t="inlineStr">
+      <c r="B167" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C167" s="16" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D167" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E167" t="n">
-        <v>256</v>
-      </c>
-      <c r="F167" t="n">
+      <c r="E167" s="16" t="n">
+        <v>307</v>
+      </c>
+      <c r="F167" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G167" t="n">
+      <c r="G167" s="16" t="n">
         <v>9999</v>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="H167" s="16" t="inlineStr">
         <is>
           <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I167" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="B168" t="inlineStr">
+      <c r="B168" s="15" t="inlineStr">
         <is>
           <t>acctnumber</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C168" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D168" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E168" t="n">
-        <v>256</v>
-      </c>
-      <c r="F168" t="inlineStr">
+      <c r="E168" s="15" t="n">
+        <v>307</v>
+      </c>
+      <c r="F168" s="15" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="G168" s="15" t="inlineStr">
         <is>
           <t>9999</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="H168" s="15" t="inlineStr">
         <is>
           <t>Unique account number</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I168" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="B169" t="inlineStr">
+      <c r="B169" s="16" t="inlineStr">
         <is>
           <t>acctname</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C169" s="16" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D169" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E169" t="n">
-        <v>253</v>
-      </c>
-      <c r="F169" t="inlineStr">
+      <c r="E169" s="16" t="n">
+        <v>304</v>
+      </c>
+      <c r="F169" s="16" t="inlineStr">
         <is>
           <t>Accounts Pay</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="G169" s="16" t="inlineStr">
         <is>
           <t>Wages Exp</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr">
+      <c r="H169" s="16" t="inlineStr"/>
+      <c r="I169" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="15" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C170" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D170" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E170" t="n">
+      <c r="E170" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F170" s="15" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G170" s="15" t="inlineStr">
         <is>
           <t>OtherExpense</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="H170" s="15" t="inlineStr">
         <is>
           <t>12 account types</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I170" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="16" t="inlineStr">
         <is>
           <t>lastmodifieddate</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C171" s="16" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D171" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E171" t="n">
-        <v>238</v>
-      </c>
-      <c r="F171" t="inlineStr">
+      <c r="E171" s="16" t="n">
+        <v>286</v>
+      </c>
+      <c r="F171" s="16" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G171" s="16" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr">
+      <c r="H171" s="16" t="inlineStr"/>
+      <c r="I171" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="B172" s="15" t="n"/>
+      <c r="C172" s="15" t="n"/>
+      <c r="D172" s="15" t="n"/>
+      <c r="E172" s="15" t="n"/>
+      <c r="F172" s="15" t="n"/>
+      <c r="G172" s="15" t="n"/>
+      <c r="H172" s="15" t="n"/>
+      <c r="I172" s="15" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="49" t="n"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="45" t="n"/>
+      <c r="C174" s="45" t="n"/>
+      <c r="D174" s="45" t="n"/>
+      <c r="E174" s="45" t="n"/>
+      <c r="F174" s="45" t="n"/>
+      <c r="G174" s="45" t="n"/>
+      <c r="H174" s="45" t="n"/>
+    </row>
     <row r="175">
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="16" t="inlineStr">
         <is>
           <t>subsidiary_id</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C175" s="16" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D175" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E175" t="n">
+      <c r="E175" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F175" s="16" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G175" s="16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="H175" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="B176" s="15" t="n"/>
+      <c r="C176" s="15" t="n"/>
+      <c r="D176" s="15" t="n"/>
+      <c r="E176" s="15" t="n"/>
+      <c r="F176" s="15" t="n"/>
+      <c r="G176" s="15" t="n"/>
+      <c r="H176" s="15" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="16" t="n"/>
+      <c r="C177" s="16" t="n"/>
+      <c r="D177" s="16" t="n"/>
+      <c r="E177" s="16" t="n"/>
+      <c r="F177" s="16" t="n"/>
+      <c r="G177" s="16" t="n"/>
+      <c r="H177" s="16" t="n"/>
+    </row>
+    <row r="178"/>
     <row r="179">
-      <c r="B179" t="inlineStr">
+      <c r="B179" s="47" t="inlineStr">
         <is>
           <t>Table 7: SUBSIDIARY</t>
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="B180" s="48" t="n"/>
+      <c r="C180" s="48" t="n"/>
+      <c r="D180" s="48" t="n"/>
+    </row>
     <row r="181">
-      <c r="D181" t="inlineStr">
+      <c r="B181" s="25" t="n"/>
+      <c r="C181" s="24" t="n"/>
+      <c r="D181" s="44" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="D182" t="inlineStr">
+      <c r="B182" s="25" t="n"/>
+      <c r="C182" s="24" t="n"/>
+      <c r="D182" s="43" t="inlineStr">
         <is>
           <t>Legal entities / subsidiaries within NetSuite OneWorld</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="D183" t="inlineStr">
+      <c r="B183" s="25" t="n"/>
+      <c r="C183" s="24" t="n"/>
+      <c r="D183" s="44" t="inlineStr">
         <is>
           <t>One row = one subsidiary</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="D184" t="n">
-        <v>-19</v>
+      <c r="B184" s="25" t="n"/>
+      <c r="C184" s="24" t="n"/>
+      <c r="D184" s="43" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="185">
-      <c r="D185" t="inlineStr">
+      <c r="B185" s="25" t="n"/>
+      <c r="C185" s="24" t="n"/>
+      <c r="D185" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="D186" t="inlineStr">
+      <c r="B186" s="25" t="n"/>
+      <c r="C186" s="24" t="n"/>
+      <c r="D186" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="B187" s="25" t="n"/>
+      <c r="C187" s="24" t="n"/>
+      <c r="D187" s="44" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="D188" t="inlineStr">
+      <c r="B188" s="25" t="n"/>
+      <c r="C188" s="24" t="n"/>
+      <c r="D188" s="43" t="inlineStr">
         <is>
           <t>D5 – Financials</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="D189" t="inlineStr">
+      <c r="B189" s="25" t="n"/>
+      <c r="C189" s="24" t="n"/>
+      <c r="D189" s="44" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="D190" t="inlineStr">
+      <c r="B190" s="25" t="n"/>
+      <c r="C190" s="24" t="n"/>
+      <c r="D190" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="B191" s="49" t="n"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="45" t="n"/>
+      <c r="C192" s="45" t="n"/>
+      <c r="D192" s="45" t="n"/>
+      <c r="E192" s="45" t="n"/>
+      <c r="F192" s="45" t="n"/>
+      <c r="G192" s="45" t="n"/>
+      <c r="H192" s="45" t="n"/>
+      <c r="I192" s="45" t="n"/>
+    </row>
     <row r="193">
-      <c r="B193" t="inlineStr">
+      <c r="B193" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C193" s="16" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D193" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E193" t="n">
-        <v>-19</v>
-      </c>
-      <c r="F193" t="n">
+      <c r="E193" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="F193" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G193" t="n">
+      <c r="G193" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="H193" s="16" t="inlineStr">
         <is>
           <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
+      <c r="I193" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="B194" t="inlineStr">
+      <c r="B194" s="15" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C194" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D194" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E194" t="n">
-        <v>-19</v>
-      </c>
-      <c r="F194" t="inlineStr">
+      <c r="E194" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="F194" s="15" t="inlineStr">
         <is>
           <t>Acme AU</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="G194" s="15" t="inlineStr">
         <is>
           <t>Zurich SA</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr">
+      <c r="H194" s="15" t="inlineStr"/>
+      <c r="I194" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="B195" t="inlineStr">
+      <c r="B195" s="16" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C195" s="16" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D195" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E195" t="n">
+      <c r="E195" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F195" s="16" t="inlineStr">
         <is>
           <t>AUD</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="G195" s="16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="H195" s="16" t="inlineStr">
         <is>
           <t>6 currencies</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="I195" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="B196" t="inlineStr">
+      <c r="B196" s="15" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C196" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D196" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="E196" t="n">
-        <v>-18</v>
-      </c>
-      <c r="H196" t="inlineStr">
+      <c r="E196" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="F196" s="15" t="n"/>
+      <c r="G196" s="15" t="n"/>
+      <c r="H196" s="15" t="inlineStr">
         <is>
           <t>5% null country</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
+      <c r="I196" s="15" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="B197" t="inlineStr">
+      <c r="B197" s="16" t="inlineStr">
         <is>
           <t>lastmodifieddate</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C197" s="16" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D197" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E197" t="n">
-        <v>-17</v>
-      </c>
-      <c r="F197" t="inlineStr">
+      <c r="E197" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="F197" s="16" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G197" s="16" t="inlineStr">
         <is>
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
+      <c r="H197" s="16" t="inlineStr"/>
+      <c r="I197" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="B198" s="15" t="n"/>
+      <c r="C198" s="15" t="n"/>
+      <c r="D198" s="15" t="n"/>
+      <c r="E198" s="15" t="n"/>
+      <c r="F198" s="15" t="n"/>
+      <c r="G198" s="15" t="n"/>
+      <c r="H198" s="15" t="n"/>
+      <c r="I198" s="15" t="n"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="49" t="n"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="45" t="n"/>
+      <c r="C200" s="45" t="n"/>
+      <c r="D200" s="45" t="n"/>
+      <c r="E200" s="45" t="n"/>
+      <c r="F200" s="45" t="n"/>
+      <c r="G200" s="45" t="n"/>
+      <c r="H200" s="45" t="n"/>
+    </row>
+    <row r="201">
+      <c r="B201" s="16" t="n"/>
+      <c r="C201" s="16" t="n"/>
+      <c r="D201" s="16" t="n"/>
+      <c r="E201" s="16" t="n"/>
+      <c r="F201" s="16" t="n"/>
+      <c r="G201" s="16" t="n"/>
+      <c r="H201" s="16" t="n"/>
+    </row>
+    <row r="202">
+      <c r="B202" s="15" t="n"/>
+      <c r="C202" s="15" t="n"/>
+      <c r="D202" s="15" t="n"/>
+      <c r="E202" s="15" t="n"/>
+      <c r="F202" s="15" t="n"/>
+      <c r="G202" s="15" t="n"/>
+      <c r="H202" s="15" t="n"/>
+    </row>
+    <row r="203">
+      <c r="B203" s="16" t="n"/>
+      <c r="C203" s="16" t="n"/>
+      <c r="D203" s="16" t="n"/>
+      <c r="E203" s="16" t="n"/>
+      <c r="F203" s="16" t="n"/>
+      <c r="G203" s="16" t="n"/>
+      <c r="H203" s="16" t="n"/>
+    </row>
+    <row r="204"/>
     <row r="205">
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="47" t="inlineStr">
         <is>
           <t>Table 8: DEPARTMENT</t>
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="B206" s="48" t="n"/>
+      <c r="C206" s="48" t="n"/>
+      <c r="D206" s="48" t="n"/>
+    </row>
     <row r="207">
-      <c r="D207" t="inlineStr">
+      <c r="B207" s="25" t="n"/>
+      <c r="C207" s="24" t="n"/>
+      <c r="D207" s="44" t="inlineStr">
         <is>
           <t>DEPARTMENT</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="D208" t="inlineStr">
+      <c r="B208" s="25" t="n"/>
+      <c r="C208" s="24" t="n"/>
+      <c r="D208" s="43" t="inlineStr">
         <is>
           <t>Cost centre / department classification</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="D209" t="inlineStr">
+      <c r="B209" s="25" t="n"/>
+      <c r="C209" s="24" t="n"/>
+      <c r="D209" s="44" t="inlineStr">
         <is>
           <t>One row = one department</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="D210" t="n">
-        <v>65</v>
+      <c r="B210" s="25" t="n"/>
+      <c r="C210" s="24" t="n"/>
+      <c r="D210" s="43" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="211">
-      <c r="D211" t="inlineStr">
+      <c r="B211" s="25" t="n"/>
+      <c r="C211" s="24" t="n"/>
+      <c r="D211" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="D212" t="inlineStr">
+      <c r="B212" s="25" t="n"/>
+      <c r="C212" s="24" t="n"/>
+      <c r="D212" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="D213" t="inlineStr">
+      <c r="B213" s="25" t="n"/>
+      <c r="C213" s="24" t="n"/>
+      <c r="D213" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="D214" t="inlineStr">
+      <c r="B214" s="25" t="n"/>
+      <c r="C214" s="24" t="n"/>
+      <c r="D214" s="43" t="inlineStr">
         <is>
           <t>D5 – Financials</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="D215" t="inlineStr">
+      <c r="B215" s="25" t="n"/>
+      <c r="C215" s="24" t="n"/>
+      <c r="D215" s="44" t="inlineStr">
         <is>
           <t>DEPARTMENT</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="D216" t="inlineStr">
+      <c r="B216" s="25" t="n"/>
+      <c r="C216" s="24" t="n"/>
+      <c r="D216" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="B217" s="49" t="n"/>
+    </row>
+    <row r="218">
+      <c r="B218" s="45" t="n"/>
+      <c r="C218" s="45" t="n"/>
+      <c r="D218" s="45" t="n"/>
+      <c r="E218" s="45" t="n"/>
+      <c r="F218" s="45" t="n"/>
+      <c r="G218" s="45" t="n"/>
+      <c r="H218" s="45" t="n"/>
+      <c r="I218" s="45" t="n"/>
+    </row>
     <row r="219">
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C219" s="16" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D219" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E219" t="n">
-        <v>65</v>
-      </c>
-      <c r="F219" t="n">
+      <c r="E219" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="F219" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G219" t="n">
+      <c r="G219" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H219" s="16" t="inlineStr">
         <is>
           <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I219" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="B220" t="inlineStr">
+      <c r="B220" s="15" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C220" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D220" s="15" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="E220" t="n">
-        <v>64</v>
-      </c>
-      <c r="F220" t="inlineStr">
+      <c r="E220" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="F220" s="15" t="inlineStr">
         <is>
           <t>Accounts</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G220" s="15" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="H220" s="15" t="inlineStr">
         <is>
           <t>2% null names</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
+      <c r="I220" s="15" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="B221" t="inlineStr">
+      <c r="B221" s="16" t="inlineStr">
         <is>
           <t>subsidiary_id</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C221" s="16" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D221" s="16" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="E221" t="n">
+      <c r="E221" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="F221" t="n">
+      <c r="F221" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G221" t="n">
+      <c r="G221" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="H221" s="16" t="inlineStr">
         <is>
           <t>4% null – orphan risk</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="I221" s="16" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="B222" t="inlineStr">
+      <c r="B222" s="15" t="inlineStr">
         <is>
           <t>lastmodifieddate</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C222" s="15" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D222" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E222" t="n">
-        <v>62</v>
-      </c>
-      <c r="F222" t="inlineStr">
+      <c r="E222" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="F222" s="15" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G222" s="15" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr">
+      <c r="H222" s="15" t="inlineStr"/>
+      <c r="I222" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="B223" s="16" t="n"/>
+      <c r="C223" s="16" t="n"/>
+      <c r="D223" s="16" t="n"/>
+      <c r="E223" s="16" t="n"/>
+      <c r="F223" s="16" t="n"/>
+      <c r="G223" s="16" t="n"/>
+      <c r="H223" s="16" t="n"/>
+      <c r="I223" s="16" t="n"/>
+    </row>
+    <row r="224">
+      <c r="B224" s="15" t="n"/>
+      <c r="C224" s="15" t="n"/>
+      <c r="D224" s="15" t="n"/>
+      <c r="E224" s="15" t="n"/>
+      <c r="F224" s="15" t="n"/>
+      <c r="G224" s="15" t="n"/>
+      <c r="H224" s="15" t="n"/>
+      <c r="I224" s="15" t="n"/>
+    </row>
+    <row r="225">
+      <c r="B225" s="49" t="n"/>
+    </row>
+    <row r="226">
+      <c r="B226" s="45" t="n"/>
+      <c r="C226" s="45" t="n"/>
+      <c r="D226" s="45" t="n"/>
+      <c r="E226" s="45" t="n"/>
+      <c r="F226" s="45" t="n"/>
+      <c r="G226" s="45" t="n"/>
+      <c r="H226" s="45" t="n"/>
+    </row>
     <row r="227">
-      <c r="B227" t="inlineStr">
+      <c r="B227" s="16" t="inlineStr">
         <is>
           <t>subsidiary_id</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C227" s="16" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D227" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E227" t="n">
+      <c r="E227" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F227" s="16" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G227" s="16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
+      <c r="H227" s="16" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="B228" s="15" t="n"/>
+      <c r="C228" s="15" t="n"/>
+      <c r="D228" s="15" t="n"/>
+      <c r="E228" s="15" t="n"/>
+      <c r="F228" s="15" t="n"/>
+      <c r="G228" s="15" t="n"/>
+      <c r="H228" s="15" t="n"/>
+    </row>
+    <row r="229">
+      <c r="B229" s="16" t="n"/>
+      <c r="C229" s="16" t="n"/>
+      <c r="D229" s="16" t="n"/>
+      <c r="E229" s="16" t="n"/>
+      <c r="F229" s="16" t="n"/>
+      <c r="G229" s="16" t="n"/>
+      <c r="H229" s="16" t="n"/>
+    </row>
+    <row r="230"/>
     <row r="231">
-      <c r="B231" t="inlineStr">
+      <c r="B231" s="47" t="inlineStr">
         <is>
           <t>Table 9: SALESORDER</t>
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="B232" s="48" t="n"/>
+      <c r="C232" s="48" t="n"/>
+      <c r="D232" s="48" t="n"/>
+    </row>
     <row r="233">
-      <c r="D233" t="inlineStr">
+      <c r="B233" s="25" t="n"/>
+      <c r="C233" s="24" t="n"/>
+      <c r="D233" s="44" t="inlineStr">
         <is>
           <t>SALESORDER</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="D234" t="inlineStr">
+      <c r="B234" s="25" t="n"/>
+      <c r="C234" s="24" t="n"/>
+      <c r="D234" s="43" t="inlineStr">
         <is>
           <t>Sales orders linked to customers and items</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="D235" t="inlineStr">
+      <c r="B235" s="25" t="n"/>
+      <c r="C235" s="24" t="n"/>
+      <c r="D235" s="44" t="inlineStr">
         <is>
           <t>One row = one sales order header</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="D236" t="n">
-        <v>2531</v>
+      <c r="B236" s="25" t="n"/>
+      <c r="C236" s="24" t="n"/>
+      <c r="D236" s="43" t="n">
+        <v>2488</v>
       </c>
     </row>
     <row r="237">
-      <c r="D237" t="inlineStr">
+      <c r="B237" s="25" t="n"/>
+      <c r="C237" s="24" t="n"/>
+      <c r="D237" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="D238" t="inlineStr">
+      <c r="B238" s="25" t="n"/>
+      <c r="C238" s="24" t="n"/>
+      <c r="D238" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="D239" t="inlineStr">
+      <c r="B239" s="25" t="n"/>
+      <c r="C239" s="24" t="n"/>
+      <c r="D239" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="D240" t="inlineStr">
+      <c r="B240" s="25" t="n"/>
+      <c r="C240" s="24" t="n"/>
+      <c r="D240" s="43" t="inlineStr">
         <is>
           <t>D2 – Contracts &amp; Revenue</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="D241" t="inlineStr">
+      <c r="B241" s="25" t="n"/>
+      <c r="C241" s="24" t="n"/>
+      <c r="D241" s="44" t="inlineStr">
         <is>
           <t>SALES_ORDER</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="D242" t="inlineStr">
+      <c r="B242" s="25" t="n"/>
+      <c r="C242" s="24" t="n"/>
+      <c r="D242" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="243">
+      <c r="B243" s="49" t="n"/>
+    </row>
+    <row r="244">
+      <c r="B244" s="45" t="n"/>
+      <c r="C244" s="45" t="n"/>
+      <c r="D244" s="45" t="n"/>
+      <c r="E244" s="45" t="n"/>
+      <c r="F244" s="45" t="n"/>
+      <c r="G244" s="45" t="n"/>
+      <c r="H244" s="45" t="n"/>
+      <c r="I244" s="45" t="n"/>
+    </row>
     <row r="245">
-      <c r="B245" t="inlineStr">
+      <c r="B245" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C245" s="16" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D245" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E245" t="n">
-        <v>2531</v>
-      </c>
-      <c r="F245" t="n">
+      <c r="E245" s="16" t="n">
+        <v>2488</v>
+      </c>
+      <c r="F245" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G245" t="n">
+      <c r="G245" s="16" t="n">
         <v>99999</v>
       </c>
-      <c r="H245" t="inlineStr">
+      <c r="H245" s="16" t="inlineStr">
         <is>
           <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
+      <c r="I245" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="B246" t="inlineStr">
+      <c r="B246" s="15" t="inlineStr">
         <is>
           <t>tranid</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C246" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D246" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E246" t="n">
-        <v>2531</v>
-      </c>
-      <c r="F246" t="inlineStr">
+      <c r="E246" s="15" t="n">
+        <v>2488</v>
+      </c>
+      <c r="F246" s="15" t="inlineStr">
         <is>
           <t>SO-00001</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G246" s="15" t="inlineStr">
         <is>
           <t>SO-09999</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
+      <c r="H246" s="15" t="inlineStr">
         <is>
           <t>Unique order reference</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
+      <c r="I246" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="B247" t="inlineStr">
+      <c r="B247" s="16" t="inlineStr">
         <is>
           <t>trandate</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C247" s="16" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D247" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E247" t="n">
-        <v>1620</v>
-      </c>
-      <c r="F247" t="inlineStr">
+      <c r="E247" s="16" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F247" s="16" t="inlineStr">
         <is>
           <t>2020-01-03</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G247" s="16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>1620 unique dates</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
+      <c r="H247" s="16" t="inlineStr">
+        <is>
+          <t>1592 unique dates</t>
+        </is>
+      </c>
+      <c r="I247" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="B248" t="inlineStr">
+      <c r="B248" s="15" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C248" s="15" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D248" s="15" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="E248" t="n">
-        <v>506</v>
-      </c>
-      <c r="F248" t="n">
+      <c r="E248" s="15" t="n">
+        <v>498</v>
+      </c>
+      <c r="F248" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G248" t="n">
+      <c r="G248" s="15" t="n">
         <v>9999</v>
       </c>
-      <c r="H248" t="inlineStr">
+      <c r="H248" s="15" t="inlineStr">
         <is>
           <t>1% null – FK to CUSTOMER</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
+      <c r="I248" s="15" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="B249" t="inlineStr">
+      <c r="B249" s="16" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C249" s="16" t="inlineStr">
         <is>
           <t>DECIMAL</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D249" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E249" t="n">
-        <v>2480</v>
-      </c>
-      <c r="F249" t="n">
+      <c r="E249" s="16" t="n">
+        <v>2438</v>
+      </c>
+      <c r="F249" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="G249" t="n">
+      <c r="G249" s="16" t="n">
         <v>99999.99000000001</v>
       </c>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr">
+      <c r="H249" s="16" t="inlineStr"/>
+      <c r="I249" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="B250" t="inlineStr">
+      <c r="B250" s="15" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C250" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D250" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E250" t="n">
+      <c r="E250" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="F250" t="inlineStr">
+      <c r="F250" s="15" t="inlineStr">
         <is>
           <t>Billed</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
+      <c r="G250" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
+      <c r="H250" s="15" t="inlineStr">
         <is>
           <t>6 order statuses</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
+      <c r="I250" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="B251" s="49" t="n"/>
+    </row>
+    <row r="252">
+      <c r="B252" s="45" t="n"/>
+      <c r="C252" s="45" t="n"/>
+      <c r="D252" s="45" t="n"/>
+      <c r="E252" s="45" t="n"/>
+      <c r="F252" s="45" t="n"/>
+      <c r="G252" s="45" t="n"/>
+      <c r="H252" s="45" t="n"/>
+    </row>
     <row r="253">
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="16" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C253" s="16" t="inlineStr">
         <is>
           <t>CUSTOMER</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D253" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E253" t="n">
+      <c r="E253" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="F253" t="inlineStr">
+      <c r="F253" s="16" t="inlineStr">
         <is>
           <t>0.9%</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
+      <c r="G253" s="16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
+      <c r="H253" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="15" t="inlineStr">
         <is>
           <t>subsidiary_id</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C254" s="15" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D254" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E254" t="n">
+      <c r="E254" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="F254" t="inlineStr">
+      <c r="F254" s="15" t="inlineStr">
         <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
+      <c r="G254" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
+      <c r="H254" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="B255" s="16" t="n"/>
+      <c r="C255" s="16" t="n"/>
+      <c r="D255" s="16" t="n"/>
+      <c r="E255" s="16" t="n"/>
+      <c r="F255" s="16" t="n"/>
+      <c r="G255" s="16" t="n"/>
+      <c r="H255" s="16" t="n"/>
+    </row>
+    <row r="256"/>
     <row r="257">
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="47" t="inlineStr">
         <is>
           <t>Table 10: PURCHASEORDER</t>
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="B258" s="48" t="n"/>
+      <c r="C258" s="48" t="n"/>
+      <c r="D258" s="48" t="n"/>
+    </row>
     <row r="259">
-      <c r="D259" t="inlineStr">
+      <c r="B259" s="25" t="n"/>
+      <c r="C259" s="24" t="n"/>
+      <c r="D259" s="44" t="inlineStr">
         <is>
           <t>PURCHASEORDER</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="D260" t="inlineStr">
+      <c r="B260" s="25" t="n"/>
+      <c r="C260" s="24" t="n"/>
+      <c r="D260" s="43" t="inlineStr">
         <is>
           <t>Purchase orders raised against vendors</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="D261" t="inlineStr">
+      <c r="B261" s="25" t="n"/>
+      <c r="C261" s="24" t="n"/>
+      <c r="D261" s="44" t="inlineStr">
         <is>
           <t>One row = one purchase order header</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="D262" t="n">
-        <v>766</v>
+      <c r="B262" s="25" t="n"/>
+      <c r="C262" s="24" t="n"/>
+      <c r="D262" s="43" t="n">
+        <v>805</v>
       </c>
     </row>
     <row r="263">
-      <c r="D263" t="inlineStr">
+      <c r="B263" s="25" t="n"/>
+      <c r="C263" s="24" t="n"/>
+      <c r="D263" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="D264" t="inlineStr">
+      <c r="B264" s="25" t="n"/>
+      <c r="C264" s="24" t="n"/>
+      <c r="D264" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="D265" t="inlineStr">
+      <c r="B265" s="25" t="n"/>
+      <c r="C265" s="24" t="n"/>
+      <c r="D265" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="D266" t="inlineStr">
+      <c r="B266" s="25" t="n"/>
+      <c r="C266" s="24" t="n"/>
+      <c r="D266" s="43" t="inlineStr">
         <is>
           <t>D5 – Financials</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="D267" t="inlineStr">
+      <c r="B267" s="25" t="n"/>
+      <c r="C267" s="24" t="n"/>
+      <c r="D267" s="44" t="inlineStr">
         <is>
           <t>PURCHASE_ORDER</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="D268" t="inlineStr">
+      <c r="B268" s="25" t="n"/>
+      <c r="C268" s="24" t="n"/>
+      <c r="D268" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="269">
+      <c r="B269" s="49" t="n"/>
+    </row>
+    <row r="270">
+      <c r="B270" s="45" t="n"/>
+      <c r="C270" s="45" t="n"/>
+      <c r="D270" s="45" t="n"/>
+      <c r="E270" s="45" t="n"/>
+      <c r="F270" s="45" t="n"/>
+      <c r="G270" s="45" t="n"/>
+      <c r="H270" s="45" t="n"/>
+      <c r="I270" s="45" t="n"/>
+    </row>
     <row r="271">
-      <c r="B271" t="inlineStr">
+      <c r="B271" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C271" s="16" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D271" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E271" t="n">
-        <v>766</v>
-      </c>
-      <c r="F271" t="n">
+      <c r="E271" s="16" t="n">
+        <v>805</v>
+      </c>
+      <c r="F271" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G271" t="n">
+      <c r="G271" s="16" t="n">
         <v>9999</v>
       </c>
-      <c r="H271" t="inlineStr">
+      <c r="H271" s="16" t="inlineStr">
         <is>
           <t>PK – no nulls, no duplicates</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr">
+      <c r="I271" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="B272" t="inlineStr">
+      <c r="B272" s="15" t="inlineStr">
         <is>
           <t>tranid</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C272" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D272" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E272" t="n">
-        <v>766</v>
-      </c>
-      <c r="F272" t="inlineStr">
+      <c r="E272" s="15" t="n">
+        <v>805</v>
+      </c>
+      <c r="F272" s="15" t="inlineStr">
         <is>
           <t>PO-00001</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="G272" s="15" t="inlineStr">
         <is>
           <t>PO-03999</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
+      <c r="H272" s="15" t="inlineStr">
         <is>
           <t>Unique PO reference</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr">
+      <c r="I272" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="B273" t="inlineStr">
+      <c r="B273" s="16" t="inlineStr">
         <is>
           <t>trandate</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C273" s="16" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D273" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E273" t="n">
-        <v>720</v>
-      </c>
-      <c r="F273" t="inlineStr">
+      <c r="E273" s="16" t="n">
+        <v>757</v>
+      </c>
+      <c r="F273" s="16" t="inlineStr">
         <is>
           <t>2020-01-05</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
+      <c r="G273" s="16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>720 unique dates</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
+      <c r="H273" s="16" t="inlineStr">
+        <is>
+          <t>757 unique dates</t>
+        </is>
+      </c>
+      <c r="I273" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="B274" t="inlineStr">
+      <c r="B274" s="15" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
+      <c r="C274" s="15" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D274" s="15" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="E274" t="n">
-        <v>184</v>
-      </c>
-      <c r="F274" t="n">
+      <c r="E274" s="15" t="n">
+        <v>193</v>
+      </c>
+      <c r="F274" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G274" t="n">
+      <c r="G274" s="15" t="n">
         <v>9999</v>
       </c>
-      <c r="H274" t="inlineStr">
+      <c r="H274" s="15" t="inlineStr">
         <is>
           <t>2% null – FK to VENDOR</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr">
+      <c r="I274" s="15" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="B275" t="inlineStr">
+      <c r="B275" s="16" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
+      <c r="C275" s="16" t="inlineStr">
         <is>
           <t>DECIMAL</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D275" s="16" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="E275" t="n">
-        <v>743</v>
-      </c>
-      <c r="F275" t="n">
+      <c r="E275" s="16" t="n">
+        <v>781</v>
+      </c>
+      <c r="F275" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="G275" t="n">
+      <c r="G275" s="16" t="n">
         <v>49999.99</v>
       </c>
-      <c r="H275" t="inlineStr">
+      <c r="H275" s="16" t="inlineStr">
         <is>
           <t>1% null amounts</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr">
+      <c r="I275" s="16" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="B276" t="inlineStr">
+      <c r="B276" s="15" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C276" s="15" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D276" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E276" t="n">
+      <c r="E276" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F276" t="inlineStr">
+      <c r="F276" s="15" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
+      <c r="G276" s="15" t="inlineStr">
         <is>
           <t>PendingReceipt</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
+      <c r="H276" s="15" t="inlineStr">
         <is>
           <t>5 statuses</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr">
+      <c r="I276" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="B277" s="49" t="n"/>
+    </row>
+    <row r="278">
+      <c r="B278" s="45" t="n"/>
+      <c r="C278" s="45" t="n"/>
+      <c r="D278" s="45" t="n"/>
+      <c r="E278" s="45" t="n"/>
+      <c r="F278" s="45" t="n"/>
+      <c r="G278" s="45" t="n"/>
+      <c r="H278" s="45" t="n"/>
+    </row>
     <row r="279">
-      <c r="B279" t="inlineStr">
+      <c r="B279" s="16" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
+      <c r="C279" s="16" t="inlineStr">
         <is>
           <t>VENDOR</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D279" s="16" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E279" t="n">
+      <c r="E279" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="F279" t="inlineStr">
+      <c r="F279" s="16" t="inlineStr">
         <is>
           <t>2.0%</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
+      <c r="G279" s="16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
+      <c r="H279" s="16" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="B280" t="inlineStr">
+      <c r="B280" s="15" t="inlineStr">
         <is>
           <t>subsidiary_id</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
+      <c r="C280" s="15" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D280" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E280" t="n">
+      <c r="E280" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F280" t="inlineStr">
+      <c r="F280" s="15" t="inlineStr">
         <is>
           <t>0.6%</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
+      <c r="G280" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
+      <c r="H280" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="B281" s="16" t="n"/>
+      <c r="C281" s="16" t="n"/>
+      <c r="D281" s="16" t="n"/>
+      <c r="E281" s="16" t="n"/>
+      <c r="F281" s="16" t="n"/>
+      <c r="G281" s="16" t="n"/>
+      <c r="H281" s="16" t="n"/>
+    </row>
+    <row r="282"/>
     <row r="284">
       <c r="B284" t="inlineStr">
         <is>
@@ -8112,7 +8537,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8121,16 +8546,16 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>Investigate load delay</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8572,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -8156,7 +8581,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -8182,7 +8607,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -8191,16 +8616,16 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8642,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -8226,7 +8651,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -8252,7 +8677,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -8261,7 +8686,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -8287,7 +8712,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -8296,16 +8721,16 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>Investigate load delay</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8747,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8331,16 +8756,16 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8782,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8366,7 +8791,7 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -8392,7 +8817,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -8401,16 +8826,16 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>Investigate load delay</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8852,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -8436,16 +8861,16 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>Investigate load delay</t>
         </is>
       </c>
     </row>
@@ -8466,11 +8891,11 @@
     <row r="298">
       <c r="D298" t="inlineStr">
         <is>
-          <t>1. Null subsidiary_id on 100 TRANSACTION rows (2.0%)
-2. DEPARTMENT: 3 rows with null subsidiary_id (4.6%) – orphan risk
+          <t>1. Null subsidiary_id on 101 TRANSACTION rows (2.0%)
+2. DEPARTMENT: 2 rows with null subsidiary_id (5.0%) – orphan risk
 3. No direct FK from SALESORDER to CONTRACT
-4. VENDOR: 45 rows with null email (20.2%) – enrich before CRM migration
-5. PURCHASEORDER: 15 rows with null entity_id (2.0%) – verify vendor onboarding</t>
+4. VENDOR: 39 rows with null email (19.9%) – enrich before CRM migration
+5. PURCHASEORDER: 16 rows with null entity_id (2.0%) – verify vendor onboarding</t>
         </is>
       </c>
     </row>

--- a/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
+++ b/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
@@ -3723,7 +3723,7 @@
       </c>
       <c r="D13" s="44" t="inlineStr">
         <is>
-          <t>10,636 rows across 10 key tables</t>
+          <t>10,548 rows across 10 key tables</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="D28" s="43" t="n">
-        <v>513</v>
+        <v>544</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="E37" s="16" t="n">
-        <v>513</v>
+        <v>544</v>
       </c>
       <c r="F37" s="16" t="n">
         <v>1</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="E38" s="15" t="n">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="E39" s="16" t="n">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="F39" s="16" t="n"/>
       <c r="G39" s="16" t="n"/>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="E40" s="15" t="n">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="D54" s="43" t="n">
-        <v>196</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="E63" s="16" t="n">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="F63" s="16" t="n">
         <v>1</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="E64" s="15" t="n">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="E65" s="16" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="F65" s="16" t="n"/>
       <c r="G65" s="16" t="n"/>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="E66" s="15" t="n">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="D80" s="43" t="n">
-        <v>1011</v>
+        <v>984</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="E89" s="16" t="n">
-        <v>1011</v>
+        <v>984</v>
       </c>
       <c r="F89" s="16" t="n">
         <v>1</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="E90" s="15" t="n">
-        <v>1011</v>
+        <v>984</v>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="E91" s="16" t="n">
-        <v>930</v>
+        <v>905</v>
       </c>
       <c r="F91" s="16" t="n"/>
       <c r="G91" s="16" t="n"/>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="E92" s="15" t="n">
-        <v>809</v>
+        <v>787</v>
       </c>
       <c r="F92" s="15" t="n">
         <v>0.01</v>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="E93" s="16" t="n">
-        <v>960</v>
+        <v>935</v>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
@@ -5496,22 +5496,33 @@
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  C  |  COVERAGE CASCADE — Can you answer 'revenue by customer' from this system alone?</t>
-        </is>
-      </c>
-      <c r="B102" s="48" t="n"/>
-      <c r="C102" s="48" t="n"/>
-      <c r="D102" s="48" t="n"/>
+      <c r="B102" s="48" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C102" s="48" t="inlineStr">
+        <is>
+          <t>How to measure</t>
+        </is>
+      </c>
+      <c r="D102" s="48" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="31.5" customHeight="1">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>Trace the question: 'What is total revenue by customer this fiscal year?' through this source system. Document each step: what table you'd use, what's available, and where the chain breaks.</t>
-        </is>
-      </c>
-      <c r="C103" s="24" t="n"/>
+          <t>Table / view name</t>
+        </is>
+      </c>
+      <c r="C103" s="24" t="inlineStr">
+        <is>
+          <t>Exact name as it appears in source schema</t>
+        </is>
+      </c>
       <c r="D103" s="44" t="inlineStr">
         <is>
           <t>TRANSACTION</t>
@@ -5521,44 +5532,29 @@
     <row r="104" ht="18" customHeight="1">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>Step #</t>
+          <t>Business purpose</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
         <is>
-          <t>Question / Join Required</t>
+          <t>What business process does this table record?</t>
         </is>
       </c>
       <c r="D104" s="43" t="inlineStr">
         <is>
           <t>Records all financial transactions (invoices, payments, journals)</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Available in This System?</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Gap / Breakage Point</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>RAG</t>
         </is>
       </c>
     </row>
     <row r="105" ht="21.75" customHeight="1">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
         <is>
-          <t>Get all customers in this system</t>
+          <t>One row = one [what]? e.g. one invoice line, one work order</t>
         </is>
       </c>
       <c r="D105" s="44" t="inlineStr">
@@ -5570,27 +5566,27 @@
     <row r="106" ht="21.75" customHeight="1">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Total row count</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
         <is>
-          <t>Get all contracts linked to each customer</t>
+          <t>SELECT COUNT(*) FROM table</t>
         </is>
       </c>
       <c r="D106" s="43" t="n">
-        <v>5047</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="107" ht="21.75" customHeight="1">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Date range</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
         <is>
-          <t>Get invoices linked to each contract</t>
+          <t>MIN and MAX of primary date field</t>
         </is>
       </c>
       <c r="D107" s="44" t="inlineStr">
@@ -5602,12 +5598,12 @@
     <row r="108" ht="21.75" customHeight="1">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Primary key field(s)</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>Sum invoice amounts by customer, filter by fiscal year</t>
+          <t>Field name(s) — is it a surrogate or natural key?</t>
         </is>
       </c>
       <c r="D108" s="43" t="inlineStr">
@@ -5619,12 +5615,12 @@
     <row r="109" ht="21.75" customHeight="1">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>PK uniqueness check</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
         <is>
-          <t>Does this system cover ALL customers? (or only some divisions?)</t>
+          <t>SELECT COUNT(*) vs COUNT(DISTINCT pk) — match = PASS</t>
         </is>
       </c>
       <c r="D109" s="44" t="inlineStr">
@@ -5636,12 +5632,12 @@
     <row r="110" ht="21.75" customHeight="1">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Canonical domain</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
         <is>
-          <t>Any customers in other systems not in this one?</t>
+          <t>Which canonical domain does this table feed? (Domain 1–5)</t>
         </is>
       </c>
       <c r="D110" s="43" t="inlineStr">
@@ -5651,8 +5647,16 @@
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="25" t="n"/>
-      <c r="C111" s="24" t="n"/>
+      <c r="B111" s="25" t="inlineStr">
+        <is>
+          <t>Canonical entities</t>
+        </is>
+      </c>
+      <c r="C111" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical entities? e.g. WORK_ORDER, WORK_ORDER_LINE</t>
+        </is>
+      </c>
       <c r="D111" s="44" t="inlineStr">
         <is>
           <t>TRANSACTION, INVOICE, JOURNAL_ENTRY</t>
@@ -5660,8 +5664,16 @@
       </c>
     </row>
     <row r="112" ht="7.5" customHeight="1">
-      <c r="B112" s="25" t="n"/>
-      <c r="C112" s="24" t="n"/>
+      <c r="B112" s="25" t="inlineStr">
+        <is>
+          <t>Overall table RAG</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>GREEN / AMBER / RED — your assessment of table usability</t>
+        </is>
+      </c>
       <c r="D112" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -5669,50 +5681,53 @@
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  D  |  DATA FRESHNESS — Is the data current enough to be trusted?</t>
-        </is>
-      </c>
-      <c r="B113" s="49" t="n"/>
+      <c r="B113" s="49" t="inlineStr">
+        <is>
+          <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="B114" s="45" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Field Name</t>
         </is>
       </c>
       <c r="C114" s="45" t="inlineStr">
         <is>
-          <t>Date Field Used</t>
+          <t>Field Type</t>
         </is>
       </c>
       <c r="D114" s="45" t="inlineStr">
         <is>
-          <t>Most Recent Record</t>
+          <t>Null %</t>
         </is>
       </c>
       <c r="E114" s="45" t="inlineStr">
         <is>
-          <t>Load / Extract Date</t>
+          <t>Distinct Count</t>
         </is>
       </c>
       <c r="F114" s="45" t="inlineStr">
         <is>
-          <t>Lag (days)</t>
+          <t>Min Value</t>
         </is>
       </c>
       <c r="G114" s="45" t="inlineStr">
         <is>
-          <t>Acceptable?</t>
+          <t>Max Value</t>
         </is>
       </c>
       <c r="H114" s="45" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="I114" s="45" t="n"/>
+          <t>Notes / Issues</t>
+        </is>
+      </c>
+      <c r="I114" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="B115" s="16" t="inlineStr">
@@ -5731,7 +5746,7 @@
         </is>
       </c>
       <c r="E115" s="16" t="n">
-        <v>5047</v>
+        <v>5043</v>
       </c>
       <c r="F115" s="16" t="n">
         <v>1</v>
@@ -5767,7 +5782,7 @@
         </is>
       </c>
       <c r="E116" s="15" t="n">
-        <v>5047</v>
+        <v>5043</v>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
@@ -5847,7 +5862,7 @@
         </is>
       </c>
       <c r="E118" s="15" t="n">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -5861,7 +5876,7 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>1817 unique dates</t>
+          <t>1815 unique dates</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
@@ -5887,7 +5902,7 @@
         </is>
       </c>
       <c r="E119" s="16" t="n">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F119" s="16" t="n">
         <v>1</v>
@@ -5959,7 +5974,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4845</v>
+        <v>4841</v>
       </c>
       <c r="F121" t="n">
         <v>0.01</v>
@@ -5975,18 +5990,41 @@
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  E  |  ENGINEER SUMMARY — Your overall assessment and flags for the Discovery report</t>
-        </is>
-      </c>
-      <c r="B122" s="45" t="n"/>
-      <c r="C122" s="45" t="n"/>
-      <c r="D122" s="45" t="n"/>
-      <c r="E122" s="45" t="n"/>
-      <c r="F122" s="45" t="n"/>
-      <c r="G122" s="45" t="n"/>
-      <c r="H122" s="45" t="n"/>
+      <c r="B122" s="45" t="inlineStr">
+        <is>
+          <t>FK Field</t>
+        </is>
+      </c>
+      <c r="C122" s="45" t="inlineStr">
+        <is>
+          <t>References Table</t>
+        </is>
+      </c>
+      <c r="D122" s="45" t="inlineStr">
+        <is>
+          <t>References Field</t>
+        </is>
+      </c>
+      <c r="E122" s="45" t="inlineStr">
+        <is>
+          <t>Orphan Row Count</t>
+        </is>
+      </c>
+      <c r="F122" s="45" t="inlineStr">
+        <is>
+          <t>Orphan %</t>
+        </is>
+      </c>
+      <c r="G122" s="45" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H122" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="19.5" customHeight="1">
       <c r="B123" s="16" t="inlineStr">
@@ -6093,52 +6131,40 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="30" customHeight="1">
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Recommended ingestion path</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Which tables/API endpoints should be in scope for Phase 2 build?</t>
-        </is>
-      </c>
-    </row>
+    <row r="126" ht="30" customHeight="1"/>
     <row r="127" ht="30" customHeight="1">
       <c r="B127" s="47" t="inlineStr">
         <is>
           <t>Table 5: EMPLOYEE</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Which entity fields exist for cross-system matching? How clean are they?</t>
-        </is>
-      </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="B128" s="48" t="inlineStr">
         <is>
-          <t>Blockers for Discovery</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C128" s="48" t="inlineStr">
         <is>
-          <t>Anything that prevents completing this profile by Discovery deadline?</t>
-        </is>
-      </c>
-      <c r="D128" s="48" t="n"/>
+          <t>How to measure</t>
+        </is>
+      </c>
+      <c r="D128" s="48" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>Recommended next action</t>
+          <t>Table / view name</t>
         </is>
       </c>
       <c r="C129" s="24" t="inlineStr">
         <is>
-          <t>What should the team do based on this profile?</t>
+          <t>Exact name as it appears in source schema</t>
         </is>
       </c>
       <c r="D129" s="44" t="inlineStr">
@@ -6150,12 +6176,12 @@
     <row r="130" ht="30" customHeight="1">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>Open questions for TFG SME</t>
+          <t>Business purpose</t>
         </is>
       </c>
       <c r="C130" s="24" t="inlineStr">
         <is>
-          <t>Questions to raise in the SME interview for this system</t>
+          <t>What business process does this table record?</t>
         </is>
       </c>
       <c r="D130" s="43" t="inlineStr">
@@ -6165,8 +6191,16 @@
       </c>
     </row>
     <row r="131">
-      <c r="B131" s="25" t="n"/>
-      <c r="C131" s="24" t="n"/>
+      <c r="B131" s="25" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="C131" s="24" t="inlineStr">
+        <is>
+          <t>One row = one [what]? e.g. one invoice line, one work order</t>
+        </is>
+      </c>
       <c r="D131" s="44" t="inlineStr">
         <is>
           <t>One row = one employee</t>
@@ -6174,15 +6208,31 @@
       </c>
     </row>
     <row r="132">
-      <c r="B132" s="25" t="n"/>
-      <c r="C132" s="24" t="n"/>
+      <c r="B132" s="25" t="inlineStr">
+        <is>
+          <t>Total row count</t>
+        </is>
+      </c>
+      <c r="C132" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM table</t>
+        </is>
+      </c>
       <c r="D132" s="43" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="133">
-      <c r="B133" s="25" t="n"/>
-      <c r="C133" s="24" t="n"/>
+      <c r="B133" s="25" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="C133" s="24" t="inlineStr">
+        <is>
+          <t>MIN and MAX of primary date field</t>
+        </is>
+      </c>
       <c r="D133" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
@@ -6190,8 +6240,16 @@
       </c>
     </row>
     <row r="134">
-      <c r="B134" s="25" t="n"/>
-      <c r="C134" s="24" t="n"/>
+      <c r="B134" s="25" t="inlineStr">
+        <is>
+          <t>Primary key field(s)</t>
+        </is>
+      </c>
+      <c r="C134" s="24" t="inlineStr">
+        <is>
+          <t>Field name(s) — is it a surrogate or natural key?</t>
+        </is>
+      </c>
       <c r="D134" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
@@ -6199,8 +6257,16 @@
       </c>
     </row>
     <row r="135">
-      <c r="B135" s="25" t="n"/>
-      <c r="C135" s="24" t="n"/>
+      <c r="B135" s="25" t="inlineStr">
+        <is>
+          <t>PK uniqueness check</t>
+        </is>
+      </c>
+      <c r="C135" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) vs COUNT(DISTINCT pk) — match = PASS</t>
+        </is>
+      </c>
       <c r="D135" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6208,8 +6274,16 @@
       </c>
     </row>
     <row r="136">
-      <c r="B136" s="25" t="n"/>
-      <c r="C136" s="24" t="n"/>
+      <c r="B136" s="25" t="inlineStr">
+        <is>
+          <t>Canonical domain</t>
+        </is>
+      </c>
+      <c r="C136" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical domain does this table feed? (Domain 1–5)</t>
+        </is>
+      </c>
       <c r="D136" s="43" t="inlineStr">
         <is>
           <t>D3 – Workforce</t>
@@ -6217,8 +6291,16 @@
       </c>
     </row>
     <row r="137">
-      <c r="B137" s="25" t="n"/>
-      <c r="C137" s="24" t="n"/>
+      <c r="B137" s="25" t="inlineStr">
+        <is>
+          <t>Canonical entities</t>
+        </is>
+      </c>
+      <c r="C137" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical entities? e.g. WORK_ORDER, WORK_ORDER_LINE</t>
+        </is>
+      </c>
       <c r="D137" s="44" t="inlineStr">
         <is>
           <t>EMPLOYEE</t>
@@ -6226,8 +6308,16 @@
       </c>
     </row>
     <row r="138">
-      <c r="B138" s="25" t="n"/>
-      <c r="C138" s="24" t="n"/>
+      <c r="B138" s="25" t="inlineStr">
+        <is>
+          <t>Overall table RAG</t>
+        </is>
+      </c>
+      <c r="C138" s="24" t="inlineStr">
+        <is>
+          <t>GREEN / AMBER / RED — your assessment of table usability</t>
+        </is>
+      </c>
       <c r="D138" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -6235,17 +6325,53 @@
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="49" t="n"/>
+      <c r="B139" s="49" t="inlineStr">
+        <is>
+          <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="B140" s="45" t="n"/>
-      <c r="C140" s="45" t="n"/>
-      <c r="D140" s="45" t="n"/>
-      <c r="E140" s="45" t="n"/>
-      <c r="F140" s="45" t="n"/>
-      <c r="G140" s="45" t="n"/>
-      <c r="H140" s="45" t="n"/>
-      <c r="I140" s="45" t="n"/>
+      <c r="B140" s="45" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="C140" s="45" t="inlineStr">
+        <is>
+          <t>Field Type</t>
+        </is>
+      </c>
+      <c r="D140" s="45" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="E140" s="45" t="inlineStr">
+        <is>
+          <t>Distinct Count</t>
+        </is>
+      </c>
+      <c r="F140" s="45" t="inlineStr">
+        <is>
+          <t>Min Value</t>
+        </is>
+      </c>
+      <c r="G140" s="45" t="inlineStr">
+        <is>
+          <t>Max Value</t>
+        </is>
+      </c>
+      <c r="H140" s="45" t="inlineStr">
+        <is>
+          <t>Notes / Issues</t>
+        </is>
+      </c>
+      <c r="I140" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="B141" s="16" t="inlineStr">
@@ -6264,7 +6390,7 @@
         </is>
       </c>
       <c r="E141" s="16" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F141" s="16" t="n">
         <v>1</v>
@@ -6300,7 +6426,7 @@
         </is>
       </c>
       <c r="E142" s="15" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F142" s="15" t="inlineStr">
         <is>
@@ -6340,7 +6466,7 @@
         </is>
       </c>
       <c r="E143" s="16" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F143" s="16" t="inlineStr">
         <is>
@@ -6376,7 +6502,7 @@
         </is>
       </c>
       <c r="E144" s="15" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F144" s="15" t="inlineStr">
         <is>
@@ -6444,7 +6570,7 @@
         </is>
       </c>
       <c r="E146" s="15" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
@@ -6500,13 +6626,41 @@
       </c>
     </row>
     <row r="148">
-      <c r="B148" s="45" t="n"/>
-      <c r="C148" s="45" t="n"/>
-      <c r="D148" s="45" t="n"/>
-      <c r="E148" s="45" t="n"/>
-      <c r="F148" s="45" t="n"/>
-      <c r="G148" s="45" t="n"/>
-      <c r="H148" s="45" t="n"/>
+      <c r="B148" s="45" t="inlineStr">
+        <is>
+          <t>FK Field</t>
+        </is>
+      </c>
+      <c r="C148" s="45" t="inlineStr">
+        <is>
+          <t>References Table</t>
+        </is>
+      </c>
+      <c r="D148" s="45" t="inlineStr">
+        <is>
+          <t>References Field</t>
+        </is>
+      </c>
+      <c r="E148" s="45" t="inlineStr">
+        <is>
+          <t>Orphan Row Count</t>
+        </is>
+      </c>
+      <c r="F148" s="45" t="inlineStr">
+        <is>
+          <t>Orphan %</t>
+        </is>
+      </c>
+      <c r="G148" s="45" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H148" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="B149" s="16" t="inlineStr">
@@ -6596,13 +6750,33 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" s="48" t="n"/>
-      <c r="C154" s="48" t="n"/>
-      <c r="D154" s="48" t="n"/>
+      <c r="B154" s="48" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C154" s="48" t="inlineStr">
+        <is>
+          <t>How to measure</t>
+        </is>
+      </c>
+      <c r="D154" s="48" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="155">
-      <c r="B155" s="25" t="n"/>
-      <c r="C155" s="24" t="n"/>
+      <c r="B155" s="25" t="inlineStr">
+        <is>
+          <t>Table / view name</t>
+        </is>
+      </c>
+      <c r="C155" s="24" t="inlineStr">
+        <is>
+          <t>Exact name as it appears in source schema</t>
+        </is>
+      </c>
       <c r="D155" s="44" t="inlineStr">
         <is>
           <t>ACCOUNT</t>
@@ -6610,8 +6784,16 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" s="25" t="n"/>
-      <c r="C156" s="24" t="n"/>
+      <c r="B156" s="25" t="inlineStr">
+        <is>
+          <t>Business purpose</t>
+        </is>
+      </c>
+      <c r="C156" s="24" t="inlineStr">
+        <is>
+          <t>What business process does this table record?</t>
+        </is>
+      </c>
       <c r="D156" s="43" t="inlineStr">
         <is>
           <t>Chart of accounts for GL posting</t>
@@ -6619,8 +6801,16 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" s="25" t="n"/>
-      <c r="C157" s="24" t="n"/>
+      <c r="B157" s="25" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="C157" s="24" t="inlineStr">
+        <is>
+          <t>One row = one [what]? e.g. one invoice line, one work order</t>
+        </is>
+      </c>
       <c r="D157" s="44" t="inlineStr">
         <is>
           <t>One row = one GL account</t>
@@ -6628,15 +6818,31 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" s="25" t="n"/>
-      <c r="C158" s="24" t="n"/>
+      <c r="B158" s="25" t="inlineStr">
+        <is>
+          <t>Total row count</t>
+        </is>
+      </c>
+      <c r="C158" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM table</t>
+        </is>
+      </c>
       <c r="D158" s="43" t="n">
-        <v>307</v>
+        <v>326</v>
       </c>
     </row>
     <row r="159">
-      <c r="B159" s="25" t="n"/>
-      <c r="C159" s="24" t="n"/>
+      <c r="B159" s="25" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="C159" s="24" t="inlineStr">
+        <is>
+          <t>MIN and MAX of primary date field</t>
+        </is>
+      </c>
       <c r="D159" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
@@ -6644,8 +6850,16 @@
       </c>
     </row>
     <row r="160">
-      <c r="B160" s="25" t="n"/>
-      <c r="C160" s="24" t="n"/>
+      <c r="B160" s="25" t="inlineStr">
+        <is>
+          <t>Primary key field(s)</t>
+        </is>
+      </c>
+      <c r="C160" s="24" t="inlineStr">
+        <is>
+          <t>Field name(s) — is it a surrogate or natural key?</t>
+        </is>
+      </c>
       <c r="D160" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
@@ -6653,8 +6867,16 @@
       </c>
     </row>
     <row r="161">
-      <c r="B161" s="25" t="n"/>
-      <c r="C161" s="24" t="n"/>
+      <c r="B161" s="25" t="inlineStr">
+        <is>
+          <t>PK uniqueness check</t>
+        </is>
+      </c>
+      <c r="C161" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) vs COUNT(DISTINCT pk) — match = PASS</t>
+        </is>
+      </c>
       <c r="D161" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6662,8 +6884,16 @@
       </c>
     </row>
     <row r="162">
-      <c r="B162" s="25" t="n"/>
-      <c r="C162" s="24" t="n"/>
+      <c r="B162" s="25" t="inlineStr">
+        <is>
+          <t>Canonical domain</t>
+        </is>
+      </c>
+      <c r="C162" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical domain does this table feed? (Domain 1–5)</t>
+        </is>
+      </c>
       <c r="D162" s="43" t="inlineStr">
         <is>
           <t>D5 – Financials</t>
@@ -6671,8 +6901,16 @@
       </c>
     </row>
     <row r="163">
-      <c r="B163" s="25" t="n"/>
-      <c r="C163" s="24" t="n"/>
+      <c r="B163" s="25" t="inlineStr">
+        <is>
+          <t>Canonical entities</t>
+        </is>
+      </c>
+      <c r="C163" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical entities? e.g. WORK_ORDER, WORK_ORDER_LINE</t>
+        </is>
+      </c>
       <c r="D163" s="44" t="inlineStr">
         <is>
           <t>GL_ACCOUNT</t>
@@ -6680,8 +6918,16 @@
       </c>
     </row>
     <row r="164">
-      <c r="B164" s="25" t="n"/>
-      <c r="C164" s="24" t="n"/>
+      <c r="B164" s="25" t="inlineStr">
+        <is>
+          <t>Overall table RAG</t>
+        </is>
+      </c>
+      <c r="C164" s="24" t="inlineStr">
+        <is>
+          <t>GREEN / AMBER / RED — your assessment of table usability</t>
+        </is>
+      </c>
       <c r="D164" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -6689,17 +6935,53 @@
       </c>
     </row>
     <row r="165">
-      <c r="B165" s="49" t="n"/>
+      <c r="B165" s="49" t="inlineStr">
+        <is>
+          <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
-      <c r="B166" s="45" t="n"/>
-      <c r="C166" s="45" t="n"/>
-      <c r="D166" s="45" t="n"/>
-      <c r="E166" s="45" t="n"/>
-      <c r="F166" s="45" t="n"/>
-      <c r="G166" s="45" t="n"/>
-      <c r="H166" s="45" t="n"/>
-      <c r="I166" s="45" t="n"/>
+      <c r="B166" s="45" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="C166" s="45" t="inlineStr">
+        <is>
+          <t>Field Type</t>
+        </is>
+      </c>
+      <c r="D166" s="45" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="E166" s="45" t="inlineStr">
+        <is>
+          <t>Distinct Count</t>
+        </is>
+      </c>
+      <c r="F166" s="45" t="inlineStr">
+        <is>
+          <t>Min Value</t>
+        </is>
+      </c>
+      <c r="G166" s="45" t="inlineStr">
+        <is>
+          <t>Max Value</t>
+        </is>
+      </c>
+      <c r="H166" s="45" t="inlineStr">
+        <is>
+          <t>Notes / Issues</t>
+        </is>
+      </c>
+      <c r="I166" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="B167" s="16" t="inlineStr">
@@ -6718,7 +7000,7 @@
         </is>
       </c>
       <c r="E167" s="16" t="n">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="F167" s="16" t="n">
         <v>1</v>
@@ -6754,7 +7036,7 @@
         </is>
       </c>
       <c r="E168" s="15" t="n">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
@@ -6794,7 +7076,7 @@
         </is>
       </c>
       <c r="E169" s="16" t="n">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="F169" s="16" t="inlineStr">
         <is>
@@ -6870,7 +7152,7 @@
         </is>
       </c>
       <c r="E171" s="16" t="n">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="F171" s="16" t="inlineStr">
         <is>
@@ -6900,16 +7182,48 @@
       <c r="I172" s="15" t="n"/>
     </row>
     <row r="173">
-      <c r="B173" s="49" t="n"/>
+      <c r="B173" s="49" t="inlineStr">
+        <is>
+          <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="B174" s="45" t="n"/>
-      <c r="C174" s="45" t="n"/>
-      <c r="D174" s="45" t="n"/>
-      <c r="E174" s="45" t="n"/>
-      <c r="F174" s="45" t="n"/>
-      <c r="G174" s="45" t="n"/>
-      <c r="H174" s="45" t="n"/>
+      <c r="B174" s="45" t="inlineStr">
+        <is>
+          <t>FK Field</t>
+        </is>
+      </c>
+      <c r="C174" s="45" t="inlineStr">
+        <is>
+          <t>References Table</t>
+        </is>
+      </c>
+      <c r="D174" s="45" t="inlineStr">
+        <is>
+          <t>References Field</t>
+        </is>
+      </c>
+      <c r="E174" s="45" t="inlineStr">
+        <is>
+          <t>Orphan Row Count</t>
+        </is>
+      </c>
+      <c r="F174" s="45" t="inlineStr">
+        <is>
+          <t>Orphan %</t>
+        </is>
+      </c>
+      <c r="G174" s="45" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H174" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="B175" s="16" t="inlineStr">
@@ -6973,13 +7287,33 @@
       </c>
     </row>
     <row r="180">
-      <c r="B180" s="48" t="n"/>
-      <c r="C180" s="48" t="n"/>
-      <c r="D180" s="48" t="n"/>
+      <c r="B180" s="48" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C180" s="48" t="inlineStr">
+        <is>
+          <t>How to measure</t>
+        </is>
+      </c>
+      <c r="D180" s="48" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="B181" s="25" t="n"/>
-      <c r="C181" s="24" t="n"/>
+      <c r="B181" s="25" t="inlineStr">
+        <is>
+          <t>Table / view name</t>
+        </is>
+      </c>
+      <c r="C181" s="24" t="inlineStr">
+        <is>
+          <t>Exact name as it appears in source schema</t>
+        </is>
+      </c>
       <c r="D181" s="44" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
@@ -6987,8 +7321,16 @@
       </c>
     </row>
     <row r="182">
-      <c r="B182" s="25" t="n"/>
-      <c r="C182" s="24" t="n"/>
+      <c r="B182" s="25" t="inlineStr">
+        <is>
+          <t>Business purpose</t>
+        </is>
+      </c>
+      <c r="C182" s="24" t="inlineStr">
+        <is>
+          <t>What business process does this table record?</t>
+        </is>
+      </c>
       <c r="D182" s="43" t="inlineStr">
         <is>
           <t>Legal entities / subsidiaries within NetSuite OneWorld</t>
@@ -6996,8 +7338,16 @@
       </c>
     </row>
     <row r="183">
-      <c r="B183" s="25" t="n"/>
-      <c r="C183" s="24" t="n"/>
+      <c r="B183" s="25" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="C183" s="24" t="inlineStr">
+        <is>
+          <t>One row = one [what]? e.g. one invoice line, one work order</t>
+        </is>
+      </c>
       <c r="D183" s="44" t="inlineStr">
         <is>
           <t>One row = one subsidiary</t>
@@ -7005,15 +7355,31 @@
       </c>
     </row>
     <row r="184">
-      <c r="B184" s="25" t="n"/>
-      <c r="C184" s="24" t="n"/>
+      <c r="B184" s="25" t="inlineStr">
+        <is>
+          <t>Total row count</t>
+        </is>
+      </c>
+      <c r="C184" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM table</t>
+        </is>
+      </c>
       <c r="D184" s="43" t="n">
-        <v>40</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="185">
-      <c r="B185" s="25" t="n"/>
-      <c r="C185" s="24" t="n"/>
+      <c r="B185" s="25" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="C185" s="24" t="inlineStr">
+        <is>
+          <t>MIN and MAX of primary date field</t>
+        </is>
+      </c>
       <c r="D185" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
@@ -7021,8 +7387,16 @@
       </c>
     </row>
     <row r="186">
-      <c r="B186" s="25" t="n"/>
-      <c r="C186" s="24" t="n"/>
+      <c r="B186" s="25" t="inlineStr">
+        <is>
+          <t>Primary key field(s)</t>
+        </is>
+      </c>
+      <c r="C186" s="24" t="inlineStr">
+        <is>
+          <t>Field name(s) — is it a surrogate or natural key?</t>
+        </is>
+      </c>
       <c r="D186" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
@@ -7030,17 +7404,33 @@
       </c>
     </row>
     <row r="187">
-      <c r="B187" s="25" t="n"/>
-      <c r="C187" s="24" t="n"/>
+      <c r="B187" s="25" t="inlineStr">
+        <is>
+          <t>PK uniqueness check</t>
+        </is>
+      </c>
+      <c r="C187" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) vs COUNT(DISTINCT pk) — match = PASS</t>
+        </is>
+      </c>
       <c r="D187" s="44" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="B188" s="25" t="n"/>
-      <c r="C188" s="24" t="n"/>
+      <c r="B188" s="25" t="inlineStr">
+        <is>
+          <t>Canonical domain</t>
+        </is>
+      </c>
+      <c r="C188" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical domain does this table feed? (Domain 1–5)</t>
+        </is>
+      </c>
       <c r="D188" s="43" t="inlineStr">
         <is>
           <t>D5 – Financials</t>
@@ -7048,8 +7438,16 @@
       </c>
     </row>
     <row r="189">
-      <c r="B189" s="25" t="n"/>
-      <c r="C189" s="24" t="n"/>
+      <c r="B189" s="25" t="inlineStr">
+        <is>
+          <t>Canonical entities</t>
+        </is>
+      </c>
+      <c r="C189" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical entities? e.g. WORK_ORDER, WORK_ORDER_LINE</t>
+        </is>
+      </c>
       <c r="D189" s="44" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
@@ -7057,8 +7455,16 @@
       </c>
     </row>
     <row r="190">
-      <c r="B190" s="25" t="n"/>
-      <c r="C190" s="24" t="n"/>
+      <c r="B190" s="25" t="inlineStr">
+        <is>
+          <t>Overall table RAG</t>
+        </is>
+      </c>
+      <c r="C190" s="24" t="inlineStr">
+        <is>
+          <t>GREEN / AMBER / RED — your assessment of table usability</t>
+        </is>
+      </c>
       <c r="D190" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -7066,17 +7472,53 @@
       </c>
     </row>
     <row r="191">
-      <c r="B191" s="49" t="n"/>
+      <c r="B191" s="49" t="inlineStr">
+        <is>
+          <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
+        </is>
+      </c>
     </row>
     <row r="192">
-      <c r="B192" s="45" t="n"/>
-      <c r="C192" s="45" t="n"/>
-      <c r="D192" s="45" t="n"/>
-      <c r="E192" s="45" t="n"/>
-      <c r="F192" s="45" t="n"/>
-      <c r="G192" s="45" t="n"/>
-      <c r="H192" s="45" t="n"/>
-      <c r="I192" s="45" t="n"/>
+      <c r="B192" s="45" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="C192" s="45" t="inlineStr">
+        <is>
+          <t>Field Type</t>
+        </is>
+      </c>
+      <c r="D192" s="45" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="E192" s="45" t="inlineStr">
+        <is>
+          <t>Distinct Count</t>
+        </is>
+      </c>
+      <c r="F192" s="45" t="inlineStr">
+        <is>
+          <t>Min Value</t>
+        </is>
+      </c>
+      <c r="G192" s="45" t="inlineStr">
+        <is>
+          <t>Max Value</t>
+        </is>
+      </c>
+      <c r="H192" s="45" t="inlineStr">
+        <is>
+          <t>Notes / Issues</t>
+        </is>
+      </c>
+      <c r="I192" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="B193" s="16" t="inlineStr">
@@ -7095,7 +7537,7 @@
         </is>
       </c>
       <c r="E193" s="16" t="n">
-        <v>40</v>
+        <v>-13</v>
       </c>
       <c r="F193" s="16" t="n">
         <v>1</v>
@@ -7131,7 +7573,7 @@
         </is>
       </c>
       <c r="E194" s="15" t="n">
-        <v>40</v>
+        <v>-13</v>
       </c>
       <c r="F194" s="15" t="inlineStr">
         <is>
@@ -7207,7 +7649,7 @@
         </is>
       </c>
       <c r="E196" s="15" t="n">
-        <v>38</v>
+        <v>-12</v>
       </c>
       <c r="F196" s="15" t="n"/>
       <c r="G196" s="15" t="n"/>
@@ -7239,7 +7681,7 @@
         </is>
       </c>
       <c r="E197" s="16" t="n">
-        <v>36</v>
+        <v>-12</v>
       </c>
       <c r="F197" s="16" t="inlineStr">
         <is>
@@ -7269,16 +7711,48 @@
       <c r="I198" s="15" t="n"/>
     </row>
     <row r="199">
-      <c r="B199" s="49" t="n"/>
+      <c r="B199" s="49" t="inlineStr">
+        <is>
+          <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
+        </is>
+      </c>
     </row>
     <row r="200">
-      <c r="B200" s="45" t="n"/>
-      <c r="C200" s="45" t="n"/>
-      <c r="D200" s="45" t="n"/>
-      <c r="E200" s="45" t="n"/>
-      <c r="F200" s="45" t="n"/>
-      <c r="G200" s="45" t="n"/>
-      <c r="H200" s="45" t="n"/>
+      <c r="B200" s="45" t="inlineStr">
+        <is>
+          <t>FK Field</t>
+        </is>
+      </c>
+      <c r="C200" s="45" t="inlineStr">
+        <is>
+          <t>References Table</t>
+        </is>
+      </c>
+      <c r="D200" s="45" t="inlineStr">
+        <is>
+          <t>References Field</t>
+        </is>
+      </c>
+      <c r="E200" s="45" t="inlineStr">
+        <is>
+          <t>Orphan Row Count</t>
+        </is>
+      </c>
+      <c r="F200" s="45" t="inlineStr">
+        <is>
+          <t>Orphan %</t>
+        </is>
+      </c>
+      <c r="G200" s="45" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H200" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="B201" s="16" t="n"/>
@@ -7316,13 +7790,33 @@
       </c>
     </row>
     <row r="206">
-      <c r="B206" s="48" t="n"/>
-      <c r="C206" s="48" t="n"/>
-      <c r="D206" s="48" t="n"/>
+      <c r="B206" s="48" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C206" s="48" t="inlineStr">
+        <is>
+          <t>How to measure</t>
+        </is>
+      </c>
+      <c r="D206" s="48" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="207">
-      <c r="B207" s="25" t="n"/>
-      <c r="C207" s="24" t="n"/>
+      <c r="B207" s="25" t="inlineStr">
+        <is>
+          <t>Table / view name</t>
+        </is>
+      </c>
+      <c r="C207" s="24" t="inlineStr">
+        <is>
+          <t>Exact name as it appears in source schema</t>
+        </is>
+      </c>
       <c r="D207" s="44" t="inlineStr">
         <is>
           <t>DEPARTMENT</t>
@@ -7330,8 +7824,16 @@
       </c>
     </row>
     <row r="208">
-      <c r="B208" s="25" t="n"/>
-      <c r="C208" s="24" t="n"/>
+      <c r="B208" s="25" t="inlineStr">
+        <is>
+          <t>Business purpose</t>
+        </is>
+      </c>
+      <c r="C208" s="24" t="inlineStr">
+        <is>
+          <t>What business process does this table record?</t>
+        </is>
+      </c>
       <c r="D208" s="43" t="inlineStr">
         <is>
           <t>Cost centre / department classification</t>
@@ -7339,8 +7841,16 @@
       </c>
     </row>
     <row r="209">
-      <c r="B209" s="25" t="n"/>
-      <c r="C209" s="24" t="n"/>
+      <c r="B209" s="25" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="C209" s="24" t="inlineStr">
+        <is>
+          <t>One row = one [what]? e.g. one invoice line, one work order</t>
+        </is>
+      </c>
       <c r="D209" s="44" t="inlineStr">
         <is>
           <t>One row = one department</t>
@@ -7348,15 +7858,31 @@
       </c>
     </row>
     <row r="210">
-      <c r="B210" s="25" t="n"/>
-      <c r="C210" s="24" t="n"/>
+      <c r="B210" s="25" t="inlineStr">
+        <is>
+          <t>Total row count</t>
+        </is>
+      </c>
+      <c r="C210" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM table</t>
+        </is>
+      </c>
       <c r="D210" s="43" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
-      <c r="B211" s="25" t="n"/>
-      <c r="C211" s="24" t="n"/>
+      <c r="B211" s="25" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="C211" s="24" t="inlineStr">
+        <is>
+          <t>MIN and MAX of primary date field</t>
+        </is>
+      </c>
       <c r="D211" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
@@ -7364,8 +7890,16 @@
       </c>
     </row>
     <row r="212">
-      <c r="B212" s="25" t="n"/>
-      <c r="C212" s="24" t="n"/>
+      <c r="B212" s="25" t="inlineStr">
+        <is>
+          <t>Primary key field(s)</t>
+        </is>
+      </c>
+      <c r="C212" s="24" t="inlineStr">
+        <is>
+          <t>Field name(s) — is it a surrogate or natural key?</t>
+        </is>
+      </c>
       <c r="D212" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
@@ -7373,8 +7907,16 @@
       </c>
     </row>
     <row r="213">
-      <c r="B213" s="25" t="n"/>
-      <c r="C213" s="24" t="n"/>
+      <c r="B213" s="25" t="inlineStr">
+        <is>
+          <t>PK uniqueness check</t>
+        </is>
+      </c>
+      <c r="C213" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) vs COUNT(DISTINCT pk) — match = PASS</t>
+        </is>
+      </c>
       <c r="D213" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7382,8 +7924,16 @@
       </c>
     </row>
     <row r="214">
-      <c r="B214" s="25" t="n"/>
-      <c r="C214" s="24" t="n"/>
+      <c r="B214" s="25" t="inlineStr">
+        <is>
+          <t>Canonical domain</t>
+        </is>
+      </c>
+      <c r="C214" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical domain does this table feed? (Domain 1–5)</t>
+        </is>
+      </c>
       <c r="D214" s="43" t="inlineStr">
         <is>
           <t>D5 – Financials</t>
@@ -7391,8 +7941,16 @@
       </c>
     </row>
     <row r="215">
-      <c r="B215" s="25" t="n"/>
-      <c r="C215" s="24" t="n"/>
+      <c r="B215" s="25" t="inlineStr">
+        <is>
+          <t>Canonical entities</t>
+        </is>
+      </c>
+      <c r="C215" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical entities? e.g. WORK_ORDER, WORK_ORDER_LINE</t>
+        </is>
+      </c>
       <c r="D215" s="44" t="inlineStr">
         <is>
           <t>DEPARTMENT</t>
@@ -7400,8 +7958,16 @@
       </c>
     </row>
     <row r="216">
-      <c r="B216" s="25" t="n"/>
-      <c r="C216" s="24" t="n"/>
+      <c r="B216" s="25" t="inlineStr">
+        <is>
+          <t>Overall table RAG</t>
+        </is>
+      </c>
+      <c r="C216" s="24" t="inlineStr">
+        <is>
+          <t>GREEN / AMBER / RED — your assessment of table usability</t>
+        </is>
+      </c>
       <c r="D216" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -7409,17 +7975,53 @@
       </c>
     </row>
     <row r="217">
-      <c r="B217" s="49" t="n"/>
+      <c r="B217" s="49" t="inlineStr">
+        <is>
+          <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
+        </is>
+      </c>
     </row>
     <row r="218">
-      <c r="B218" s="45" t="n"/>
-      <c r="C218" s="45" t="n"/>
-      <c r="D218" s="45" t="n"/>
-      <c r="E218" s="45" t="n"/>
-      <c r="F218" s="45" t="n"/>
-      <c r="G218" s="45" t="n"/>
-      <c r="H218" s="45" t="n"/>
-      <c r="I218" s="45" t="n"/>
+      <c r="B218" s="45" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="C218" s="45" t="inlineStr">
+        <is>
+          <t>Field Type</t>
+        </is>
+      </c>
+      <c r="D218" s="45" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="E218" s="45" t="inlineStr">
+        <is>
+          <t>Distinct Count</t>
+        </is>
+      </c>
+      <c r="F218" s="45" t="inlineStr">
+        <is>
+          <t>Min Value</t>
+        </is>
+      </c>
+      <c r="G218" s="45" t="inlineStr">
+        <is>
+          <t>Max Value</t>
+        </is>
+      </c>
+      <c r="H218" s="45" t="inlineStr">
+        <is>
+          <t>Notes / Issues</t>
+        </is>
+      </c>
+      <c r="I218" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="B219" s="16" t="inlineStr">
@@ -7438,7 +8040,7 @@
         </is>
       </c>
       <c r="E219" s="16" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F219" s="16" t="n">
         <v>1</v>
@@ -7474,7 +8076,7 @@
         </is>
       </c>
       <c r="E220" s="15" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F220" s="15" t="inlineStr">
         <is>
@@ -7550,7 +8152,7 @@
         </is>
       </c>
       <c r="E222" s="15" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F222" s="15" t="inlineStr">
         <is>
@@ -7590,16 +8192,48 @@
       <c r="I224" s="15" t="n"/>
     </row>
     <row r="225">
-      <c r="B225" s="49" t="n"/>
+      <c r="B225" s="49" t="inlineStr">
+        <is>
+          <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
+        </is>
+      </c>
     </row>
     <row r="226">
-      <c r="B226" s="45" t="n"/>
-      <c r="C226" s="45" t="n"/>
-      <c r="D226" s="45" t="n"/>
-      <c r="E226" s="45" t="n"/>
-      <c r="F226" s="45" t="n"/>
-      <c r="G226" s="45" t="n"/>
-      <c r="H226" s="45" t="n"/>
+      <c r="B226" s="45" t="inlineStr">
+        <is>
+          <t>FK Field</t>
+        </is>
+      </c>
+      <c r="C226" s="45" t="inlineStr">
+        <is>
+          <t>References Table</t>
+        </is>
+      </c>
+      <c r="D226" s="45" t="inlineStr">
+        <is>
+          <t>References Field</t>
+        </is>
+      </c>
+      <c r="E226" s="45" t="inlineStr">
+        <is>
+          <t>Orphan Row Count</t>
+        </is>
+      </c>
+      <c r="F226" s="45" t="inlineStr">
+        <is>
+          <t>Orphan %</t>
+        </is>
+      </c>
+      <c r="G226" s="45" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H226" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="B227" s="16" t="inlineStr">
@@ -7663,13 +8297,33 @@
       </c>
     </row>
     <row r="232">
-      <c r="B232" s="48" t="n"/>
-      <c r="C232" s="48" t="n"/>
-      <c r="D232" s="48" t="n"/>
+      <c r="B232" s="48" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C232" s="48" t="inlineStr">
+        <is>
+          <t>How to measure</t>
+        </is>
+      </c>
+      <c r="D232" s="48" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="233">
-      <c r="B233" s="25" t="n"/>
-      <c r="C233" s="24" t="n"/>
+      <c r="B233" s="25" t="inlineStr">
+        <is>
+          <t>Table / view name</t>
+        </is>
+      </c>
+      <c r="C233" s="24" t="inlineStr">
+        <is>
+          <t>Exact name as it appears in source schema</t>
+        </is>
+      </c>
       <c r="D233" s="44" t="inlineStr">
         <is>
           <t>SALESORDER</t>
@@ -7677,8 +8331,16 @@
       </c>
     </row>
     <row r="234">
-      <c r="B234" s="25" t="n"/>
-      <c r="C234" s="24" t="n"/>
+      <c r="B234" s="25" t="inlineStr">
+        <is>
+          <t>Business purpose</t>
+        </is>
+      </c>
+      <c r="C234" s="24" t="inlineStr">
+        <is>
+          <t>What business process does this table record?</t>
+        </is>
+      </c>
       <c r="D234" s="43" t="inlineStr">
         <is>
           <t>Sales orders linked to customers and items</t>
@@ -7686,8 +8348,16 @@
       </c>
     </row>
     <row r="235">
-      <c r="B235" s="25" t="n"/>
-      <c r="C235" s="24" t="n"/>
+      <c r="B235" s="25" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="C235" s="24" t="inlineStr">
+        <is>
+          <t>One row = one [what]? e.g. one invoice line, one work order</t>
+        </is>
+      </c>
       <c r="D235" s="44" t="inlineStr">
         <is>
           <t>One row = one sales order header</t>
@@ -7695,15 +8365,31 @@
       </c>
     </row>
     <row r="236">
-      <c r="B236" s="25" t="n"/>
-      <c r="C236" s="24" t="n"/>
+      <c r="B236" s="25" t="inlineStr">
+        <is>
+          <t>Total row count</t>
+        </is>
+      </c>
+      <c r="C236" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM table</t>
+        </is>
+      </c>
       <c r="D236" s="43" t="n">
-        <v>2488</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="237">
-      <c r="B237" s="25" t="n"/>
-      <c r="C237" s="24" t="n"/>
+      <c r="B237" s="25" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="C237" s="24" t="inlineStr">
+        <is>
+          <t>MIN and MAX of primary date field</t>
+        </is>
+      </c>
       <c r="D237" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
@@ -7711,8 +8397,16 @@
       </c>
     </row>
     <row r="238">
-      <c r="B238" s="25" t="n"/>
-      <c r="C238" s="24" t="n"/>
+      <c r="B238" s="25" t="inlineStr">
+        <is>
+          <t>Primary key field(s)</t>
+        </is>
+      </c>
+      <c r="C238" s="24" t="inlineStr">
+        <is>
+          <t>Field name(s) — is it a surrogate or natural key?</t>
+        </is>
+      </c>
       <c r="D238" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
@@ -7720,8 +8414,16 @@
       </c>
     </row>
     <row r="239">
-      <c r="B239" s="25" t="n"/>
-      <c r="C239" s="24" t="n"/>
+      <c r="B239" s="25" t="inlineStr">
+        <is>
+          <t>PK uniqueness check</t>
+        </is>
+      </c>
+      <c r="C239" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) vs COUNT(DISTINCT pk) — match = PASS</t>
+        </is>
+      </c>
       <c r="D239" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7729,8 +8431,16 @@
       </c>
     </row>
     <row r="240">
-      <c r="B240" s="25" t="n"/>
-      <c r="C240" s="24" t="n"/>
+      <c r="B240" s="25" t="inlineStr">
+        <is>
+          <t>Canonical domain</t>
+        </is>
+      </c>
+      <c r="C240" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical domain does this table feed? (Domain 1–5)</t>
+        </is>
+      </c>
       <c r="D240" s="43" t="inlineStr">
         <is>
           <t>D2 – Contracts &amp; Revenue</t>
@@ -7738,8 +8448,16 @@
       </c>
     </row>
     <row r="241">
-      <c r="B241" s="25" t="n"/>
-      <c r="C241" s="24" t="n"/>
+      <c r="B241" s="25" t="inlineStr">
+        <is>
+          <t>Canonical entities</t>
+        </is>
+      </c>
+      <c r="C241" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical entities? e.g. WORK_ORDER, WORK_ORDER_LINE</t>
+        </is>
+      </c>
       <c r="D241" s="44" t="inlineStr">
         <is>
           <t>SALES_ORDER</t>
@@ -7747,8 +8465,16 @@
       </c>
     </row>
     <row r="242">
-      <c r="B242" s="25" t="n"/>
-      <c r="C242" s="24" t="n"/>
+      <c r="B242" s="25" t="inlineStr">
+        <is>
+          <t>Overall table RAG</t>
+        </is>
+      </c>
+      <c r="C242" s="24" t="inlineStr">
+        <is>
+          <t>GREEN / AMBER / RED — your assessment of table usability</t>
+        </is>
+      </c>
       <c r="D242" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -7756,17 +8482,53 @@
       </c>
     </row>
     <row r="243">
-      <c r="B243" s="49" t="n"/>
+      <c r="B243" s="49" t="inlineStr">
+        <is>
+          <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
+        </is>
+      </c>
     </row>
     <row r="244">
-      <c r="B244" s="45" t="n"/>
-      <c r="C244" s="45" t="n"/>
-      <c r="D244" s="45" t="n"/>
-      <c r="E244" s="45" t="n"/>
-      <c r="F244" s="45" t="n"/>
-      <c r="G244" s="45" t="n"/>
-      <c r="H244" s="45" t="n"/>
-      <c r="I244" s="45" t="n"/>
+      <c r="B244" s="45" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="C244" s="45" t="inlineStr">
+        <is>
+          <t>Field Type</t>
+        </is>
+      </c>
+      <c r="D244" s="45" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="E244" s="45" t="inlineStr">
+        <is>
+          <t>Distinct Count</t>
+        </is>
+      </c>
+      <c r="F244" s="45" t="inlineStr">
+        <is>
+          <t>Min Value</t>
+        </is>
+      </c>
+      <c r="G244" s="45" t="inlineStr">
+        <is>
+          <t>Max Value</t>
+        </is>
+      </c>
+      <c r="H244" s="45" t="inlineStr">
+        <is>
+          <t>Notes / Issues</t>
+        </is>
+      </c>
+      <c r="I244" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="B245" s="16" t="inlineStr">
@@ -7785,7 +8547,7 @@
         </is>
       </c>
       <c r="E245" s="16" t="n">
-        <v>2488</v>
+        <v>2482</v>
       </c>
       <c r="F245" s="16" t="n">
         <v>1</v>
@@ -7821,7 +8583,7 @@
         </is>
       </c>
       <c r="E246" s="15" t="n">
-        <v>2488</v>
+        <v>2482</v>
       </c>
       <c r="F246" s="15" t="inlineStr">
         <is>
@@ -7861,7 +8623,7 @@
         </is>
       </c>
       <c r="E247" s="16" t="n">
-        <v>1592</v>
+        <v>1588</v>
       </c>
       <c r="F247" s="16" t="inlineStr">
         <is>
@@ -7875,7 +8637,7 @@
       </c>
       <c r="H247" s="16" t="inlineStr">
         <is>
-          <t>1592 unique dates</t>
+          <t>1588 unique dates</t>
         </is>
       </c>
       <c r="I247" s="16" t="inlineStr">
@@ -7901,7 +8663,7 @@
         </is>
       </c>
       <c r="E248" s="15" t="n">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F248" s="15" t="n">
         <v>1</v>
@@ -7937,7 +8699,7 @@
         </is>
       </c>
       <c r="E249" s="16" t="n">
-        <v>2438</v>
+        <v>2432</v>
       </c>
       <c r="F249" s="16" t="n">
         <v>50</v>
@@ -7993,16 +8755,48 @@
       </c>
     </row>
     <row r="251">
-      <c r="B251" s="49" t="n"/>
+      <c r="B251" s="49" t="inlineStr">
+        <is>
+          <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
+        </is>
+      </c>
     </row>
     <row r="252">
-      <c r="B252" s="45" t="n"/>
-      <c r="C252" s="45" t="n"/>
-      <c r="D252" s="45" t="n"/>
-      <c r="E252" s="45" t="n"/>
-      <c r="F252" s="45" t="n"/>
-      <c r="G252" s="45" t="n"/>
-      <c r="H252" s="45" t="n"/>
+      <c r="B252" s="45" t="inlineStr">
+        <is>
+          <t>FK Field</t>
+        </is>
+      </c>
+      <c r="C252" s="45" t="inlineStr">
+        <is>
+          <t>References Table</t>
+        </is>
+      </c>
+      <c r="D252" s="45" t="inlineStr">
+        <is>
+          <t>References Field</t>
+        </is>
+      </c>
+      <c r="E252" s="45" t="inlineStr">
+        <is>
+          <t>Orphan Row Count</t>
+        </is>
+      </c>
+      <c r="F252" s="45" t="inlineStr">
+        <is>
+          <t>Orphan %</t>
+        </is>
+      </c>
+      <c r="G252" s="45" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H252" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="B253" s="16" t="inlineStr">
@@ -8092,13 +8886,33 @@
       </c>
     </row>
     <row r="258">
-      <c r="B258" s="48" t="n"/>
-      <c r="C258" s="48" t="n"/>
-      <c r="D258" s="48" t="n"/>
+      <c r="B258" s="48" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C258" s="48" t="inlineStr">
+        <is>
+          <t>How to measure</t>
+        </is>
+      </c>
+      <c r="D258" s="48" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="259">
-      <c r="B259" s="25" t="n"/>
-      <c r="C259" s="24" t="n"/>
+      <c r="B259" s="25" t="inlineStr">
+        <is>
+          <t>Table / view name</t>
+        </is>
+      </c>
+      <c r="C259" s="24" t="inlineStr">
+        <is>
+          <t>Exact name as it appears in source schema</t>
+        </is>
+      </c>
       <c r="D259" s="44" t="inlineStr">
         <is>
           <t>PURCHASEORDER</t>
@@ -8106,8 +8920,16 @@
       </c>
     </row>
     <row r="260">
-      <c r="B260" s="25" t="n"/>
-      <c r="C260" s="24" t="n"/>
+      <c r="B260" s="25" t="inlineStr">
+        <is>
+          <t>Business purpose</t>
+        </is>
+      </c>
+      <c r="C260" s="24" t="inlineStr">
+        <is>
+          <t>What business process does this table record?</t>
+        </is>
+      </c>
       <c r="D260" s="43" t="inlineStr">
         <is>
           <t>Purchase orders raised against vendors</t>
@@ -8115,8 +8937,16 @@
       </c>
     </row>
     <row r="261">
-      <c r="B261" s="25" t="n"/>
-      <c r="C261" s="24" t="n"/>
+      <c r="B261" s="25" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="C261" s="24" t="inlineStr">
+        <is>
+          <t>One row = one [what]? e.g. one invoice line, one work order</t>
+        </is>
+      </c>
       <c r="D261" s="44" t="inlineStr">
         <is>
           <t>One row = one purchase order header</t>
@@ -8124,15 +8954,31 @@
       </c>
     </row>
     <row r="262">
-      <c r="B262" s="25" t="n"/>
-      <c r="C262" s="24" t="n"/>
+      <c r="B262" s="25" t="inlineStr">
+        <is>
+          <t>Total row count</t>
+        </is>
+      </c>
+      <c r="C262" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM table</t>
+        </is>
+      </c>
       <c r="D262" s="43" t="n">
-        <v>805</v>
+        <v>828</v>
       </c>
     </row>
     <row r="263">
-      <c r="B263" s="25" t="n"/>
-      <c r="C263" s="24" t="n"/>
+      <c r="B263" s="25" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="C263" s="24" t="inlineStr">
+        <is>
+          <t>MIN and MAX of primary date field</t>
+        </is>
+      </c>
       <c r="D263" s="44" t="inlineStr">
         <is>
           <t>2020-01-01 – 2025-03-01</t>
@@ -8140,8 +8986,16 @@
       </c>
     </row>
     <row r="264">
-      <c r="B264" s="25" t="n"/>
-      <c r="C264" s="24" t="n"/>
+      <c r="B264" s="25" t="inlineStr">
+        <is>
+          <t>Primary key field(s)</t>
+        </is>
+      </c>
+      <c r="C264" s="24" t="inlineStr">
+        <is>
+          <t>Field name(s) — is it a surrogate or natural key?</t>
+        </is>
+      </c>
       <c r="D264" s="43" t="inlineStr">
         <is>
           <t>id (surrogate)</t>
@@ -8149,8 +9003,16 @@
       </c>
     </row>
     <row r="265">
-      <c r="B265" s="25" t="n"/>
-      <c r="C265" s="24" t="n"/>
+      <c r="B265" s="25" t="inlineStr">
+        <is>
+          <t>PK uniqueness check</t>
+        </is>
+      </c>
+      <c r="C265" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) vs COUNT(DISTINCT pk) — match = PASS</t>
+        </is>
+      </c>
       <c r="D265" s="44" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8158,8 +9020,16 @@
       </c>
     </row>
     <row r="266">
-      <c r="B266" s="25" t="n"/>
-      <c r="C266" s="24" t="n"/>
+      <c r="B266" s="25" t="inlineStr">
+        <is>
+          <t>Canonical domain</t>
+        </is>
+      </c>
+      <c r="C266" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical domain does this table feed? (Domain 1–5)</t>
+        </is>
+      </c>
       <c r="D266" s="43" t="inlineStr">
         <is>
           <t>D5 – Financials</t>
@@ -8167,8 +9037,16 @@
       </c>
     </row>
     <row r="267">
-      <c r="B267" s="25" t="n"/>
-      <c r="C267" s="24" t="n"/>
+      <c r="B267" s="25" t="inlineStr">
+        <is>
+          <t>Canonical entities</t>
+        </is>
+      </c>
+      <c r="C267" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical entities? e.g. WORK_ORDER, WORK_ORDER_LINE</t>
+        </is>
+      </c>
       <c r="D267" s="44" t="inlineStr">
         <is>
           <t>PURCHASE_ORDER</t>
@@ -8176,8 +9054,16 @@
       </c>
     </row>
     <row r="268">
-      <c r="B268" s="25" t="n"/>
-      <c r="C268" s="24" t="n"/>
+      <c r="B268" s="25" t="inlineStr">
+        <is>
+          <t>Overall table RAG</t>
+        </is>
+      </c>
+      <c r="C268" s="24" t="inlineStr">
+        <is>
+          <t>GREEN / AMBER / RED — your assessment of table usability</t>
+        </is>
+      </c>
       <c r="D268" s="43" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -8185,17 +9071,53 @@
       </c>
     </row>
     <row r="269">
-      <c r="B269" s="49" t="n"/>
+      <c r="B269" s="49" t="inlineStr">
+        <is>
+          <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
+        </is>
+      </c>
     </row>
     <row r="270">
-      <c r="B270" s="45" t="n"/>
-      <c r="C270" s="45" t="n"/>
-      <c r="D270" s="45" t="n"/>
-      <c r="E270" s="45" t="n"/>
-      <c r="F270" s="45" t="n"/>
-      <c r="G270" s="45" t="n"/>
-      <c r="H270" s="45" t="n"/>
-      <c r="I270" s="45" t="n"/>
+      <c r="B270" s="45" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="C270" s="45" t="inlineStr">
+        <is>
+          <t>Field Type</t>
+        </is>
+      </c>
+      <c r="D270" s="45" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="E270" s="45" t="inlineStr">
+        <is>
+          <t>Distinct Count</t>
+        </is>
+      </c>
+      <c r="F270" s="45" t="inlineStr">
+        <is>
+          <t>Min Value</t>
+        </is>
+      </c>
+      <c r="G270" s="45" t="inlineStr">
+        <is>
+          <t>Max Value</t>
+        </is>
+      </c>
+      <c r="H270" s="45" t="inlineStr">
+        <is>
+          <t>Notes / Issues</t>
+        </is>
+      </c>
+      <c r="I270" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="B271" s="16" t="inlineStr">
@@ -8214,7 +9136,7 @@
         </is>
       </c>
       <c r="E271" s="16" t="n">
-        <v>805</v>
+        <v>828</v>
       </c>
       <c r="F271" s="16" t="n">
         <v>1</v>
@@ -8250,7 +9172,7 @@
         </is>
       </c>
       <c r="E272" s="15" t="n">
-        <v>805</v>
+        <v>828</v>
       </c>
       <c r="F272" s="15" t="inlineStr">
         <is>
@@ -8290,7 +9212,7 @@
         </is>
       </c>
       <c r="E273" s="16" t="n">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="F273" s="16" t="inlineStr">
         <is>
@@ -8304,7 +9226,7 @@
       </c>
       <c r="H273" s="16" t="inlineStr">
         <is>
-          <t>757 unique dates</t>
+          <t>778 unique dates</t>
         </is>
       </c>
       <c r="I273" s="16" t="inlineStr">
@@ -8330,7 +9252,7 @@
         </is>
       </c>
       <c r="E274" s="15" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F274" s="15" t="n">
         <v>1</v>
@@ -8366,7 +9288,7 @@
         </is>
       </c>
       <c r="E275" s="16" t="n">
-        <v>781</v>
+        <v>803</v>
       </c>
       <c r="F275" s="16" t="n">
         <v>10</v>
@@ -8426,16 +9348,48 @@
       </c>
     </row>
     <row r="277">
-      <c r="B277" s="49" t="n"/>
+      <c r="B277" s="49" t="inlineStr">
+        <is>
+          <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
+        </is>
+      </c>
     </row>
     <row r="278">
-      <c r="B278" s="45" t="n"/>
-      <c r="C278" s="45" t="n"/>
-      <c r="D278" s="45" t="n"/>
-      <c r="E278" s="45" t="n"/>
-      <c r="F278" s="45" t="n"/>
-      <c r="G278" s="45" t="n"/>
-      <c r="H278" s="45" t="n"/>
+      <c r="B278" s="45" t="inlineStr">
+        <is>
+          <t>FK Field</t>
+        </is>
+      </c>
+      <c r="C278" s="45" t="inlineStr">
+        <is>
+          <t>References Table</t>
+        </is>
+      </c>
+      <c r="D278" s="45" t="inlineStr">
+        <is>
+          <t>References Field</t>
+        </is>
+      </c>
+      <c r="E278" s="45" t="inlineStr">
+        <is>
+          <t>Orphan Row Count</t>
+        </is>
+      </c>
+      <c r="F278" s="45" t="inlineStr">
+        <is>
+          <t>Orphan %</t>
+        </is>
+      </c>
+      <c r="G278" s="45" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H278" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="B279" s="16" t="inlineStr">
@@ -8537,7 +9491,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8546,7 +9500,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -8572,7 +9526,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -8581,7 +9535,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -8607,7 +9561,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -8616,16 +9570,16 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>Investigate load delay</t>
         </is>
       </c>
     </row>
@@ -8677,7 +9631,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -8686,7 +9640,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -8712,7 +9666,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -8721,16 +9675,16 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -8747,7 +9701,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8756,7 +9710,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -8782,7 +9736,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8791,16 +9745,16 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -8817,7 +9771,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -8826,7 +9780,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -8892,10 +9846,10 @@
       <c r="D298" t="inlineStr">
         <is>
           <t>1. Null subsidiary_id on 101 TRANSACTION rows (2.0%)
-2. DEPARTMENT: 2 rows with null subsidiary_id (5.0%) – orphan risk
+2. DEPARTMENT: 0 rows with null subsidiary_id (0.0%) – orphan risk
 3. No direct FK from SALESORDER to CONTRACT
-4. VENDOR: 39 rows with null email (19.9%) – enrich before CRM migration
-5. PURCHASEORDER: 16 rows with null entity_id (2.0%) – verify vendor onboarding</t>
+4. VENDOR: 32 rows with null email (19.8%) – enrich before CRM migration
+5. PURCHASEORDER: 17 rows with null entity_id (2.1%) – verify vendor onboarding</t>
         </is>
       </c>
     </row>

--- a/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
+++ b/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
@@ -3723,7 +3723,7 @@
       </c>
       <c r="D13" s="44" t="inlineStr">
         <is>
-          <t>10,548 rows across 10 key tables</t>
+          <t>10,465 rows across 10 key tables</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="D28" s="43" t="n">
-        <v>544</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="E37" s="16" t="n">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="F37" s="16" t="n">
         <v>1</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="E38" s="15" t="n">
-        <v>533</v>
+        <v>490</v>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="E39" s="16" t="n">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="F39" s="16" t="n"/>
       <c r="G39" s="16" t="n"/>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="E40" s="15" t="n">
-        <v>522</v>
+        <v>480</v>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="D54" s="43" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="E63" s="16" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="F63" s="16" t="n">
         <v>1</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="E64" s="15" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="E65" s="16" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="F65" s="16" t="n"/>
       <c r="G65" s="16" t="n"/>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="E66" s="15" t="n">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="D80" s="43" t="n">
-        <v>984</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="E89" s="16" t="n">
-        <v>984</v>
+        <v>1000</v>
       </c>
       <c r="F89" s="16" t="n">
         <v>1</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="E90" s="15" t="n">
-        <v>984</v>
+        <v>1000</v>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="E91" s="16" t="n">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="F91" s="16" t="n"/>
       <c r="G91" s="16" t="n"/>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="E92" s="15" t="n">
-        <v>787</v>
+        <v>800</v>
       </c>
       <c r="F92" s="15" t="n">
         <v>0.01</v>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="E93" s="16" t="n">
-        <v>935</v>
+        <v>950</v>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="D106" s="43" t="n">
-        <v>5043</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="107" ht="21.75" customHeight="1">
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="E115" s="16" t="n">
-        <v>5043</v>
+        <v>5000</v>
       </c>
       <c r="F115" s="16" t="n">
         <v>1</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="E116" s="15" t="n">
-        <v>5043</v>
+        <v>5000</v>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="E118" s="15" t="n">
-        <v>1815</v>
+        <v>1800</v>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>1815 unique dates</t>
+          <t>1800 unique dates</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="E119" s="16" t="n">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F119" s="16" t="n">
         <v>1</v>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4841</v>
+        <v>4800</v>
       </c>
       <c r="F121" t="n">
         <v>0.01</v>
@@ -6219,7 +6219,7 @@
         </is>
       </c>
       <c r="D132" s="43" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
     </row>
     <row r="133">
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="E141" s="16" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="F141" s="16" t="n">
         <v>1</v>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="E142" s="15" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="F142" s="15" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="E143" s="16" t="n">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="F143" s="16" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="E144" s="15" t="n">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="F144" s="15" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="E145" s="16" t="n">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="F145" s="16" t="n"/>
       <c r="G145" s="16" t="n"/>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="E146" s="15" t="n">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="D158" s="43" t="n">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="159">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="E167" s="16" t="n">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="F167" s="16" t="n">
         <v>1</v>
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="E168" s="15" t="n">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="E169" s="16" t="n">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="F169" s="16" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="E171" s="16" t="n">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="F171" s="16" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="D184" s="43" t="n">
-        <v>-13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="D187" s="44" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="E193" s="16" t="n">
-        <v>-13</v>
+        <v>5</v>
       </c>
       <c r="F193" s="16" t="n">
         <v>1</v>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="E194" s="15" t="n">
-        <v>-13</v>
+        <v>5</v>
       </c>
       <c r="F194" s="15" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="E196" s="15" t="n">
-        <v>-12</v>
+        <v>5</v>
       </c>
       <c r="F196" s="15" t="n"/>
       <c r="G196" s="15" t="n"/>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="E197" s="16" t="n">
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="F197" s="16" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="D210" s="43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211">
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="E219" s="16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F219" s="16" t="n">
         <v>1</v>
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="E220" s="15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F220" s="15" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="E222" s="15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F222" s="15" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="D236" s="43" t="n">
-        <v>2482</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="237">
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="E245" s="16" t="n">
-        <v>2482</v>
+        <v>2500</v>
       </c>
       <c r="F245" s="16" t="n">
         <v>1</v>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="E246" s="15" t="n">
-        <v>2482</v>
+        <v>2500</v>
       </c>
       <c r="F246" s="15" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="E247" s="16" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F247" s="16" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="H247" s="16" t="inlineStr">
         <is>
-          <t>1588 unique dates</t>
+          <t>1600 unique dates</t>
         </is>
       </c>
       <c r="I247" s="16" t="inlineStr">
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="E248" s="15" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F248" s="15" t="n">
         <v>1</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="E249" s="16" t="n">
-        <v>2432</v>
+        <v>2450</v>
       </c>
       <c r="F249" s="16" t="n">
         <v>50</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="D262" s="43" t="n">
-        <v>828</v>
+        <v>800</v>
       </c>
     </row>
     <row r="263">
@@ -9136,7 +9136,7 @@
         </is>
       </c>
       <c r="E271" s="16" t="n">
-        <v>828</v>
+        <v>800</v>
       </c>
       <c r="F271" s="16" t="n">
         <v>1</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="E272" s="15" t="n">
-        <v>828</v>
+        <v>800</v>
       </c>
       <c r="F272" s="15" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="E273" s="16" t="n">
-        <v>778</v>
+        <v>752</v>
       </c>
       <c r="F273" s="16" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="H273" s="16" t="inlineStr">
         <is>
-          <t>778 unique dates</t>
+          <t>752 unique dates</t>
         </is>
       </c>
       <c r="I273" s="16" t="inlineStr">
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="E274" s="15" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F274" s="15" t="n">
         <v>1</v>
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="E275" s="16" t="n">
-        <v>803</v>
+        <v>776</v>
       </c>
       <c r="F275" s="16" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9500,16 +9500,16 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9570,16 +9570,16 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9605,16 +9605,16 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>Investigate load delay</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9640,16 +9640,16 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9675,7 +9675,7 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9710,16 +9710,16 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>Investigate load delay</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9745,16 +9745,16 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>Investigate load delay</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9780,16 +9780,16 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -9845,11 +9845,11 @@
     <row r="298">
       <c r="D298" t="inlineStr">
         <is>
-          <t>1. Null subsidiary_id on 101 TRANSACTION rows (2.0%)
+          <t>1. Null subsidiary_id on 100 TRANSACTION rows (2.0%)
 2. DEPARTMENT: 0 rows with null subsidiary_id (0.0%) – orphan risk
 3. No direct FK from SALESORDER to CONTRACT
-4. VENDOR: 32 rows with null email (19.8%) – enrich before CRM migration
-5. PURCHASEORDER: 17 rows with null entity_id (2.1%) – verify vendor onboarding</t>
+4. VENDOR: 40 rows with null email (20.0%) – enrich before CRM migration
+5. PURCHASEORDER: 16 rows with null entity_id (2.0%) – verify vendor onboarding</t>
         </is>
       </c>
     </row>

--- a/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
+++ b/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D29" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>2021-03-22 – 2026-03-06</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E37" s="16" t="n">
@@ -4091,11 +4091,11 @@
         <v>1</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>9999</v>
+        <v>500</v>
       </c>
       <c r="H37" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I37" s="16" t="inlineStr">
@@ -4117,30 +4117,30 @@
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E38" s="15" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Aaron Inc</t>
+          <t>Acosta, Galvan and Wood</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
         <is>
-          <t>Zurich LLC</t>
+          <t>Zuniga-Patrick</t>
         </is>
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>2% blank names</t>
+          <t>No nulls; 493 distinct value(s)</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -4157,17 +4157,25 @@
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E39" s="16" t="n">
         <v>425</v>
       </c>
-      <c r="F39" s="16" t="n"/>
-      <c r="G39" s="16" t="n"/>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>aaronadams@example.com</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>zschwartz@example.org</t>
+        </is>
+      </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>15% null – not mandatory</t>
+          <t>75 null (15.0%)</t>
         </is>
       </c>
       <c r="I39" s="16" t="inlineStr">
@@ -4189,23 +4197,27 @@
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E40" s="15" t="n">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>2020-01-03</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="inlineStr"/>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 437 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -4225,7 +4237,7 @@
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E41" s="16" t="n">
@@ -4239,12 +4251,12 @@
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>1% null – FK risk</t>
+          <t>No nulls; 5 distinct value(s)</t>
         </is>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -4319,16 +4331,16 @@
         </is>
       </c>
       <c r="E45" s="16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F45" s="16" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H45" s="16" t="inlineStr">
@@ -4340,12 +4352,12 @@
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>salesrep_id</t>
+          <t>department_id</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>EMPLOYEE</t>
+          <t>DEPARTMENT</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
@@ -4354,21 +4366,21 @@
         </is>
       </c>
       <c r="E46" s="15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4497,7 @@
       </c>
       <c r="D55" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>2021-04-02 – 2026-03-14</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4648,7 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E63" s="16" t="n">
@@ -4646,11 +4658,11 @@
         <v>1</v>
       </c>
       <c r="G63" s="16" t="n">
-        <v>9999</v>
+        <v>200</v>
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
@@ -4672,7 +4684,7 @@
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E64" s="15" t="n">
@@ -4680,15 +4692,19 @@
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>A1 Supply</t>
+          <t>Allen, Reid and Abbott</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
         <is>
-          <t>Zurich Parts</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="inlineStr"/>
+          <t>York-Perez</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -4708,17 +4724,25 @@
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="E65" s="16" t="n">
-        <v>160</v>
-      </c>
-      <c r="F65" s="16" t="n"/>
-      <c r="G65" s="16" t="n"/>
+        <v>164</v>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>abigailzhang@example.com</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>zwells@example.net</t>
+        </is>
+      </c>
       <c r="H65" s="16" t="inlineStr">
         <is>
-          <t>20% null</t>
+          <t>36 null (18.0%)</t>
         </is>
       </c>
       <c r="I65" s="16" t="inlineStr">
@@ -4740,23 +4764,27 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E66" s="15" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="inlineStr"/>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 190 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -4776,7 +4804,7 @@
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E67" s="16" t="n">
@@ -4790,12 +4818,12 @@
       </c>
       <c r="H67" s="16" t="inlineStr">
         <is>
-          <t>3% null</t>
+          <t>No nulls; 5 distinct value(s)</t>
         </is>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -4870,58 +4898,32 @@
         </is>
       </c>
       <c r="E71" s="16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F71" s="16" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H71" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>currency_id</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr">
-        <is>
-          <t>CURRENCY</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G72" s="15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H72" s="15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B72" s="15" t="n"/>
+      <c r="C72" s="15" t="n"/>
+      <c r="D72" s="15" t="n"/>
+      <c r="E72" s="15" t="n"/>
+      <c r="F72" s="15" t="n"/>
+      <c r="G72" s="15" t="n"/>
+      <c r="H72" s="15" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="16" t="n"/>
@@ -5036,7 +5038,7 @@
       </c>
       <c r="D81" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>2021-03-23 – 2026-03-22</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5189,7 @@
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E89" s="16" t="n">
@@ -5197,11 +5199,11 @@
         <v>1</v>
       </c>
       <c r="G89" s="16" t="n">
-        <v>99999</v>
+        <v>1000</v>
       </c>
       <c r="H89" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I89" s="16" t="inlineStr">
@@ -5223,7 +5225,7 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E90" s="15" t="n">
@@ -5236,12 +5238,12 @@
       </c>
       <c r="G90" s="15" t="inlineStr">
         <is>
-          <t>ITEM-9999</t>
+          <t>ITEM-1000</t>
         </is>
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Unique item code</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
@@ -5263,22 +5265,30 @@
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="E91" s="16" t="n">
-        <v>920</v>
-      </c>
-      <c r="F91" s="16" t="n"/>
-      <c r="G91" s="16" t="n"/>
+        <v>927</v>
+      </c>
+      <c r="F91" s="16" t="inlineStr">
+        <is>
+          <t>Adaptive 24/7 moratorium</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>Visionary zero administration matrices</t>
+        </is>
+      </c>
       <c r="H91" s="16" t="inlineStr">
         <is>
-          <t>8% null descriptions</t>
+          <t>73 null (7.3%)</t>
         </is>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -5295,26 +5305,26 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="E92" s="15" t="n">
-        <v>800</v>
+        <v>944</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>0.01</v>
+        <v>42.57</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>99999.99000000001</v>
+        <v>9991.610000000001</v>
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>5% null – check item type</t>
+          <t>56 null (5.6%)</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -5331,23 +5341,27 @@
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E93" s="16" t="n">
-        <v>950</v>
+        <v>767</v>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="G93" s="16" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="H93" s="16" t="inlineStr"/>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="H93" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 767 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -5460,16 +5474,16 @@
         </is>
       </c>
       <c r="E98" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
@@ -5591,7 +5605,7 @@
       </c>
       <c r="D107" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>2021-03-22 – 2026-03-22</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5756,7 @@
       </c>
       <c r="D115" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E115" s="16" t="n">
@@ -5752,11 +5766,11 @@
         <v>1</v>
       </c>
       <c r="G115" s="16" t="n">
-        <v>99999</v>
+        <v>5000</v>
       </c>
       <c r="H115" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I115" s="16" t="inlineStr">
@@ -5778,7 +5792,7 @@
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -5786,17 +5800,17 @@
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>TRN-00001</t>
+          <t>TRAN-00001</t>
         </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>TRN-09999</t>
+          <t>TRAN-05000</t>
         </is>
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Unique transaction reference</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
@@ -5808,7 +5822,7 @@
     <row r="117" ht="18" customHeight="1">
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>recordtype</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C117" s="16" t="inlineStr">
@@ -5818,25 +5832,25 @@
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E117" s="16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F117" s="16" t="inlineStr">
         <is>
-          <t>invoice</t>
+          <t>CreditMemo</t>
         </is>
       </c>
       <c r="G117" s="16" t="inlineStr">
         <is>
-          <t>vendorbill</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="H117" s="16" t="inlineStr">
         <is>
-          <t>8 distinct types</t>
+          <t>No nulls; 4 distinct value(s)</t>
         </is>
       </c>
       <c r="I117" s="16" t="inlineStr">
@@ -5858,25 +5872,25 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
-        <v>1800</v>
+        <v>1697</v>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>2020-01-02</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>1800 unique dates</t>
+          <t>No nulls; 1697 distinct value(s)</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
@@ -5888,7 +5902,7 @@
     <row r="119" ht="18" customHeight="1">
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>entity_id</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="C119" s="16" t="inlineStr">
@@ -5898,7 +5912,7 @@
       </c>
       <c r="D119" s="16" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E119" s="16" t="n">
@@ -5908,16 +5922,16 @@
         <v>1</v>
       </c>
       <c r="G119" s="16" t="n">
-        <v>9999</v>
+        <v>500</v>
       </c>
       <c r="H119" s="16" t="inlineStr">
         <is>
-          <t>2% null – FK risk</t>
+          <t>No nulls; 500 distinct value(s)</t>
         </is>
       </c>
       <c r="I119" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5948,7 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -5948,12 +5962,12 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>2% null – known issue</t>
+          <t>No nulls; 5 distinct value(s)</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -5970,19 +5984,23 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4800</v>
+        <v>4998</v>
       </c>
       <c r="F121" t="n">
-        <v>0.01</v>
+        <v>104.26</v>
       </c>
       <c r="G121" t="n">
-        <v>999999.99</v>
-      </c>
-      <c r="H121" t="inlineStr"/>
+        <v>49990.84</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>No nulls; 4998 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -6029,7 +6047,7 @@
     <row r="123" ht="19.5" customHeight="1">
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>entity_id</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="C123" s="16" t="inlineStr">
@@ -6043,21 +6061,21 @@
         </is>
       </c>
       <c r="E123" s="16" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F123" s="16" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G123" s="16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H123" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -6078,21 +6096,21 @@
         </is>
       </c>
       <c r="E124" s="15" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G124" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -6113,16 +6131,16 @@
         </is>
       </c>
       <c r="E125" s="16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F125" s="16" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G125" s="16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H125" s="16" t="inlineStr">
@@ -6235,7 +6253,7 @@
       </c>
       <c r="D133" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>2021-03-31 – 2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6404,7 @@
       </c>
       <c r="D141" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E141" s="16" t="n">
@@ -6396,11 +6414,11 @@
         <v>1</v>
       </c>
       <c r="G141" s="16" t="n">
-        <v>9999</v>
+        <v>150</v>
       </c>
       <c r="H141" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I141" s="16" t="inlineStr">
@@ -6422,7 +6440,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -6430,17 +6448,17 @@
       </c>
       <c r="F142" s="15" t="inlineStr">
         <is>
-          <t>EMP-001</t>
+          <t>EMP-0001</t>
         </is>
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>EMP-150</t>
+          <t>EMP-0150</t>
         </is>
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Unique employee code</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
@@ -6462,23 +6480,27 @@
       </c>
       <c r="D143" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E143" s="16" t="n">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="F143" s="16" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Alejandra</t>
         </is>
       </c>
       <c r="G143" s="16" t="inlineStr">
         <is>
-          <t>Zoe</t>
-        </is>
-      </c>
-      <c r="H143" s="16" t="inlineStr"/>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="H143" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 104 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I143" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -6498,11 +6520,11 @@
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="F144" s="15" t="inlineStr">
         <is>
@@ -6511,10 +6533,14 @@
       </c>
       <c r="G144" s="15" t="inlineStr">
         <is>
-          <t>Young</t>
-        </is>
-      </c>
-      <c r="H144" s="15" t="inlineStr"/>
+          <t>Zuniga</t>
+        </is>
+      </c>
+      <c r="H144" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 137 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -6534,17 +6560,25 @@
       </c>
       <c r="D145" s="16" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="E145" s="16" t="n">
-        <v>142</v>
-      </c>
-      <c r="F145" s="16" t="n"/>
-      <c r="G145" s="16" t="n"/>
+        <v>128</v>
+      </c>
+      <c r="F145" s="16" t="inlineStr">
+        <is>
+          <t>aaron97@example.com</t>
+        </is>
+      </c>
+      <c r="G145" s="16" t="inlineStr">
+        <is>
+          <t>zpatterson@example.org</t>
+        </is>
+      </c>
       <c r="H145" s="16" t="inlineStr">
         <is>
-          <t>5% null</t>
+          <t>22 null (14.7%)</t>
         </is>
       </c>
       <c r="I145" s="16" t="inlineStr">
@@ -6556,33 +6590,37 @@
     <row r="146">
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>hiredate</t>
+          <t>datecreated</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
-          <t>2015-01-15</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="G146" s="15" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="H146" s="15" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 147 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -6602,7 +6640,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -6616,7 +6654,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>1% null</t>
+          <t>No nulls; 5 distinct value(s)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6679,16 +6717,16 @@
         </is>
       </c>
       <c r="E149" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F149" s="16" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G149" s="16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H149" s="16" t="inlineStr">
@@ -6845,7 +6883,7 @@
       </c>
       <c r="D159" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -6996,7 +7034,7 @@
       </c>
       <c r="D167" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E167" s="16" t="n">
@@ -7006,11 +7044,11 @@
         <v>1</v>
       </c>
       <c r="G167" s="16" t="n">
-        <v>9999</v>
+        <v>300</v>
       </c>
       <c r="H167" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I167" s="16" t="inlineStr">
@@ -7032,7 +7070,7 @@
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -7040,17 +7078,17 @@
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Unique account number</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
@@ -7072,23 +7110,27 @@
       </c>
       <c r="D169" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E169" s="16" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F169" s="16" t="inlineStr">
         <is>
-          <t>Accounts Pay</t>
+          <t>Aggregate B2C Roi</t>
         </is>
       </c>
       <c r="G169" s="16" t="inlineStr">
         <is>
-          <t>Wages Exp</t>
-        </is>
-      </c>
-      <c r="H169" s="16" t="inlineStr"/>
+          <t>Whiteboard Vertical Channels</t>
+        </is>
+      </c>
+      <c r="H169" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 299 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I169" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -7098,7 +7140,7 @@
     <row r="170">
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>accttype</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
@@ -7108,25 +7150,25 @@
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F170" s="15" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>OtherExpense</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>12 account types</t>
+          <t>No nulls; 5 distinct value(s)</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
@@ -7138,33 +7180,33 @@
     <row r="171">
       <c r="B171" s="16" t="inlineStr">
         <is>
-          <t>lastmodifieddate</t>
+          <t>subsidiary_id</t>
         </is>
       </c>
       <c r="C171" s="16" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D171" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E171" s="16" t="n">
-        <v>279</v>
-      </c>
-      <c r="F171" s="16" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="G171" s="16" t="inlineStr">
-        <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="H171" s="16" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="F171" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H171" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 5 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I171" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -7382,7 +7424,7 @@
       </c>
       <c r="D185" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7575,7 @@
       </c>
       <c r="D193" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E193" s="16" t="n">
@@ -7543,11 +7585,11 @@
         <v>1</v>
       </c>
       <c r="G193" s="16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H193" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I193" s="16" t="inlineStr">
@@ -7569,7 +7611,7 @@
       </c>
       <c r="D194" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E194" s="15" t="n">
@@ -7577,15 +7619,19 @@
       </c>
       <c r="F194" s="15" t="inlineStr">
         <is>
-          <t>Acme AU</t>
+          <t>Subsidiary 1</t>
         </is>
       </c>
       <c r="G194" s="15" t="inlineStr">
         <is>
-          <t>Zurich SA</t>
-        </is>
-      </c>
-      <c r="H194" s="15" t="inlineStr"/>
+          <t>Subsidiary 5</t>
+        </is>
+      </c>
+      <c r="H194" s="15" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
       <c r="I194" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -7593,112 +7639,34 @@
       </c>
     </row>
     <row r="195">
-      <c r="B195" s="16" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="C195" s="16" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D195" s="16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E195" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F195" s="16" t="inlineStr">
-        <is>
-          <t>AUD</t>
-        </is>
-      </c>
-      <c r="G195" s="16" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H195" s="16" t="inlineStr">
-        <is>
-          <t>6 currencies</t>
-        </is>
-      </c>
-      <c r="I195" s="16" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B195" s="16" t="n"/>
+      <c r="C195" s="16" t="n"/>
+      <c r="D195" s="16" t="n"/>
+      <c r="E195" s="16" t="n"/>
+      <c r="F195" s="16" t="n"/>
+      <c r="G195" s="16" t="n"/>
+      <c r="H195" s="16" t="n"/>
+      <c r="I195" s="16" t="n"/>
     </row>
     <row r="196">
-      <c r="B196" s="15" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="C196" s="15" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D196" s="15" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="E196" s="15" t="n">
-        <v>5</v>
-      </c>
+      <c r="B196" s="15" t="n"/>
+      <c r="C196" s="15" t="n"/>
+      <c r="D196" s="15" t="n"/>
+      <c r="E196" s="15" t="n"/>
       <c r="F196" s="15" t="n"/>
       <c r="G196" s="15" t="n"/>
-      <c r="H196" s="15" t="inlineStr">
-        <is>
-          <t>5% null country</t>
-        </is>
-      </c>
-      <c r="I196" s="15" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
+      <c r="H196" s="15" t="n"/>
+      <c r="I196" s="15" t="n"/>
     </row>
     <row r="197">
-      <c r="B197" s="16" t="inlineStr">
-        <is>
-          <t>lastmodifieddate</t>
-        </is>
-      </c>
-      <c r="C197" s="16" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="D197" s="16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E197" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F197" s="16" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="G197" s="16" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="H197" s="16" t="inlineStr"/>
-      <c r="I197" s="16" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B197" s="16" t="n"/>
+      <c r="C197" s="16" t="n"/>
+      <c r="D197" s="16" t="n"/>
+      <c r="E197" s="16" t="n"/>
+      <c r="F197" s="16" t="n"/>
+      <c r="G197" s="16" t="n"/>
+      <c r="H197" s="16" t="n"/>
+      <c r="I197" s="16" t="n"/>
     </row>
     <row r="198">
       <c r="B198" s="15" t="n"/>
@@ -7885,7 +7853,7 @@
       </c>
       <c r="D211" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8004,7 @@
       </c>
       <c r="D219" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E219" s="16" t="n">
@@ -8046,11 +8014,11 @@
         <v>1</v>
       </c>
       <c r="G219" s="16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H219" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I219" s="16" t="inlineStr">
@@ -8072,7 +8040,7 @@
       </c>
       <c r="D220" s="15" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E220" s="15" t="n">
@@ -8080,22 +8048,22 @@
       </c>
       <c r="F220" s="15" t="inlineStr">
         <is>
-          <t>Accounts</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G220" s="15" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="H220" s="15" t="inlineStr">
         <is>
-          <t>2% null names</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I220" s="15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -8112,11 +8080,11 @@
       </c>
       <c r="D221" s="16" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E221" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F221" s="16" t="n">
         <v>1</v>
@@ -8126,50 +8094,24 @@
       </c>
       <c r="H221" s="16" t="inlineStr">
         <is>
-          <t>4% null – orphan risk</t>
+          <t>No nulls; 4 distinct value(s)</t>
         </is>
       </c>
       <c r="I221" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="B222" s="15" t="inlineStr">
-        <is>
-          <t>lastmodifieddate</t>
-        </is>
-      </c>
-      <c r="C222" s="15" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="D222" s="15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E222" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="F222" s="15" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="G222" s="15" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="H222" s="15" t="inlineStr"/>
-      <c r="I222" s="15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B222" s="15" t="n"/>
+      <c r="C222" s="15" t="n"/>
+      <c r="D222" s="15" t="n"/>
+      <c r="E222" s="15" t="n"/>
+      <c r="F222" s="15" t="n"/>
+      <c r="G222" s="15" t="n"/>
+      <c r="H222" s="15" t="n"/>
+      <c r="I222" s="15" t="n"/>
     </row>
     <row r="223">
       <c r="B223" s="16" t="n"/>
@@ -8252,21 +8194,21 @@
         </is>
       </c>
       <c r="E227" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F227" s="16" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G227" s="16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H227" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8334,7 @@
       </c>
       <c r="D237" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>2021-03-22 – 2026-03-22</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8485,7 @@
       </c>
       <c r="D245" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E245" s="16" t="n">
@@ -8553,11 +8495,11 @@
         <v>1</v>
       </c>
       <c r="G245" s="16" t="n">
-        <v>99999</v>
+        <v>2500</v>
       </c>
       <c r="H245" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I245" s="16" t="inlineStr">
@@ -8579,7 +8521,7 @@
       </c>
       <c r="D246" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E246" s="15" t="n">
@@ -8592,12 +8534,12 @@
       </c>
       <c r="G246" s="15" t="inlineStr">
         <is>
-          <t>SO-09999</t>
+          <t>SO-02500</t>
         </is>
       </c>
       <c r="H246" s="15" t="inlineStr">
         <is>
-          <t>Unique order reference</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I246" s="15" t="inlineStr">
@@ -8619,25 +8561,25 @@
       </c>
       <c r="D247" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E247" s="16" t="n">
-        <v>1600</v>
+        <v>1381</v>
       </c>
       <c r="F247" s="16" t="inlineStr">
         <is>
-          <t>2020-01-03</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="G247" s="16" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H247" s="16" t="inlineStr">
         <is>
-          <t>1600 unique dates</t>
+          <t>No nulls; 1381 distinct value(s)</t>
         </is>
       </c>
       <c r="I247" s="16" t="inlineStr">
@@ -8649,7 +8591,7 @@
     <row r="248">
       <c r="B248" s="15" t="inlineStr">
         <is>
-          <t>entity_id</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="C248" s="15" t="inlineStr">
@@ -8659,26 +8601,26 @@
       </c>
       <c r="D248" s="15" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E248" s="15" t="n">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F248" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G248" s="15" t="n">
-        <v>9999</v>
+        <v>500</v>
       </c>
       <c r="H248" s="15" t="inlineStr">
         <is>
-          <t>1% null – FK to CUSTOMER</t>
+          <t>No nulls; 497 distinct value(s)</t>
         </is>
       </c>
       <c r="I248" s="15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -8695,19 +8637,23 @@
       </c>
       <c r="D249" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E249" s="16" t="n">
-        <v>2450</v>
+        <v>2499</v>
       </c>
       <c r="F249" s="16" t="n">
-        <v>50</v>
+        <v>510.55</v>
       </c>
       <c r="G249" s="16" t="n">
-        <v>99999.99000000001</v>
-      </c>
-      <c r="H249" s="16" t="inlineStr"/>
+        <v>99989.25999999999</v>
+      </c>
+      <c r="H249" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 2499 distinct value(s)</t>
+        </is>
+      </c>
       <c r="I249" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
@@ -8727,25 +8673,25 @@
       </c>
       <c r="D250" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E250" s="15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F250" s="15" t="inlineStr">
         <is>
-          <t>Billed</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="G250" s="15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Pending Fulfillment</t>
         </is>
       </c>
       <c r="H250" s="15" t="inlineStr">
         <is>
-          <t>6 order statuses</t>
+          <t>No nulls; 3 distinct value(s)</t>
         </is>
       </c>
       <c r="I250" s="15" t="inlineStr">
@@ -8801,7 +8747,7 @@
     <row r="253">
       <c r="B253" s="16" t="inlineStr">
         <is>
-          <t>entity_id</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="C253" s="16" t="inlineStr">
@@ -8815,16 +8761,16 @@
         </is>
       </c>
       <c r="E253" s="16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F253" s="16" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G253" s="16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H253" s="16" t="inlineStr">
@@ -8850,16 +8796,16 @@
         </is>
       </c>
       <c r="E254" s="15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F254" s="15" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G254" s="15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H254" s="15" t="inlineStr">
@@ -8981,7 +8927,7 @@
       </c>
       <c r="D263" s="44" t="inlineStr">
         <is>
-          <t>2020-01-01 – 2025-03-01</t>
+          <t>2021-03-23 – 2026-03-21</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9078,7 @@
       </c>
       <c r="D271" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E271" s="16" t="n">
@@ -9142,11 +9088,11 @@
         <v>1</v>
       </c>
       <c r="G271" s="16" t="n">
-        <v>9999</v>
+        <v>800</v>
       </c>
       <c r="H271" s="16" t="inlineStr">
         <is>
-          <t>PK – no nulls, no duplicates</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I271" s="16" t="inlineStr">
@@ -9168,7 +9114,7 @@
       </c>
       <c r="D272" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E272" s="15" t="n">
@@ -9181,12 +9127,12 @@
       </c>
       <c r="G272" s="15" t="inlineStr">
         <is>
-          <t>PO-03999</t>
+          <t>PO-00800</t>
         </is>
       </c>
       <c r="H272" s="15" t="inlineStr">
         <is>
-          <t>Unique PO reference</t>
+          <t>No nulls, no duplicates</t>
         </is>
       </c>
       <c r="I272" s="15" t="inlineStr">
@@ -9208,25 +9154,25 @@
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E273" s="16" t="n">
-        <v>752</v>
+        <v>654</v>
       </c>
       <c r="F273" s="16" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="G273" s="16" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="H273" s="16" t="inlineStr">
         <is>
-          <t>752 unique dates</t>
+          <t>No nulls; 654 distinct value(s)</t>
         </is>
       </c>
       <c r="I273" s="16" t="inlineStr">
@@ -9238,7 +9184,7 @@
     <row r="274">
       <c r="B274" s="15" t="inlineStr">
         <is>
-          <t>entity_id</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="C274" s="15" t="inlineStr">
@@ -9248,26 +9194,26 @@
       </c>
       <c r="D274" s="15" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E274" s="15" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F274" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G274" s="15" t="n">
-        <v>9999</v>
+        <v>200</v>
       </c>
       <c r="H274" s="15" t="inlineStr">
         <is>
-          <t>2% null – FK to VENDOR</t>
+          <t>No nulls; 194 distinct value(s)</t>
         </is>
       </c>
       <c r="I274" s="15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -9284,26 +9230,26 @@
       </c>
       <c r="D275" s="16" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E275" s="16" t="n">
-        <v>776</v>
+        <v>799</v>
       </c>
       <c r="F275" s="16" t="n">
-        <v>10</v>
+        <v>253.05</v>
       </c>
       <c r="G275" s="16" t="n">
-        <v>49999.99</v>
+        <v>49872.73</v>
       </c>
       <c r="H275" s="16" t="inlineStr">
         <is>
-          <t>1% null amounts</t>
+          <t>No nulls; 799 distinct value(s)</t>
         </is>
       </c>
       <c r="I275" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -9320,25 +9266,25 @@
       </c>
       <c r="D276" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E276" s="15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F276" s="15" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="G276" s="15" t="inlineStr">
         <is>
-          <t>PendingReceipt</t>
+          <t>Pending Receipt</t>
         </is>
       </c>
       <c r="H276" s="15" t="inlineStr">
         <is>
-          <t>5 statuses</t>
+          <t>No nulls; 3 distinct value(s)</t>
         </is>
       </c>
       <c r="I276" s="15" t="inlineStr">
@@ -9394,7 +9340,7 @@
     <row r="279">
       <c r="B279" s="16" t="inlineStr">
         <is>
-          <t>entity_id</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="C279" s="16" t="inlineStr">
@@ -9408,21 +9354,21 @@
         </is>
       </c>
       <c r="E279" s="16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F279" s="16" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G279" s="16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H279" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -9443,16 +9389,16 @@
         </is>
       </c>
       <c r="E280" s="15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F280" s="15" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G280" s="15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H280" s="15" t="inlineStr">
@@ -9491,25 +9437,25 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>17-day lag – investigate</t>
         </is>
       </c>
     </row>
@@ -9526,16 +9472,16 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F286" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -9544,7 +9490,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>9-day lag – investigate</t>
         </is>
       </c>
     </row>
@@ -9561,16 +9507,16 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F287" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -9596,25 +9542,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F288" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -9631,25 +9577,25 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F289" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>7-day lag – investigate</t>
         </is>
       </c>
     </row>
@@ -9666,25 +9612,27 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="F290" t="n">
-        <v>3</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Within SLA</t>
+          <t>No date column</t>
         </is>
       </c>
     </row>
@@ -9701,25 +9649,27 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="F291" t="n">
-        <v>6</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>No date column</t>
         </is>
       </c>
     </row>
@@ -9736,25 +9686,27 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="F292" t="n">
-        <v>4</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>No date column</t>
         </is>
       </c>
     </row>
@@ -9771,12 +9723,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -9806,25 +9758,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F294" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Investigate load delay</t>
+          <t>Within SLA</t>
         </is>
       </c>
     </row>
@@ -9845,11 +9797,11 @@
     <row r="298">
       <c r="D298" t="inlineStr">
         <is>
-          <t>1. Null subsidiary_id on 100 TRANSACTION rows (2.0%)
-2. DEPARTMENT: 0 rows with null subsidiary_id (0.0%) – orphan risk
-3. No direct FK from SALESORDER to CONTRACT
-4. VENDOR: 40 rows with null email (20.0%) – enrich before CRM migration
-5. PURCHASEORDER: 16 rows with null entity_id (2.0%) – verify vendor onboarding</t>
+          <t>1. CUSTOMER email: 75 null (15.0%)
+2. VENDOR email: 36 null (18.0%)
+3. EMPLOYEE email: 22 null (14.7%)
+4. ITEM salesdescription: 73 null (7.3%)
+5. ITEM rate: 56 null (5.6%)</t>
         </is>
       </c>
     </row>

--- a/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
+++ b/output/TFG_DataProfiling_Template_NetSuite_Filled.xlsx
@@ -3554,7 +3554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L303"/>
+  <dimension ref="A2:L357"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="D13" s="44" t="inlineStr">
         <is>
-          <t>10,465 rows across 10 key tables</t>
+          <t>20,485 rows across 10 key tables</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D29" s="44" t="inlineStr">
         <is>
-          <t>2021-03-22 – 2026-03-06</t>
+          <t>2021-03-28 – 2026-03-22</t>
         </is>
       </c>
     </row>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E38" s="15" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Acosta, Galvan and Wood</t>
+          <t>Acevedo Ltd</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
         <is>
-          <t>Zuniga-Patrick</t>
+          <t>Zimmerman-Meyer</t>
         </is>
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>No nulls; 493 distinct value(s)</t>
+          <t>No nulls; 496 distinct value(s)</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
@@ -4161,16 +4161,16 @@
         </is>
       </c>
       <c r="E39" s="16" t="n">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
-          <t>aaronadams@example.com</t>
+          <t>aarmstrong@example.net</t>
         </is>
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>zschwartz@example.org</t>
+          <t>zmorrison@example.com</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
@@ -4187,12 +4187,12 @@
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>datecreated</t>
+          <t>location_id</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
@@ -4201,21 +4201,17 @@
         </is>
       </c>
       <c r="E40" s="15" t="n">
-        <v>437</v>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>2021-03-22</t>
-        </is>
-      </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>No nulls; 437 distinct value(s)</t>
+          <t>No nulls; 20 distinct value(s)</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
@@ -4261,19 +4257,82 @@
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="15" t="n"/>
-      <c r="E42" s="15" t="n"/>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
-      <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>datecreated</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>433</v>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>2021-03-28</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 433 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="49" t="inlineStr">
         <is>
-          <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
+          <t>contract_ref</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>30.4%</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>339</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CTR-1018</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CTR-9998</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>152 null (30.4%)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>RED</t>
         </is>
       </c>
     </row>
@@ -4317,12 +4376,12 @@
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>subsidiary_id</t>
+          <t>location_id</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>SUBSIDIARY</t>
+          <t>LOCATION</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
@@ -4352,12 +4411,12 @@
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>department_id</t>
+          <t>subsidiary_id</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>DEPARTMENT</t>
+          <t>SUBSIDIARY</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
@@ -4385,13 +4444,39 @@
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="16" t="n"/>
-      <c r="H47" s="16" t="n"/>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>department_id</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="7.5" customHeight="1"/>
     <row r="49" ht="18" customHeight="1">
@@ -4497,7 +4582,7 @@
       </c>
       <c r="D55" s="44" t="inlineStr">
         <is>
-          <t>2021-04-02 – 2026-03-14</t>
+          <t>2021-03-26 – 2026-03-13</t>
         </is>
       </c>
     </row>
@@ -4688,21 +4773,21 @@
         </is>
       </c>
       <c r="E64" s="15" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>Allen, Reid and Abbott</t>
+          <t>Adams-Anderson</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
         <is>
-          <t>York-Perez</t>
+          <t>Young PLC</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>No nulls, no duplicates</t>
+          <t>No nulls; 196 distinct value(s)</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
@@ -4728,16 +4813,16 @@
         </is>
       </c>
       <c r="E65" s="16" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>abigailzhang@example.com</t>
+          <t>alvaradorobert@example.com</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>zwells@example.net</t>
+          <t>zwaller@example.net</t>
         </is>
       </c>
       <c r="H65" s="16" t="inlineStr">
@@ -4768,21 +4853,21 @@
         </is>
       </c>
       <c r="E66" s="15" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>No nulls; 190 distinct value(s)</t>
+          <t>No nulls; 183 distinct value(s)</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
@@ -5038,7 +5123,7 @@
       </c>
       <c r="D81" s="44" t="inlineStr">
         <is>
-          <t>2021-03-23 – 2026-03-22</t>
+          <t>2021-03-22 – 2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5269,16 +5354,16 @@
         </is>
       </c>
       <c r="E91" s="16" t="n">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F91" s="16" t="inlineStr">
         <is>
-          <t>Adaptive 24/7 moratorium</t>
+          <t>Adaptive client-driven complexity</t>
         </is>
       </c>
       <c r="G91" s="16" t="inlineStr">
         <is>
-          <t>Visionary zero administration matrices</t>
+          <t>Visionary regional middleware</t>
         </is>
       </c>
       <c r="H91" s="16" t="inlineStr">
@@ -5295,31 +5380,35 @@
     <row r="92" ht="18" customHeight="1">
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>rate</t>
+          <t>itemtype</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>DECIMAL</t>
+          <t>VARCHAR</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E92" s="15" t="n">
-        <v>944</v>
-      </c>
-      <c r="F92" s="15" t="n">
-        <v>42.57</v>
-      </c>
-      <c r="G92" s="15" t="n">
-        <v>9991.610000000001</v>
+        <v>3</v>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>InvtPart</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>56 null (5.6%)</t>
+          <t>No nulls; 3 distinct value(s)</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
@@ -5331,52 +5420,78 @@
     <row r="93" ht="18" customHeight="1">
       <c r="B93" s="16" t="inlineStr">
         <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>DECIMAL</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>944</v>
+      </c>
+      <c r="F93" s="16" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="G93" s="16" t="n">
+        <v>9991.610000000001</v>
+      </c>
+      <c r="H93" s="16" t="inlineStr">
+        <is>
+          <t>56 null (5.6%)</t>
+        </is>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="B94" s="15" t="inlineStr">
+        <is>
           <t>lastmodifieddate</t>
         </is>
       </c>
-      <c r="C93" s="16" t="inlineStr">
+      <c r="C94" s="15" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="D93" s="16" t="inlineStr">
+      <c r="D94" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="E93" s="16" t="n">
-        <v>767</v>
-      </c>
-      <c r="F93" s="16" t="inlineStr">
-        <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="G93" s="16" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="H93" s="16" t="inlineStr">
-        <is>
-          <t>No nulls; 767 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
+      <c r="E94" s="15" t="n">
+        <v>763</v>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>2021-03-22</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 763 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="B94" s="15" t="n"/>
-      <c r="C94" s="15" t="n"/>
-      <c r="D94" s="15" t="n"/>
-      <c r="E94" s="15" t="n"/>
-      <c r="F94" s="15" t="n"/>
-      <c r="G94" s="15" t="n"/>
-      <c r="H94" s="15" t="n"/>
-      <c r="I94" s="15" t="n"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="B95" s="49" t="inlineStr">
@@ -5556,7 +5671,7 @@
       </c>
       <c r="D104" s="43" t="inlineStr">
         <is>
-          <t>Records all financial transactions (invoices, payments, journals)</t>
+          <t>All transaction headers: WorkOrd, Invoice, Payment, Journal, CreditMemo. createdfrom links child transactions (e.g. Invoice) to source (e.g. WorkOrd).</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5788,7 @@
       </c>
       <c r="D111" s="44" t="inlineStr">
         <is>
-          <t>TRANSACTION, INVOICE, JOURNAL_ENTRY</t>
+          <t>TRANSACTION, WORKORDER, INVOICE, JOURNAL_ENTRY</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5951,7 @@
         </is>
       </c>
       <c r="E117" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F117" s="16" t="inlineStr">
         <is>
@@ -5845,12 +5960,12 @@
       </c>
       <c r="G117" s="16" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>WorkOrd</t>
         </is>
       </c>
       <c r="H117" s="16" t="inlineStr">
         <is>
-          <t>No nulls; 4 distinct value(s)</t>
+          <t>No nulls; 5 distinct value(s)</t>
         </is>
       </c>
       <c r="I117" s="16" t="inlineStr">
@@ -5876,7 +5991,7 @@
         </is>
       </c>
       <c r="E118" s="15" t="n">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -5890,7 +6005,7 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>No nulls; 1697 distinct value(s)</t>
+          <t>No nulls; 1706 distinct value(s)</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
@@ -5988,17 +6103,17 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4998</v>
+        <v>4997</v>
       </c>
       <c r="F121" t="n">
-        <v>104.26</v>
+        <v>123.48</v>
       </c>
       <c r="G121" t="n">
-        <v>49990.84</v>
+        <v>49999.44</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>No nulls; 4998 distinct value(s)</t>
+          <t>No nulls; 4997 distinct value(s)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6010,37 +6125,36 @@
     <row r="122" ht="15.75" customHeight="1">
       <c r="B122" s="45" t="inlineStr">
         <is>
-          <t>FK Field</t>
+          <t>createdfrom</t>
         </is>
       </c>
       <c r="C122" s="45" t="inlineStr">
         <is>
-          <t>References Table</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D122" s="45" t="inlineStr">
         <is>
-          <t>References Field</t>
-        </is>
-      </c>
-      <c r="E122" s="45" t="inlineStr">
-        <is>
-          <t>Orphan Row Count</t>
-        </is>
-      </c>
-      <c r="F122" s="45" t="inlineStr">
-        <is>
-          <t>Orphan %</t>
-        </is>
-      </c>
-      <c r="G122" s="45" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
+          <t>78.5%</t>
+        </is>
+      </c>
+      <c r="E122" s="45" t="n">
+        <v>659</v>
+      </c>
+      <c r="F122" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" s="45" t="n">
+        <v>1000</v>
       </c>
       <c r="H122" s="45" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>3927 null (78.5%)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>RED</t>
         </is>
       </c>
     </row>
@@ -6078,6 +6192,11 @@
           <t>GREEN</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="B124" s="15" t="inlineStr">
@@ -6149,11 +6268,45 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="30" customHeight="1"/>
+    <row r="126" ht="30" customHeight="1">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>createdfrom</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>TRANSACTION</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
     <row r="127" ht="30" customHeight="1">
       <c r="B127" s="47" t="inlineStr">
         <is>
-          <t>Table 5: EMPLOYEE</t>
+          <t>Table 5: TRANSACTIONLINE</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6340,7 @@
       </c>
       <c r="D129" s="44" t="inlineStr">
         <is>
-          <t>EMPLOYEE</t>
+          <t>TRANSACTIONLINE</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6357,7 @@
       </c>
       <c r="D130" s="43" t="inlineStr">
         <is>
-          <t>HR employee master used for approvals and assignments</t>
+          <t>Line-level detail per transaction. employee_id populated for Service (labour) lines; NULL for material/non-labour lines.</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6374,7 @@
       </c>
       <c r="D131" s="44" t="inlineStr">
         <is>
-          <t>One row = one employee</t>
+          <t>One row = one transaction line</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6390,7 @@
         </is>
       </c>
       <c r="D132" s="43" t="n">
-        <v>150</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="133">
@@ -6253,7 +6406,7 @@
       </c>
       <c r="D133" s="44" t="inlineStr">
         <is>
-          <t>2021-03-31 – 2026-03-16</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6457,7 @@
       </c>
       <c r="D136" s="43" t="inlineStr">
         <is>
-          <t>D3 – Workforce</t>
+          <t>D5 – Financials</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6474,7 @@
       </c>
       <c r="D137" s="44" t="inlineStr">
         <is>
-          <t>EMPLOYEE</t>
+          <t>TRANSACTION_LINE</t>
         </is>
       </c>
     </row>
@@ -6408,13 +6561,13 @@
         </is>
       </c>
       <c r="E141" s="16" t="n">
-        <v>150</v>
+        <v>10000</v>
       </c>
       <c r="F141" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="16" t="n">
-        <v>150</v>
+        <v>10000</v>
       </c>
       <c r="H141" s="16" t="inlineStr">
         <is>
@@ -6430,12 +6583,12 @@
     <row r="142">
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>entityid</t>
+          <t>transaction_id</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
@@ -6444,21 +6597,17 @@
         </is>
       </c>
       <c r="E142" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="F142" s="15" t="inlineStr">
-        <is>
-          <t>EMP-0001</t>
-        </is>
-      </c>
-      <c r="G142" s="15" t="inlineStr">
-        <is>
-          <t>EMP-0150</t>
-        </is>
+        <v>5000</v>
+      </c>
+      <c r="F142" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="15" t="n">
+        <v>5000</v>
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>No nulls, no duplicates</t>
+          <t>No nulls; 5000 distinct value(s)</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
@@ -6470,12 +6619,12 @@
     <row r="143">
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>firstname</t>
+          <t>line</t>
         </is>
       </c>
       <c r="C143" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D143" s="16" t="inlineStr">
@@ -6484,21 +6633,17 @@
         </is>
       </c>
       <c r="E143" s="16" t="n">
-        <v>104</v>
-      </c>
-      <c r="F143" s="16" t="inlineStr">
-        <is>
-          <t>Alejandra</t>
-        </is>
-      </c>
-      <c r="G143" s="16" t="inlineStr">
-        <is>
-          <t>William</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F143" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="H143" s="16" t="inlineStr">
         <is>
-          <t>No nulls; 104 distinct value(s)</t>
+          <t>No nulls; 2 distinct value(s)</t>
         </is>
       </c>
       <c r="I143" s="16" t="inlineStr">
@@ -6510,12 +6655,12 @@
     <row r="144">
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>lastname</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
@@ -6524,21 +6669,17 @@
         </is>
       </c>
       <c r="E144" s="15" t="n">
-        <v>137</v>
-      </c>
-      <c r="F144" s="15" t="inlineStr">
-        <is>
-          <t>Adams</t>
-        </is>
-      </c>
-      <c r="G144" s="15" t="inlineStr">
-        <is>
-          <t>Zuniga</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="F144" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="15" t="n">
+        <v>1000</v>
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>No nulls; 137 distinct value(s)</t>
+          <t>No nulls; 1000 distinct value(s)</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr">
@@ -6550,52 +6691,48 @@
     <row r="145">
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C145" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="D145" s="16" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E145" s="16" t="n">
-        <v>128</v>
-      </c>
-      <c r="F145" s="16" t="inlineStr">
-        <is>
-          <t>aaron97@example.com</t>
-        </is>
-      </c>
-      <c r="G145" s="16" t="inlineStr">
-        <is>
-          <t>zpatterson@example.org</t>
-        </is>
+        <v>4259</v>
+      </c>
+      <c r="F145" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="H145" s="16" t="inlineStr">
         <is>
-          <t>22 null (14.7%)</t>
+          <t>No nulls; 4259 distinct value(s)</t>
         </is>
       </c>
       <c r="I145" s="16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>datecreated</t>
+          <t>rate</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
@@ -6604,21 +6741,17 @@
         </is>
       </c>
       <c r="E146" s="15" t="n">
-        <v>147</v>
-      </c>
-      <c r="F146" s="15" t="inlineStr">
-        <is>
-          <t>2021-03-31</t>
-        </is>
-      </c>
-      <c r="G146" s="15" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
+        <v>9102</v>
+      </c>
+      <c r="F146" s="15" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="G146" s="15" t="n">
+        <v>499.84</v>
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>No nulls; 147 distinct value(s)</t>
+          <t>No nulls; 9102 distinct value(s)</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
@@ -6630,12 +6763,12 @@
     <row r="147">
       <c r="B147" s="49" t="inlineStr">
         <is>
-          <t>subsidiary_id</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6644,17 +6777,17 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5</v>
+        <v>9969</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>17.65</v>
       </c>
       <c r="G147" t="n">
-        <v>5</v>
+        <v>24858.55</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>No nulls; 5 distinct value(s)</t>
+          <t>No nulls; 9969 distinct value(s)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6666,49 +6799,48 @@
     <row r="148">
       <c r="B148" s="45" t="inlineStr">
         <is>
-          <t>FK Field</t>
+          <t>account_id</t>
         </is>
       </c>
       <c r="C148" s="45" t="inlineStr">
         <is>
-          <t>References Table</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D148" s="45" t="inlineStr">
         <is>
-          <t>References Field</t>
-        </is>
-      </c>
-      <c r="E148" s="45" t="inlineStr">
-        <is>
-          <t>Orphan Row Count</t>
-        </is>
-      </c>
-      <c r="F148" s="45" t="inlineStr">
-        <is>
-          <t>Orphan %</t>
-        </is>
-      </c>
-      <c r="G148" s="45" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E148" s="45" t="n">
+        <v>300</v>
+      </c>
+      <c r="F148" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="45" t="n">
+        <v>300</v>
       </c>
       <c r="H148" s="45" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>No nulls; 300 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>subsidiary_id</t>
+          <t>transaction_id</t>
         </is>
       </c>
       <c r="C149" s="16" t="inlineStr">
         <is>
-          <t>SUBSIDIARY</t>
+          <t>TRANSACTION</t>
         </is>
       </c>
       <c r="D149" s="16" t="inlineStr">
@@ -6734,16 +6866,21 @@
           <t>GREEN</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>department_id</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>DEPARTMENT</t>
+          <t>ITEM</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
@@ -6771,19 +6908,79 @@
       </c>
     </row>
     <row r="151">
-      <c r="B151" s="16" t="n"/>
-      <c r="C151" s="16" t="n"/>
-      <c r="D151" s="16" t="n"/>
-      <c r="E151" s="16" t="n"/>
-      <c r="F151" s="16" t="n"/>
-      <c r="G151" s="16" t="n"/>
-      <c r="H151" s="16" t="n"/>
-    </row>
-    <row r="152"/>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>account_id</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>ACCOUNT</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H151" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>employee_id</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
     <row r="153">
       <c r="B153" s="47" t="inlineStr">
         <is>
-          <t>Table 6: ACCOUNT</t>
+          <t>Table 6: EMPLOYEE</t>
         </is>
       </c>
     </row>
@@ -6817,7 +7014,7 @@
       </c>
       <c r="D155" s="44" t="inlineStr">
         <is>
-          <t>ACCOUNT</t>
+          <t>EMPLOYEE</t>
         </is>
       </c>
     </row>
@@ -6834,7 +7031,7 @@
       </c>
       <c r="D156" s="43" t="inlineStr">
         <is>
-          <t>Chart of accounts for GL posting</t>
+          <t>HR employee master used for approvals and assignments</t>
         </is>
       </c>
     </row>
@@ -6851,7 +7048,7 @@
       </c>
       <c r="D157" s="44" t="inlineStr">
         <is>
-          <t>One row = one GL account</t>
+          <t>One row = one employee</t>
         </is>
       </c>
     </row>
@@ -6867,7 +7064,7 @@
         </is>
       </c>
       <c r="D158" s="43" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="159">
@@ -6883,7 +7080,7 @@
       </c>
       <c r="D159" s="44" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2021-03-22 – 2026-03-21</t>
         </is>
       </c>
     </row>
@@ -6934,7 +7131,7 @@
       </c>
       <c r="D162" s="43" t="inlineStr">
         <is>
-          <t>D5 – Financials</t>
+          <t>D3 – Workforce</t>
         </is>
       </c>
     </row>
@@ -6951,7 +7148,7 @@
       </c>
       <c r="D163" s="44" t="inlineStr">
         <is>
-          <t>GL_ACCOUNT</t>
+          <t>EMPLOYEE</t>
         </is>
       </c>
     </row>
@@ -7038,13 +7235,13 @@
         </is>
       </c>
       <c r="E167" s="16" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F167" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G167" s="16" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H167" s="16" t="inlineStr">
         <is>
@@ -7060,7 +7257,7 @@
     <row r="168">
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>acctnumber</t>
+          <t>entityid</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
@@ -7074,16 +7271,16 @@
         </is>
       </c>
       <c r="E168" s="15" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>EMP-0001</t>
         </is>
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>EMP-0150</t>
         </is>
       </c>
       <c r="H168" s="15" t="inlineStr">
@@ -7100,7 +7297,7 @@
     <row r="169">
       <c r="B169" s="16" t="inlineStr">
         <is>
-          <t>acctname</t>
+          <t>firstname</t>
         </is>
       </c>
       <c r="C169" s="16" t="inlineStr">
@@ -7114,21 +7311,21 @@
         </is>
       </c>
       <c r="E169" s="16" t="n">
-        <v>299</v>
+        <v>101</v>
       </c>
       <c r="F169" s="16" t="inlineStr">
         <is>
-          <t>Aggregate B2C Roi</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="G169" s="16" t="inlineStr">
         <is>
-          <t>Whiteboard Vertical Channels</t>
+          <t>William</t>
         </is>
       </c>
       <c r="H169" s="16" t="inlineStr">
         <is>
-          <t>No nulls; 299 distinct value(s)</t>
+          <t>No nulls; 101 distinct value(s)</t>
         </is>
       </c>
       <c r="I169" s="16" t="inlineStr">
@@ -7140,7 +7337,7 @@
     <row r="170">
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>accttype</t>
+          <t>lastname</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
@@ -7154,21 +7351,21 @@
         </is>
       </c>
       <c r="E170" s="15" t="n">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="F170" s="15" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>No nulls; 5 distinct value(s)</t>
+          <t>No nulls; 124 distinct value(s)</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
@@ -7180,53 +7377,116 @@
     <row r="171">
       <c r="B171" s="16" t="inlineStr">
         <is>
-          <t>subsidiary_id</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C171" s="16" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>VARCHAR</t>
         </is>
       </c>
       <c r="D171" s="16" t="inlineStr">
         <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>128</v>
+      </c>
+      <c r="F171" s="16" t="inlineStr">
+        <is>
+          <t>abigailmartinez@example.net</t>
+        </is>
+      </c>
+      <c r="G171" s="16" t="inlineStr">
+        <is>
+          <t>zgarcia@example.com</t>
+        </is>
+      </c>
+      <c r="H171" s="16" t="inlineStr">
+        <is>
+          <t>22 null (14.7%)</t>
+        </is>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="15" t="inlineStr">
+        <is>
+          <t>datecreated</t>
+        </is>
+      </c>
+      <c r="C172" s="15" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D172" s="15" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="E171" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F171" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H171" s="16" t="inlineStr">
-        <is>
-          <t>No nulls; 5 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I171" s="16" t="inlineStr">
+      <c r="E172" s="15" t="n">
+        <v>145</v>
+      </c>
+      <c r="F172" s="15" t="inlineStr">
+        <is>
+          <t>2021-03-22</t>
+        </is>
+      </c>
+      <c r="G172" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="H172" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 145 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I172" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-    </row>
-    <row r="172">
-      <c r="B172" s="15" t="n"/>
-      <c r="C172" s="15" t="n"/>
-      <c r="D172" s="15" t="n"/>
-      <c r="E172" s="15" t="n"/>
-      <c r="F172" s="15" t="n"/>
-      <c r="G172" s="15" t="n"/>
-      <c r="H172" s="15" t="n"/>
-      <c r="I172" s="15" t="n"/>
     </row>
     <row r="173">
       <c r="B173" s="49" t="inlineStr">
         <is>
-          <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>5</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" t="n">
+        <v>5</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>No nulls; 5 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
     </row>
@@ -7303,13 +7563,39 @@
       </c>
     </row>
     <row r="176">
-      <c r="B176" s="15" t="n"/>
-      <c r="C176" s="15" t="n"/>
-      <c r="D176" s="15" t="n"/>
-      <c r="E176" s="15" t="n"/>
-      <c r="F176" s="15" t="n"/>
-      <c r="G176" s="15" t="n"/>
-      <c r="H176" s="15" t="n"/>
+      <c r="B176" s="15" t="inlineStr">
+        <is>
+          <t>department_id</t>
+        </is>
+      </c>
+      <c r="C176" s="15" t="inlineStr">
+        <is>
+          <t>DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="D176" s="15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E176" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G176" s="15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H176" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="B177" s="16" t="n"/>
@@ -7324,7 +7610,7 @@
     <row r="179">
       <c r="B179" s="47" t="inlineStr">
         <is>
-          <t>Table 7: SUBSIDIARY</t>
+          <t>Table 7: ACCOUNT</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7644,7 @@
       </c>
       <c r="D181" s="44" t="inlineStr">
         <is>
-          <t>SUBSIDIARY</t>
+          <t>ACCOUNT</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7661,7 @@
       </c>
       <c r="D182" s="43" t="inlineStr">
         <is>
-          <t>Legal entities / subsidiaries within NetSuite OneWorld</t>
+          <t>Chart of accounts for GL posting</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7678,7 @@
       </c>
       <c r="D183" s="44" t="inlineStr">
         <is>
-          <t>One row = one subsidiary</t>
+          <t>One row = one GL account</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7694,7 @@
         </is>
       </c>
       <c r="D184" s="43" t="n">
-        <v>5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="185">
@@ -7492,7 +7778,7 @@
       </c>
       <c r="D189" s="44" t="inlineStr">
         <is>
-          <t>SUBSIDIARY</t>
+          <t>GL_ACCOUNT</t>
         </is>
       </c>
     </row>
@@ -7579,13 +7865,13 @@
         </is>
       </c>
       <c r="E193" s="16" t="n">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="F193" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G193" s="16" t="n">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="H193" s="16" t="inlineStr">
         <is>
@@ -7601,7 +7887,7 @@
     <row r="194">
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>acctnumber</t>
         </is>
       </c>
       <c r="C194" s="15" t="inlineStr">
@@ -7615,58 +7901,144 @@
         </is>
       </c>
       <c r="E194" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="F194" s="15" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="G194" s="15" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="H194" s="15" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I194" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="16" t="inlineStr">
+        <is>
+          <t>acctname</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D195" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E195" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="F195" s="16" t="inlineStr">
+        <is>
+          <t>Aggregate Clicks-And-Mortar Applications</t>
+        </is>
+      </c>
+      <c r="G195" s="16" t="inlineStr">
+        <is>
+          <t>Whiteboard Web-Enabled Partnerships</t>
+        </is>
+      </c>
+      <c r="H195" s="16" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I195" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" s="15" t="inlineStr">
+        <is>
+          <t>accttype</t>
+        </is>
+      </c>
+      <c r="C196" s="15" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D196" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E196" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F194" s="15" t="inlineStr">
-        <is>
-          <t>Subsidiary 1</t>
-        </is>
-      </c>
-      <c r="G194" s="15" t="inlineStr">
-        <is>
-          <t>Subsidiary 5</t>
-        </is>
-      </c>
-      <c r="H194" s="15" t="inlineStr">
-        <is>
-          <t>No nulls, no duplicates</t>
-        </is>
-      </c>
-      <c r="I194" s="15" t="inlineStr">
+      <c r="F196" s="15" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="G196" s="15" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="H196" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 5 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I196" s="15" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="B195" s="16" t="n"/>
-      <c r="C195" s="16" t="n"/>
-      <c r="D195" s="16" t="n"/>
-      <c r="E195" s="16" t="n"/>
-      <c r="F195" s="16" t="n"/>
-      <c r="G195" s="16" t="n"/>
-      <c r="H195" s="16" t="n"/>
-      <c r="I195" s="16" t="n"/>
-    </row>
-    <row r="196">
-      <c r="B196" s="15" t="n"/>
-      <c r="C196" s="15" t="n"/>
-      <c r="D196" s="15" t="n"/>
-      <c r="E196" s="15" t="n"/>
-      <c r="F196" s="15" t="n"/>
-      <c r="G196" s="15" t="n"/>
-      <c r="H196" s="15" t="n"/>
-      <c r="I196" s="15" t="n"/>
-    </row>
     <row r="197">
-      <c r="B197" s="16" t="n"/>
-      <c r="C197" s="16" t="n"/>
-      <c r="D197" s="16" t="n"/>
-      <c r="E197" s="16" t="n"/>
-      <c r="F197" s="16" t="n"/>
-      <c r="G197" s="16" t="n"/>
-      <c r="H197" s="16" t="n"/>
-      <c r="I197" s="16" t="n"/>
+      <c r="B197" s="16" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C197" s="16" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D197" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E197" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F197" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H197" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 5 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I197" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="B198" s="15" t="n"/>
@@ -7723,13 +8095,39 @@
       </c>
     </row>
     <row r="201">
-      <c r="B201" s="16" t="n"/>
-      <c r="C201" s="16" t="n"/>
-      <c r="D201" s="16" t="n"/>
-      <c r="E201" s="16" t="n"/>
-      <c r="F201" s="16" t="n"/>
-      <c r="G201" s="16" t="n"/>
-      <c r="H201" s="16" t="n"/>
+      <c r="B201" s="16" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C201" s="16" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="D201" s="16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G201" s="16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H201" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="B202" s="15" t="n"/>
@@ -7753,7 +8151,7 @@
     <row r="205">
       <c r="B205" s="47" t="inlineStr">
         <is>
-          <t>Table 8: DEPARTMENT</t>
+          <t>Table 8: LOCATION</t>
         </is>
       </c>
     </row>
@@ -7787,7 +8185,7 @@
       </c>
       <c r="D207" s="44" t="inlineStr">
         <is>
-          <t>DEPARTMENT</t>
+          <t>LOCATION</t>
         </is>
       </c>
     </row>
@@ -7804,7 +8202,7 @@
       </c>
       <c r="D208" s="43" t="inlineStr">
         <is>
-          <t>Cost centre / department classification</t>
+          <t>Physical office / site locations. customer.location_id references this table.</t>
         </is>
       </c>
     </row>
@@ -7821,7 +8219,7 @@
       </c>
       <c r="D209" s="44" t="inlineStr">
         <is>
-          <t>One row = one department</t>
+          <t>One row = one location</t>
         </is>
       </c>
     </row>
@@ -7837,7 +8235,7 @@
         </is>
       </c>
       <c r="D210" s="43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="211">
@@ -7904,7 +8302,7 @@
       </c>
       <c r="D214" s="43" t="inlineStr">
         <is>
-          <t>D5 – Financials</t>
+          <t>D1 – Customers &amp; Locations</t>
         </is>
       </c>
     </row>
@@ -7921,7 +8319,7 @@
       </c>
       <c r="D215" s="44" t="inlineStr">
         <is>
-          <t>DEPARTMENT</t>
+          <t>LOCATION</t>
         </is>
       </c>
     </row>
@@ -8008,13 +8406,13 @@
         </is>
       </c>
       <c r="E219" s="16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F219" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G219" s="16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H219" s="16" t="inlineStr">
         <is>
@@ -8044,16 +8442,16 @@
         </is>
       </c>
       <c r="E220" s="15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F220" s="15" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Adelaide Office</t>
         </is>
       </c>
       <c r="G220" s="15" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Vancouver Office</t>
         </is>
       </c>
       <c r="H220" s="15" t="inlineStr">
@@ -8070,58 +8468,118 @@
     <row r="221">
       <c r="B221" s="16" t="inlineStr">
         <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="C221" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D221" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E221" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F221" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="G221" s="16" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="H221" s="16" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I221" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" s="15" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C222" s="15" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D222" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E222" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F222" s="15" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G222" s="15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H222" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 8 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I222" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" s="16" t="inlineStr">
+        <is>
           <t>subsidiary_id</t>
         </is>
       </c>
-      <c r="C221" s="16" t="inlineStr">
+      <c r="C223" s="16" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D221" s="16" t="inlineStr">
+      <c r="D223" s="16" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="E221" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F221" s="16" t="n">
+      <c r="E223" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F223" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G221" s="16" t="n">
+      <c r="G223" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="H221" s="16" t="inlineStr">
-        <is>
-          <t>No nulls; 4 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I221" s="16" t="inlineStr">
+      <c r="H223" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 5 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I223" s="16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-    </row>
-    <row r="222">
-      <c r="B222" s="15" t="n"/>
-      <c r="C222" s="15" t="n"/>
-      <c r="D222" s="15" t="n"/>
-      <c r="E222" s="15" t="n"/>
-      <c r="F222" s="15" t="n"/>
-      <c r="G222" s="15" t="n"/>
-      <c r="H222" s="15" t="n"/>
-      <c r="I222" s="15" t="n"/>
-    </row>
-    <row r="223">
-      <c r="B223" s="16" t="n"/>
-      <c r="C223" s="16" t="n"/>
-      <c r="D223" s="16" t="n"/>
-      <c r="E223" s="16" t="n"/>
-      <c r="F223" s="16" t="n"/>
-      <c r="G223" s="16" t="n"/>
-      <c r="H223" s="16" t="n"/>
-      <c r="I223" s="16" t="n"/>
     </row>
     <row r="224">
       <c r="B224" s="15" t="n"/>
@@ -8234,7 +8692,7 @@
     <row r="231">
       <c r="B231" s="47" t="inlineStr">
         <is>
-          <t>Table 9: SALESORDER</t>
+          <t>Table 9: SUBSIDIARY</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8726,7 @@
       </c>
       <c r="D233" s="44" t="inlineStr">
         <is>
-          <t>SALESORDER</t>
+          <t>SUBSIDIARY</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8743,7 @@
       </c>
       <c r="D234" s="43" t="inlineStr">
         <is>
-          <t>Sales orders linked to customers and items</t>
+          <t>Legal entities / subsidiaries within NetSuite OneWorld</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8760,7 @@
       </c>
       <c r="D235" s="44" t="inlineStr">
         <is>
-          <t>One row = one sales order header</t>
+          <t>One row = one subsidiary</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8776,7 @@
         </is>
       </c>
       <c r="D236" s="43" t="n">
-        <v>2500</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237">
@@ -8334,7 +8792,7 @@
       </c>
       <c r="D237" s="44" t="inlineStr">
         <is>
-          <t>2021-03-22 – 2026-03-22</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8843,7 @@
       </c>
       <c r="D240" s="43" t="inlineStr">
         <is>
-          <t>D2 – Contracts &amp; Revenue</t>
+          <t>D5 – Financials</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8860,7 @@
       </c>
       <c r="D241" s="44" t="inlineStr">
         <is>
-          <t>SALES_ORDER</t>
+          <t>SUBSIDIARY</t>
         </is>
       </c>
     </row>
@@ -8489,13 +8947,13 @@
         </is>
       </c>
       <c r="E245" s="16" t="n">
-        <v>2500</v>
+        <v>5</v>
       </c>
       <c r="F245" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G245" s="16" t="n">
-        <v>2500</v>
+        <v>5</v>
       </c>
       <c r="H245" s="16" t="inlineStr">
         <is>
@@ -8511,7 +8969,7 @@
     <row r="246">
       <c r="B246" s="15" t="inlineStr">
         <is>
-          <t>tranid</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C246" s="15" t="inlineStr">
@@ -8525,16 +8983,16 @@
         </is>
       </c>
       <c r="E246" s="15" t="n">
-        <v>2500</v>
+        <v>5</v>
       </c>
       <c r="F246" s="15" t="inlineStr">
         <is>
-          <t>SO-00001</t>
+          <t>Subsidiary 1</t>
         </is>
       </c>
       <c r="G246" s="15" t="inlineStr">
         <is>
-          <t>SO-02500</t>
+          <t>Subsidiary 5</t>
         </is>
       </c>
       <c r="H246" s="15" t="inlineStr">
@@ -8549,156 +9007,44 @@
       </c>
     </row>
     <row r="247">
-      <c r="B247" s="16" t="inlineStr">
-        <is>
-          <t>trandate</t>
-        </is>
-      </c>
-      <c r="C247" s="16" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D247" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E247" s="16" t="n">
-        <v>1381</v>
-      </c>
-      <c r="F247" s="16" t="inlineStr">
-        <is>
-          <t>2021-03-22</t>
-        </is>
-      </c>
-      <c r="G247" s="16" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="H247" s="16" t="inlineStr">
-        <is>
-          <t>No nulls; 1381 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I247" s="16" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B247" s="16" t="n"/>
+      <c r="C247" s="16" t="n"/>
+      <c r="D247" s="16" t="n"/>
+      <c r="E247" s="16" t="n"/>
+      <c r="F247" s="16" t="n"/>
+      <c r="G247" s="16" t="n"/>
+      <c r="H247" s="16" t="n"/>
+      <c r="I247" s="16" t="n"/>
     </row>
     <row r="248">
-      <c r="B248" s="15" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="C248" s="15" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D248" s="15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E248" s="15" t="n">
-        <v>497</v>
-      </c>
-      <c r="F248" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G248" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="H248" s="15" t="inlineStr">
-        <is>
-          <t>No nulls; 497 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I248" s="15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B248" s="15" t="n"/>
+      <c r="C248" s="15" t="n"/>
+      <c r="D248" s="15" t="n"/>
+      <c r="E248" s="15" t="n"/>
+      <c r="F248" s="15" t="n"/>
+      <c r="G248" s="15" t="n"/>
+      <c r="H248" s="15" t="n"/>
+      <c r="I248" s="15" t="n"/>
     </row>
     <row r="249">
-      <c r="B249" s="16" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C249" s="16" t="inlineStr">
-        <is>
-          <t>DECIMAL</t>
-        </is>
-      </c>
-      <c r="D249" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E249" s="16" t="n">
-        <v>2499</v>
-      </c>
-      <c r="F249" s="16" t="n">
-        <v>510.55</v>
-      </c>
-      <c r="G249" s="16" t="n">
-        <v>99989.25999999999</v>
-      </c>
-      <c r="H249" s="16" t="inlineStr">
-        <is>
-          <t>No nulls; 2499 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I249" s="16" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B249" s="16" t="n"/>
+      <c r="C249" s="16" t="n"/>
+      <c r="D249" s="16" t="n"/>
+      <c r="E249" s="16" t="n"/>
+      <c r="F249" s="16" t="n"/>
+      <c r="G249" s="16" t="n"/>
+      <c r="H249" s="16" t="n"/>
+      <c r="I249" s="16" t="n"/>
     </row>
     <row r="250">
-      <c r="B250" s="15" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C250" s="15" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D250" s="15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E250" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F250" s="15" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-      <c r="G250" s="15" t="inlineStr">
-        <is>
-          <t>Pending Fulfillment</t>
-        </is>
-      </c>
-      <c r="H250" s="15" t="inlineStr">
-        <is>
-          <t>No nulls; 3 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I250" s="15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B250" s="15" t="n"/>
+      <c r="C250" s="15" t="n"/>
+      <c r="D250" s="15" t="n"/>
+      <c r="E250" s="15" t="n"/>
+      <c r="F250" s="15" t="n"/>
+      <c r="G250" s="15" t="n"/>
+      <c r="H250" s="15" t="n"/>
+      <c r="I250" s="15" t="n"/>
     </row>
     <row r="251">
       <c r="B251" s="49" t="inlineStr">
@@ -8745,74 +9091,22 @@
       </c>
     </row>
     <row r="253">
-      <c r="B253" s="16" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="C253" s="16" t="inlineStr">
-        <is>
-          <t>CUSTOMER</t>
-        </is>
-      </c>
-      <c r="D253" s="16" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E253" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F253" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G253" s="16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H253" s="16" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B253" s="16" t="n"/>
+      <c r="C253" s="16" t="n"/>
+      <c r="D253" s="16" t="n"/>
+      <c r="E253" s="16" t="n"/>
+      <c r="F253" s="16" t="n"/>
+      <c r="G253" s="16" t="n"/>
+      <c r="H253" s="16" t="n"/>
     </row>
     <row r="254">
-      <c r="B254" s="15" t="inlineStr">
-        <is>
-          <t>subsidiary_id</t>
-        </is>
-      </c>
-      <c r="C254" s="15" t="inlineStr">
-        <is>
-          <t>SUBSIDIARY</t>
-        </is>
-      </c>
-      <c r="D254" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E254" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F254" s="15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G254" s="15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H254" s="15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B254" s="15" t="n"/>
+      <c r="C254" s="15" t="n"/>
+      <c r="D254" s="15" t="n"/>
+      <c r="E254" s="15" t="n"/>
+      <c r="F254" s="15" t="n"/>
+      <c r="G254" s="15" t="n"/>
+      <c r="H254" s="15" t="n"/>
     </row>
     <row r="255">
       <c r="B255" s="16" t="n"/>
@@ -8827,7 +9121,7 @@
     <row r="257">
       <c r="B257" s="47" t="inlineStr">
         <is>
-          <t>Table 10: PURCHASEORDER</t>
+          <t>Table 10: DEPARTMENT</t>
         </is>
       </c>
     </row>
@@ -8861,7 +9155,7 @@
       </c>
       <c r="D259" s="44" t="inlineStr">
         <is>
-          <t>PURCHASEORDER</t>
+          <t>DEPARTMENT</t>
         </is>
       </c>
     </row>
@@ -8878,7 +9172,7 @@
       </c>
       <c r="D260" s="43" t="inlineStr">
         <is>
-          <t>Purchase orders raised against vendors</t>
+          <t>Cost centre / department classification</t>
         </is>
       </c>
     </row>
@@ -8895,7 +9189,7 @@
       </c>
       <c r="D261" s="44" t="inlineStr">
         <is>
-          <t>One row = one purchase order header</t>
+          <t>One row = one department</t>
         </is>
       </c>
     </row>
@@ -8911,7 +9205,7 @@
         </is>
       </c>
       <c r="D262" s="43" t="n">
-        <v>800</v>
+        <v>10</v>
       </c>
     </row>
     <row r="263">
@@ -8927,7 +9221,7 @@
       </c>
       <c r="D263" s="44" t="inlineStr">
         <is>
-          <t>2021-03-23 – 2026-03-21</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8995,7 +9289,7 @@
       </c>
       <c r="D267" s="44" t="inlineStr">
         <is>
-          <t>PURCHASE_ORDER</t>
+          <t>DEPARTMENT</t>
         </is>
       </c>
     </row>
@@ -9082,13 +9376,13 @@
         </is>
       </c>
       <c r="E271" s="16" t="n">
-        <v>800</v>
+        <v>10</v>
       </c>
       <c r="F271" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G271" s="16" t="n">
-        <v>800</v>
+        <v>10</v>
       </c>
       <c r="H271" s="16" t="inlineStr">
         <is>
@@ -9104,7 +9398,7 @@
     <row r="272">
       <c r="B272" s="15" t="inlineStr">
         <is>
-          <t>tranid</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C272" s="15" t="inlineStr">
@@ -9118,16 +9412,16 @@
         </is>
       </c>
       <c r="E272" s="15" t="n">
-        <v>800</v>
+        <v>10</v>
       </c>
       <c r="F272" s="15" t="inlineStr">
         <is>
-          <t>PO-00001</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G272" s="15" t="inlineStr">
         <is>
-          <t>PO-00800</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="H272" s="15" t="inlineStr">
@@ -9144,12 +9438,12 @@
     <row r="273">
       <c r="B273" s="16" t="inlineStr">
         <is>
-          <t>trandate</t>
+          <t>subsidiary_id</t>
         </is>
       </c>
       <c r="C273" s="16" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D273" s="16" t="inlineStr">
@@ -9158,21 +9452,17 @@
         </is>
       </c>
       <c r="E273" s="16" t="n">
-        <v>654</v>
-      </c>
-      <c r="F273" s="16" t="inlineStr">
-        <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="G273" s="16" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="F273" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G273" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H273" s="16" t="inlineStr">
         <is>
-          <t>No nulls; 654 distinct value(s)</t>
+          <t>No nulls; 4 distinct value(s)</t>
         </is>
       </c>
       <c r="I273" s="16" t="inlineStr">
@@ -9182,116 +9472,34 @@
       </c>
     </row>
     <row r="274">
-      <c r="B274" s="15" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="C274" s="15" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D274" s="15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E274" s="15" t="n">
-        <v>194</v>
-      </c>
-      <c r="F274" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G274" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="H274" s="15" t="inlineStr">
-        <is>
-          <t>No nulls; 194 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I274" s="15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B274" s="15" t="n"/>
+      <c r="C274" s="15" t="n"/>
+      <c r="D274" s="15" t="n"/>
+      <c r="E274" s="15" t="n"/>
+      <c r="F274" s="15" t="n"/>
+      <c r="G274" s="15" t="n"/>
+      <c r="H274" s="15" t="n"/>
+      <c r="I274" s="15" t="n"/>
     </row>
     <row r="275">
-      <c r="B275" s="16" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C275" s="16" t="inlineStr">
-        <is>
-          <t>DECIMAL</t>
-        </is>
-      </c>
-      <c r="D275" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E275" s="16" t="n">
-        <v>799</v>
-      </c>
-      <c r="F275" s="16" t="n">
-        <v>253.05</v>
-      </c>
-      <c r="G275" s="16" t="n">
-        <v>49872.73</v>
-      </c>
-      <c r="H275" s="16" t="inlineStr">
-        <is>
-          <t>No nulls; 799 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I275" s="16" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B275" s="16" t="n"/>
+      <c r="C275" s="16" t="n"/>
+      <c r="D275" s="16" t="n"/>
+      <c r="E275" s="16" t="n"/>
+      <c r="F275" s="16" t="n"/>
+      <c r="G275" s="16" t="n"/>
+      <c r="H275" s="16" t="n"/>
+      <c r="I275" s="16" t="n"/>
     </row>
     <row r="276">
-      <c r="B276" s="15" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C276" s="15" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D276" s="15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E276" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F276" s="15" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-      <c r="G276" s="15" t="inlineStr">
-        <is>
-          <t>Pending Receipt</t>
-        </is>
-      </c>
-      <c r="H276" s="15" t="inlineStr">
-        <is>
-          <t>No nulls; 3 distinct value(s)</t>
-        </is>
-      </c>
-      <c r="I276" s="15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B276" s="15" t="n"/>
+      <c r="C276" s="15" t="n"/>
+      <c r="D276" s="15" t="n"/>
+      <c r="E276" s="15" t="n"/>
+      <c r="F276" s="15" t="n"/>
+      <c r="G276" s="15" t="n"/>
+      <c r="H276" s="15" t="n"/>
+      <c r="I276" s="15" t="n"/>
     </row>
     <row r="277">
       <c r="B277" s="49" t="inlineStr">
@@ -9340,12 +9548,12 @@
     <row r="279">
       <c r="B279" s="16" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>subsidiary_id</t>
         </is>
       </c>
       <c r="C279" s="16" t="inlineStr">
         <is>
-          <t>VENDOR</t>
+          <t>SUBSIDIARY</t>
         </is>
       </c>
       <c r="D279" s="16" t="inlineStr">
@@ -9373,39 +9581,13 @@
       </c>
     </row>
     <row r="280">
-      <c r="B280" s="15" t="inlineStr">
-        <is>
-          <t>subsidiary_id</t>
-        </is>
-      </c>
-      <c r="C280" s="15" t="inlineStr">
-        <is>
-          <t>SUBSIDIARY</t>
-        </is>
-      </c>
-      <c r="D280" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E280" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" s="15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G280" s="15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H280" s="15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
+      <c r="B280" s="15" t="n"/>
+      <c r="C280" s="15" t="n"/>
+      <c r="D280" s="15" t="n"/>
+      <c r="E280" s="15" t="n"/>
+      <c r="F280" s="15" t="n"/>
+      <c r="G280" s="15" t="n"/>
+      <c r="H280" s="15" t="n"/>
     </row>
     <row r="281">
       <c r="B281" s="16" t="n"/>
@@ -9417,385 +9599,1645 @@
       <c r="H281" s="16" t="n"/>
     </row>
     <row r="282"/>
+    <row r="283">
+      <c r="B283" s="47" t="inlineStr">
+        <is>
+          <t>Table 11: SALESORDER</t>
+        </is>
+      </c>
+    </row>
     <row r="284">
-      <c r="B284" t="inlineStr">
+      <c r="B284" s="48" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C284" s="48" t="inlineStr">
+        <is>
+          <t>How to measure</t>
+        </is>
+      </c>
+      <c r="D284" s="48" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" s="25" t="inlineStr">
+        <is>
+          <t>Table / view name</t>
+        </is>
+      </c>
+      <c r="C285" s="24" t="inlineStr">
+        <is>
+          <t>Exact name as it appears in source schema</t>
+        </is>
+      </c>
+      <c r="D285" s="44" t="inlineStr">
+        <is>
+          <t>SALESORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" s="25" t="inlineStr">
+        <is>
+          <t>Business purpose</t>
+        </is>
+      </c>
+      <c r="C286" s="24" t="inlineStr">
+        <is>
+          <t>What business process does this table record?</t>
+        </is>
+      </c>
+      <c r="D286" s="43" t="inlineStr">
+        <is>
+          <t>Sales orders linked to customers and items</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" s="25" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="C287" s="24" t="inlineStr">
+        <is>
+          <t>One row = one [what]? e.g. one invoice line, one work order</t>
+        </is>
+      </c>
+      <c r="D287" s="44" t="inlineStr">
+        <is>
+          <t>One row = one sales order header</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" s="25" t="inlineStr">
+        <is>
+          <t>Total row count</t>
+        </is>
+      </c>
+      <c r="C288" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM table</t>
+        </is>
+      </c>
+      <c r="D288" s="43" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" s="25" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="C289" s="24" t="inlineStr">
+        <is>
+          <t>MIN and MAX of primary date field</t>
+        </is>
+      </c>
+      <c r="D289" s="44" t="inlineStr">
+        <is>
+          <t>2021-03-22 – 2026-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" s="25" t="inlineStr">
+        <is>
+          <t>Primary key field(s)</t>
+        </is>
+      </c>
+      <c r="C290" s="24" t="inlineStr">
+        <is>
+          <t>Field name(s) — is it a surrogate or natural key?</t>
+        </is>
+      </c>
+      <c r="D290" s="43" t="inlineStr">
+        <is>
+          <t>id (surrogate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" s="25" t="inlineStr">
+        <is>
+          <t>PK uniqueness check</t>
+        </is>
+      </c>
+      <c r="C291" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) vs COUNT(DISTINCT pk) — match = PASS</t>
+        </is>
+      </c>
+      <c r="D291" s="44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" s="25" t="inlineStr">
+        <is>
+          <t>Canonical domain</t>
+        </is>
+      </c>
+      <c r="C292" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical domain does this table feed? (Domain 1–5)</t>
+        </is>
+      </c>
+      <c r="D292" s="43" t="inlineStr">
+        <is>
+          <t>D2 – Contracts &amp; Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" s="25" t="inlineStr">
+        <is>
+          <t>Canonical entities</t>
+        </is>
+      </c>
+      <c r="C293" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical entities? e.g. WORK_ORDER, WORK_ORDER_LINE</t>
+        </is>
+      </c>
+      <c r="D293" s="44" t="inlineStr">
+        <is>
+          <t>SALES_ORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" s="25" t="inlineStr">
+        <is>
+          <t>Overall table RAG</t>
+        </is>
+      </c>
+      <c r="C294" s="24" t="inlineStr">
+        <is>
+          <t>GREEN / AMBER / RED — your assessment of table usability</t>
+        </is>
+      </c>
+      <c r="D294" s="43" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" s="49" t="inlineStr">
+        <is>
+          <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" s="45" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="C296" s="45" t="inlineStr">
+        <is>
+          <t>Field Type</t>
+        </is>
+      </c>
+      <c r="D296" s="45" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="E296" s="45" t="inlineStr">
+        <is>
+          <t>Distinct Count</t>
+        </is>
+      </c>
+      <c r="F296" s="45" t="inlineStr">
+        <is>
+          <t>Min Value</t>
+        </is>
+      </c>
+      <c r="G296" s="45" t="inlineStr">
+        <is>
+          <t>Max Value</t>
+        </is>
+      </c>
+      <c r="H296" s="45" t="inlineStr">
+        <is>
+          <t>Notes / Issues</t>
+        </is>
+      </c>
+      <c r="I296" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" s="16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C297" s="16" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D297" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E297" s="16" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F297" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G297" s="16" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H297" s="16" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I297" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" s="15" t="inlineStr">
+        <is>
+          <t>tranid</t>
+        </is>
+      </c>
+      <c r="C298" s="15" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D298" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E298" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F298" s="15" t="inlineStr">
+        <is>
+          <t>SO-00001</t>
+        </is>
+      </c>
+      <c r="G298" s="15" t="inlineStr">
+        <is>
+          <t>SO-02500</t>
+        </is>
+      </c>
+      <c r="H298" s="15" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I298" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" s="16" t="inlineStr">
+        <is>
+          <t>trandate</t>
+        </is>
+      </c>
+      <c r="C299" s="16" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D299" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E299" s="16" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F299" s="16" t="inlineStr">
+        <is>
+          <t>2021-03-22</t>
+        </is>
+      </c>
+      <c r="G299" s="16" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="H299" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 1360 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I299" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" s="15" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="C300" s="15" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D300" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E300" s="15" t="n">
+        <v>497</v>
+      </c>
+      <c r="F300" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G300" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="H300" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 497 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I300" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" s="16" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C301" s="16" t="inlineStr">
+        <is>
+          <t>DECIMAL</t>
+        </is>
+      </c>
+      <c r="D301" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E301" s="16" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F301" s="16" t="n">
+        <v>525.71</v>
+      </c>
+      <c r="G301" s="16" t="n">
+        <v>99932.39</v>
+      </c>
+      <c r="H301" s="16" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I301" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="15" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C302" s="15" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D302" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E302" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F302" s="15" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="G302" s="15" t="inlineStr">
+        <is>
+          <t>Pending Fulfillment</t>
+        </is>
+      </c>
+      <c r="H302" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 3 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I302" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" s="49" t="inlineStr">
+        <is>
+          <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" s="45" t="inlineStr">
+        <is>
+          <t>FK Field</t>
+        </is>
+      </c>
+      <c r="C304" s="45" t="inlineStr">
+        <is>
+          <t>References Table</t>
+        </is>
+      </c>
+      <c r="D304" s="45" t="inlineStr">
+        <is>
+          <t>References Field</t>
+        </is>
+      </c>
+      <c r="E304" s="45" t="inlineStr">
+        <is>
+          <t>Orphan Row Count</t>
+        </is>
+      </c>
+      <c r="F304" s="45" t="inlineStr">
+        <is>
+          <t>Orphan %</t>
+        </is>
+      </c>
+      <c r="G304" s="45" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H304" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" s="16" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="C305" s="16" t="inlineStr">
+        <is>
+          <t>CUSTOMER</t>
+        </is>
+      </c>
+      <c r="D305" s="16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E305" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F305" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G305" s="16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H305" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" s="15" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C306" s="15" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="D306" s="15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E306" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G306" s="15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H306" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="16" t="n"/>
+      <c r="C307" s="16" t="n"/>
+      <c r="D307" s="16" t="n"/>
+      <c r="E307" s="16" t="n"/>
+      <c r="F307" s="16" t="n"/>
+      <c r="G307" s="16" t="n"/>
+      <c r="H307" s="16" t="n"/>
+    </row>
+    <row r="308"/>
+    <row r="309">
+      <c r="B309" s="47" t="inlineStr">
+        <is>
+          <t>Table 12: PURCHASEORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" s="48" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C310" s="48" t="inlineStr">
+        <is>
+          <t>How to measure</t>
+        </is>
+      </c>
+      <c r="D310" s="48" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" s="25" t="inlineStr">
+        <is>
+          <t>Table / view name</t>
+        </is>
+      </c>
+      <c r="C311" s="24" t="inlineStr">
+        <is>
+          <t>Exact name as it appears in source schema</t>
+        </is>
+      </c>
+      <c r="D311" s="44" t="inlineStr">
+        <is>
+          <t>PURCHASEORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" s="25" t="inlineStr">
+        <is>
+          <t>Business purpose</t>
+        </is>
+      </c>
+      <c r="C312" s="24" t="inlineStr">
+        <is>
+          <t>What business process does this table record?</t>
+        </is>
+      </c>
+      <c r="D312" s="43" t="inlineStr">
+        <is>
+          <t>Purchase orders raised against vendors</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" s="25" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="C313" s="24" t="inlineStr">
+        <is>
+          <t>One row = one [what]? e.g. one invoice line, one work order</t>
+        </is>
+      </c>
+      <c r="D313" s="44" t="inlineStr">
+        <is>
+          <t>One row = one purchase order header</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="25" t="inlineStr">
+        <is>
+          <t>Total row count</t>
+        </is>
+      </c>
+      <c r="C314" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM table</t>
+        </is>
+      </c>
+      <c r="D314" s="43" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" s="25" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="C315" s="24" t="inlineStr">
+        <is>
+          <t>MIN and MAX of primary date field</t>
+        </is>
+      </c>
+      <c r="D315" s="44" t="inlineStr">
+        <is>
+          <t>2021-03-22 – 2026-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" s="25" t="inlineStr">
+        <is>
+          <t>Primary key field(s)</t>
+        </is>
+      </c>
+      <c r="C316" s="24" t="inlineStr">
+        <is>
+          <t>Field name(s) — is it a surrogate or natural key?</t>
+        </is>
+      </c>
+      <c r="D316" s="43" t="inlineStr">
+        <is>
+          <t>id (surrogate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" s="25" t="inlineStr">
+        <is>
+          <t>PK uniqueness check</t>
+        </is>
+      </c>
+      <c r="C317" s="24" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) vs COUNT(DISTINCT pk) — match = PASS</t>
+        </is>
+      </c>
+      <c r="D317" s="44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" s="25" t="inlineStr">
+        <is>
+          <t>Canonical domain</t>
+        </is>
+      </c>
+      <c r="C318" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical domain does this table feed? (Domain 1–5)</t>
+        </is>
+      </c>
+      <c r="D318" s="43" t="inlineStr">
+        <is>
+          <t>D5 – Financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" s="25" t="inlineStr">
+        <is>
+          <t>Canonical entities</t>
+        </is>
+      </c>
+      <c r="C319" s="24" t="inlineStr">
+        <is>
+          <t>Which canonical entities? e.g. WORK_ORDER, WORK_ORDER_LINE</t>
+        </is>
+      </c>
+      <c r="D319" s="44" t="inlineStr">
+        <is>
+          <t>PURCHASE_ORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="25" t="inlineStr">
+        <is>
+          <t>Overall table RAG</t>
+        </is>
+      </c>
+      <c r="C320" s="24" t="inlineStr">
+        <is>
+          <t>GREEN / AMBER / RED — your assessment of table usability</t>
+        </is>
+      </c>
+      <c r="D320" s="43" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" s="49" t="inlineStr">
+        <is>
+          <t>↳  Field-Level Quality — Key fields only (PK, FK, dates, amounts). Add rows as needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" s="45" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="C322" s="45" t="inlineStr">
+        <is>
+          <t>Field Type</t>
+        </is>
+      </c>
+      <c r="D322" s="45" t="inlineStr">
+        <is>
+          <t>Null %</t>
+        </is>
+      </c>
+      <c r="E322" s="45" t="inlineStr">
+        <is>
+          <t>Distinct Count</t>
+        </is>
+      </c>
+      <c r="F322" s="45" t="inlineStr">
+        <is>
+          <t>Min Value</t>
+        </is>
+      </c>
+      <c r="G322" s="45" t="inlineStr">
+        <is>
+          <t>Max Value</t>
+        </is>
+      </c>
+      <c r="H322" s="45" t="inlineStr">
+        <is>
+          <t>Notes / Issues</t>
+        </is>
+      </c>
+      <c r="I322" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" s="16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C323" s="16" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E323" s="16" t="n">
+        <v>800</v>
+      </c>
+      <c r="F323" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G323" s="16" t="n">
+        <v>800</v>
+      </c>
+      <c r="H323" s="16" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I323" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" s="15" t="inlineStr">
+        <is>
+          <t>tranid</t>
+        </is>
+      </c>
+      <c r="C324" s="15" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D324" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E324" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="F324" s="15" t="inlineStr">
+        <is>
+          <t>PO-00001</t>
+        </is>
+      </c>
+      <c r="G324" s="15" t="inlineStr">
+        <is>
+          <t>PO-00800</t>
+        </is>
+      </c>
+      <c r="H324" s="15" t="inlineStr">
+        <is>
+          <t>No nulls, no duplicates</t>
+        </is>
+      </c>
+      <c r="I324" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" s="16" t="inlineStr">
+        <is>
+          <t>trandate</t>
+        </is>
+      </c>
+      <c r="C325" s="16" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D325" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E325" s="16" t="n">
+        <v>647</v>
+      </c>
+      <c r="F325" s="16" t="inlineStr">
+        <is>
+          <t>2021-03-22</t>
+        </is>
+      </c>
+      <c r="G325" s="16" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="H325" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 647 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I325" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" s="15" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="C326" s="15" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D326" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E326" s="15" t="n">
+        <v>197</v>
+      </c>
+      <c r="F326" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G326" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="H326" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 197 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I326" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" s="16" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C327" s="16" t="inlineStr">
+        <is>
+          <t>DECIMAL</t>
+        </is>
+      </c>
+      <c r="D327" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E327" s="16" t="n">
+        <v>799</v>
+      </c>
+      <c r="F327" s="16" t="n">
+        <v>253.25</v>
+      </c>
+      <c r="G327" s="16" t="n">
+        <v>49869.28</v>
+      </c>
+      <c r="H327" s="16" t="inlineStr">
+        <is>
+          <t>No nulls; 799 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I327" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" s="15" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C328" s="15" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D328" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E328" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F328" s="15" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="G328" s="15" t="inlineStr">
+        <is>
+          <t>Pending Receipt</t>
+        </is>
+      </c>
+      <c r="H328" s="15" t="inlineStr">
+        <is>
+          <t>No nulls; 3 distinct value(s)</t>
+        </is>
+      </c>
+      <c r="I328" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" s="49" t="inlineStr">
+        <is>
+          <t>↳  Referential Integrity Checks — FK fields that should join to another table</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" s="45" t="inlineStr">
+        <is>
+          <t>FK Field</t>
+        </is>
+      </c>
+      <c r="C330" s="45" t="inlineStr">
+        <is>
+          <t>References Table</t>
+        </is>
+      </c>
+      <c r="D330" s="45" t="inlineStr">
+        <is>
+          <t>References Field</t>
+        </is>
+      </c>
+      <c r="E330" s="45" t="inlineStr">
+        <is>
+          <t>Orphan Row Count</t>
+        </is>
+      </c>
+      <c r="F330" s="45" t="inlineStr">
+        <is>
+          <t>Orphan %</t>
+        </is>
+      </c>
+      <c r="G330" s="45" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H330" s="45" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" s="16" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="C331" s="16" t="inlineStr">
+        <is>
+          <t>VENDOR</t>
+        </is>
+      </c>
+      <c r="D331" s="16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E331" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F331" s="16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G331" s="16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H331" s="16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" s="15" t="inlineStr">
+        <is>
+          <t>subsidiary_id</t>
+        </is>
+      </c>
+      <c r="C332" s="15" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="D332" s="15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E332" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F332" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G332" s="15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H332" s="15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" s="16" t="n"/>
+      <c r="C333" s="16" t="n"/>
+      <c r="D333" s="16" t="n"/>
+      <c r="E333" s="16" t="n"/>
+      <c r="F333" s="16" t="n"/>
+      <c r="G333" s="16" t="n"/>
+      <c r="H333" s="16" t="n"/>
+    </row>
+    <row r="334"/>
+    <row r="336">
+      <c r="B336" t="inlineStr">
         <is>
           <t>Section D – Data Freshness</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="B285" t="inlineStr">
+    <row r="337">
+      <c r="B337" t="inlineStr">
         <is>
           <t>CUSTOMER</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="C337" t="inlineStr">
         <is>
           <t>datecreated</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="F285" t="n">
-        <v>17</v>
-      </c>
-      <c r="G285" t="inlineStr">
+      <c r="F337" t="n">
+        <v>1</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Within SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>VENDOR</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>datecreated</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>10</v>
+      </c>
+      <c r="G338" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>17-day lag – investigate</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>VENDOR</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>10-day lag – investigate</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>5</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>5-day lag – investigate</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>TRANSACTION</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>trandate</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>1</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Within SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>TRANSACTIONLINE</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>No date field defined</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
         <is>
           <t>datecreated</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="F286" t="n">
-        <v>9</v>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>9-day lag – investigate</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>ITEM</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
+      <c r="F342" t="n">
+        <v>2</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Within SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>ACCOUNT</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
         <is>
           <t>lastmodifieddate</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>No date column</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>LOCATION</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>No date field defined</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>SUBSIDIARY</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>No date column</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>lastmodifieddate</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>No date column</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>SALESORDER</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>trandate</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
         <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
+      <c r="E347" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="F287" t="n">
+      <c r="F347" t="n">
         <v>1</v>
       </c>
-      <c r="G287" t="inlineStr">
+      <c r="G347" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
+      <c r="H347" t="inlineStr">
         <is>
           <t>Within SLA</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>TRANSACTION</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
+    <row r="348">
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>PURCHASEORDER</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
         <is>
           <t>trandate</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D348" t="inlineStr">
         <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
+      <c r="E348" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="F288" t="n">
+      <c r="F348" t="n">
         <v>1</v>
       </c>
-      <c r="G288" t="inlineStr">
+      <c r="G348" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
+      <c r="H348" t="inlineStr">
         <is>
           <t>Within SLA</t>
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>EMPLOYEE</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>datecreated</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="F289" t="n">
-        <v>7</v>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>7-day lag – investigate</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>ACCOUNT</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>lastmodifieddate</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>No date column</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>SUBSIDIARY</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>lastmodifieddate</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>No date column</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>DEPARTMENT</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>lastmodifieddate</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>No date column</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>SALESORDER</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>trandate</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="F293" t="n">
-        <v>1</v>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>Within SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>PURCHASEORDER</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>trandate</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="F294" t="n">
-        <v>2</v>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>Within SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="B296" t="inlineStr">
+    <row r="350">
+      <c r="B350" t="inlineStr">
         <is>
           <t>Section E – Engineer Summary</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="D297" t="inlineStr">
+    <row r="351">
+      <c r="D351" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
     </row>
-    <row r="298">
-      <c r="D298" t="inlineStr">
+    <row r="352">
+      <c r="D352" t="inlineStr">
         <is>
           <t>1. CUSTOMER email: 75 null (15.0%)
 2. VENDOR email: 36 null (18.0%)
@@ -9805,36 +11247,36 @@
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="D299" t="inlineStr">
+    <row r="353">
+      <c r="D353" t="inlineStr">
         <is>
           <t>Fabric Tables (pipeline confirmed PASS)</t>
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="D300" t="inlineStr">
+    <row r="354">
+      <c r="D354" t="inlineStr">
         <is>
           <t>CUSTOMER and VENDOR joinable on entity_id; EMPLOYEE separate</t>
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="D301" t="inlineStr">
+    <row r="355">
+      <c r="D355" t="inlineStr">
         <is>
           <t>None — pipeline accessible</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="D302" t="inlineStr">
+    <row r="356">
+      <c r="D356" t="inlineStr">
         <is>
           <t>Proceed to field-level profiling for TRANSACTION and CUSTOMER</t>
         </is>
       </c>
     </row>
-    <row r="303">
-      <c r="D303" t="inlineStr">
+    <row r="357">
+      <c r="D357" t="inlineStr">
         <is>
           <t>Confirm fiscal year definition used in trandate filters</t>
         </is>
